--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehrnia\Desktop\Job\AtlasCopco\Business Analysis Project and Stakeholder Management\Excel_PLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61DC408-47F7-4B7D-9374-0056F45553A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2B96CE-AD0B-4DBA-9C1E-623B6B9B74B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="1124">
   <si>
     <t>Description</t>
   </si>
@@ -3444,6 +3444,9 @@
   </si>
   <si>
     <t>COST BENEFIT ANALYSIS: CAPEX, OPEX, Payback and IRR Controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project: Multi-Site Pressure Reducing &amp; Power Generation </t>
   </si>
 </sst>
 </file>
@@ -3457,7 +3460,7 @@
     <numFmt numFmtId="166" formatCode="\$#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3687,6 +3690,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3992,7 +4003,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -4109,6 +4120,9 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4272,8 +4286,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -29742,14 +29754,14 @@
       <c r="R40" s="38"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="56" t="s">
+      <c r="A41" s="59" t="s">
         <v>1120</v>
       </c>
-      <c r="B41" s="56"/>
-      <c r="C41" s="56" t="s">
+      <c r="B41" s="59"/>
+      <c r="C41" s="59" t="s">
         <v>1121</v>
       </c>
-      <c r="D41" s="56"/>
+      <c r="D41" s="59"/>
       <c r="E41" s="39" t="s">
         <v>9</v>
       </c>
@@ -29770,10 +29782,10 @@
       <c r="R41" s="43"/>
     </row>
     <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="57"/>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
+      <c r="A42" s="60"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
       <c r="E42" s="44"/>
       <c r="F42" s="38"/>
       <c r="G42" s="38"/>
@@ -29862,38 +29874,38 @@
       <c r="R46" s="47"/>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="58" t="s">
+      <c r="A47" s="61" t="s">
         <v>1096</v>
       </c>
-      <c r="B47" s="59"/>
-      <c r="C47" s="64" t="s">
+      <c r="B47" s="62"/>
+      <c r="C47" s="67" t="s">
         <v>1097</v>
       </c>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="65"/>
-      <c r="L47" s="66"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="69"/>
       <c r="M47" s="38"/>
       <c r="N47" s="38"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="60"/>
-      <c r="B48" s="61"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="69"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="70"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="71"/>
+      <c r="L48" s="72"/>
       <c r="M48" s="38"/>
       <c r="N48" s="38"/>
       <c r="O48" s="41" t="s">
@@ -29904,28 +29916,28 @@
       <c r="R48" s="43"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="60"/>
-      <c r="B49" s="61"/>
-      <c r="C49" s="70" t="s">
+      <c r="A49" s="63"/>
+      <c r="B49" s="64"/>
+      <c r="C49" s="73" t="s">
         <v>1099</v>
       </c>
-      <c r="D49" s="71"/>
-      <c r="E49" s="70" t="s">
+      <c r="D49" s="74"/>
+      <c r="E49" s="73" t="s">
         <v>1100</v>
       </c>
-      <c r="F49" s="71"/>
-      <c r="G49" s="70" t="s">
+      <c r="F49" s="74"/>
+      <c r="G49" s="73" t="s">
         <v>1101</v>
       </c>
-      <c r="H49" s="71"/>
-      <c r="I49" s="74" t="s">
+      <c r="H49" s="74"/>
+      <c r="I49" s="77" t="s">
         <v>1102</v>
       </c>
-      <c r="J49" s="75"/>
-      <c r="K49" s="70" t="s">
+      <c r="J49" s="78"/>
+      <c r="K49" s="73" t="s">
         <v>1103</v>
       </c>
-      <c r="L49" s="71"/>
+      <c r="L49" s="74"/>
       <c r="M49" s="38"/>
       <c r="N49" s="38"/>
       <c r="O49" s="48" t="s">
@@ -29936,18 +29948,18 @@
       <c r="R49" s="43"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="62"/>
-      <c r="B50" s="63"/>
-      <c r="C50" s="72"/>
-      <c r="D50" s="73"/>
-      <c r="E50" s="72"/>
-      <c r="F50" s="73"/>
-      <c r="G50" s="72"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="76"/>
-      <c r="J50" s="77"/>
-      <c r="K50" s="72"/>
-      <c r="L50" s="73"/>
+      <c r="A50" s="65"/>
+      <c r="B50" s="66"/>
+      <c r="C50" s="75"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="79"/>
+      <c r="J50" s="80"/>
+      <c r="K50" s="75"/>
+      <c r="L50" s="76"/>
       <c r="M50" s="38"/>
       <c r="N50" s="38"/>
       <c r="O50" s="48" t="s">
@@ -29958,32 +29970,32 @@
       <c r="R50" s="43"/>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="78" t="s">
+      <c r="A51" s="81" t="s">
         <v>1106</v>
       </c>
-      <c r="B51" s="81" t="s">
+      <c r="B51" s="84" t="s">
         <v>1107</v>
       </c>
-      <c r="C51" s="84" t="s">
+      <c r="C51" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="85"/>
-      <c r="E51" s="90" t="s">
+      <c r="D51" s="88"/>
+      <c r="E51" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="91"/>
-      <c r="G51" s="96" t="s">
+      <c r="F51" s="94"/>
+      <c r="G51" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="97"/>
-      <c r="I51" s="96" t="s">
+      <c r="H51" s="100"/>
+      <c r="I51" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="97"/>
-      <c r="K51" s="96" t="s">
+      <c r="J51" s="100"/>
+      <c r="K51" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="97"/>
+      <c r="L51" s="100"/>
       <c r="M51" s="38"/>
       <c r="N51" s="38"/>
       <c r="O51" s="48" t="s">
@@ -29994,18 +30006,18 @@
       <c r="R51" s="43"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="79"/>
-      <c r="B52" s="82"/>
-      <c r="C52" s="86"/>
-      <c r="D52" s="87"/>
-      <c r="E52" s="92"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="98"/>
-      <c r="H52" s="99"/>
-      <c r="I52" s="98"/>
-      <c r="J52" s="99"/>
-      <c r="K52" s="98"/>
-      <c r="L52" s="99"/>
+      <c r="A52" s="82"/>
+      <c r="B52" s="85"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="95"/>
+      <c r="F52" s="96"/>
+      <c r="G52" s="101"/>
+      <c r="H52" s="102"/>
+      <c r="I52" s="101"/>
+      <c r="J52" s="102"/>
+      <c r="K52" s="101"/>
+      <c r="L52" s="102"/>
       <c r="M52" s="38"/>
       <c r="N52" s="38"/>
       <c r="O52" s="48" t="s">
@@ -30016,18 +30028,18 @@
       <c r="R52" s="43"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="79"/>
-      <c r="B53" s="82"/>
-      <c r="C53" s="86"/>
-      <c r="D53" s="87"/>
-      <c r="E53" s="92"/>
-      <c r="F53" s="93"/>
-      <c r="G53" s="98"/>
-      <c r="H53" s="99"/>
-      <c r="I53" s="98"/>
-      <c r="J53" s="99"/>
-      <c r="K53" s="98"/>
-      <c r="L53" s="99"/>
+      <c r="A53" s="82"/>
+      <c r="B53" s="85"/>
+      <c r="C53" s="89"/>
+      <c r="D53" s="90"/>
+      <c r="E53" s="95"/>
+      <c r="F53" s="96"/>
+      <c r="G53" s="101"/>
+      <c r="H53" s="102"/>
+      <c r="I53" s="101"/>
+      <c r="J53" s="102"/>
+      <c r="K53" s="101"/>
+      <c r="L53" s="102"/>
       <c r="M53" s="38"/>
       <c r="N53" s="38"/>
       <c r="O53" s="45" t="s">
@@ -30038,34 +30050,34 @@
       <c r="R53" s="47"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="79"/>
-      <c r="B54" s="82"/>
-      <c r="C54" s="86"/>
-      <c r="D54" s="87"/>
-      <c r="E54" s="92"/>
-      <c r="F54" s="93"/>
-      <c r="G54" s="98"/>
-      <c r="H54" s="99"/>
-      <c r="I54" s="98"/>
-      <c r="J54" s="99"/>
-      <c r="K54" s="98"/>
-      <c r="L54" s="99"/>
+      <c r="A54" s="82"/>
+      <c r="B54" s="85"/>
+      <c r="C54" s="89"/>
+      <c r="D54" s="90"/>
+      <c r="E54" s="95"/>
+      <c r="F54" s="96"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="102"/>
+      <c r="I54" s="101"/>
+      <c r="J54" s="102"/>
+      <c r="K54" s="101"/>
+      <c r="L54" s="102"/>
       <c r="M54" s="38"/>
       <c r="N54" s="38"/>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="79"/>
-      <c r="B55" s="83"/>
-      <c r="C55" s="88"/>
-      <c r="D55" s="89"/>
-      <c r="E55" s="94"/>
-      <c r="F55" s="95"/>
-      <c r="G55" s="100"/>
-      <c r="H55" s="101"/>
-      <c r="I55" s="100"/>
-      <c r="J55" s="101"/>
-      <c r="K55" s="100"/>
-      <c r="L55" s="101"/>
+      <c r="A55" s="82"/>
+      <c r="B55" s="86"/>
+      <c r="C55" s="91"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="97"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="103"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="103"/>
+      <c r="J55" s="104"/>
+      <c r="K55" s="103"/>
+      <c r="L55" s="104"/>
       <c r="M55" s="38"/>
       <c r="N55" s="38"/>
       <c r="O55" s="41" t="s">
@@ -30076,30 +30088,30 @@
       <c r="R55" s="43"/>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="79"/>
-      <c r="B56" s="81" t="s">
+      <c r="A56" s="82"/>
+      <c r="B56" s="84" t="s">
         <v>1112</v>
       </c>
-      <c r="C56" s="84" t="s">
+      <c r="C56" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="85"/>
-      <c r="E56" s="90" t="s">
+      <c r="D56" s="88"/>
+      <c r="E56" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="91"/>
-      <c r="G56" s="90" t="s">
+      <c r="F56" s="94"/>
+      <c r="G56" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="91"/>
-      <c r="I56" s="96" t="s">
+      <c r="H56" s="94"/>
+      <c r="I56" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="97"/>
-      <c r="K56" s="96" t="s">
+      <c r="J56" s="100"/>
+      <c r="K56" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="97"/>
+      <c r="L56" s="100"/>
       <c r="M56" s="38"/>
       <c r="N56" s="38"/>
       <c r="O56" s="48" t="s">
@@ -30110,18 +30122,18 @@
       <c r="R56" s="43"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="79"/>
-      <c r="B57" s="82"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="87"/>
-      <c r="E57" s="92"/>
-      <c r="F57" s="93"/>
-      <c r="G57" s="92"/>
-      <c r="H57" s="93"/>
-      <c r="I57" s="98"/>
-      <c r="J57" s="99"/>
-      <c r="K57" s="98"/>
-      <c r="L57" s="99"/>
+      <c r="A57" s="82"/>
+      <c r="B57" s="85"/>
+      <c r="C57" s="89"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="95"/>
+      <c r="F57" s="96"/>
+      <c r="G57" s="95"/>
+      <c r="H57" s="96"/>
+      <c r="I57" s="101"/>
+      <c r="J57" s="102"/>
+      <c r="K57" s="101"/>
+      <c r="L57" s="102"/>
       <c r="M57" s="38"/>
       <c r="N57" s="38"/>
       <c r="O57" s="48" t="s">
@@ -30132,18 +30144,18 @@
       <c r="R57" s="43"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="79"/>
-      <c r="B58" s="82"/>
-      <c r="C58" s="86"/>
-      <c r="D58" s="87"/>
-      <c r="E58" s="92"/>
-      <c r="F58" s="93"/>
-      <c r="G58" s="92"/>
-      <c r="H58" s="93"/>
-      <c r="I58" s="98"/>
-      <c r="J58" s="99"/>
-      <c r="K58" s="98"/>
-      <c r="L58" s="99"/>
+      <c r="A58" s="82"/>
+      <c r="B58" s="85"/>
+      <c r="C58" s="89"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="95"/>
+      <c r="F58" s="96"/>
+      <c r="G58" s="95"/>
+      <c r="H58" s="96"/>
+      <c r="I58" s="101"/>
+      <c r="J58" s="102"/>
+      <c r="K58" s="101"/>
+      <c r="L58" s="102"/>
       <c r="M58" s="38"/>
       <c r="N58" s="38"/>
       <c r="O58" s="48" t="s">
@@ -30154,18 +30166,18 @@
       <c r="R58" s="43"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="79"/>
-      <c r="B59" s="82"/>
-      <c r="C59" s="86"/>
-      <c r="D59" s="87"/>
-      <c r="E59" s="92"/>
-      <c r="F59" s="93"/>
-      <c r="G59" s="92"/>
-      <c r="H59" s="93"/>
-      <c r="I59" s="98"/>
-      <c r="J59" s="99"/>
-      <c r="K59" s="98"/>
-      <c r="L59" s="99"/>
+      <c r="A59" s="82"/>
+      <c r="B59" s="85"/>
+      <c r="C59" s="89"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="95"/>
+      <c r="F59" s="96"/>
+      <c r="G59" s="95"/>
+      <c r="H59" s="96"/>
+      <c r="I59" s="101"/>
+      <c r="J59" s="102"/>
+      <c r="K59" s="101"/>
+      <c r="L59" s="102"/>
       <c r="M59" s="38"/>
       <c r="N59" s="38"/>
       <c r="O59" s="45" t="s">
@@ -30176,18 +30188,18 @@
       <c r="R59" s="47"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="79"/>
-      <c r="B60" s="83"/>
-      <c r="C60" s="88"/>
-      <c r="D60" s="89"/>
-      <c r="E60" s="94"/>
-      <c r="F60" s="95"/>
-      <c r="G60" s="94"/>
-      <c r="H60" s="95"/>
-      <c r="I60" s="100"/>
-      <c r="J60" s="101"/>
-      <c r="K60" s="100"/>
-      <c r="L60" s="101"/>
+      <c r="A60" s="82"/>
+      <c r="B60" s="86"/>
+      <c r="C60" s="91"/>
+      <c r="D60" s="92"/>
+      <c r="E60" s="97"/>
+      <c r="F60" s="98"/>
+      <c r="G60" s="97"/>
+      <c r="H60" s="98"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="103"/>
+      <c r="L60" s="104"/>
       <c r="M60" s="38"/>
       <c r="N60" s="38"/>
       <c r="O60" s="38"/>
@@ -30196,30 +30208,30 @@
       <c r="R60" s="38"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="79"/>
-      <c r="B61" s="81" t="s">
+      <c r="A61" s="82"/>
+      <c r="B61" s="84" t="s">
         <v>1117</v>
       </c>
-      <c r="C61" s="102" t="s">
+      <c r="C61" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="103"/>
-      <c r="E61" s="84" t="s">
+      <c r="D61" s="106"/>
+      <c r="E61" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="85"/>
-      <c r="G61" s="90" t="s">
+      <c r="F61" s="88"/>
+      <c r="G61" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="91"/>
-      <c r="I61" s="90" t="s">
+      <c r="H61" s="94"/>
+      <c r="I61" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="91"/>
-      <c r="K61" s="96" t="s">
+      <c r="J61" s="94"/>
+      <c r="K61" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="97"/>
+      <c r="L61" s="100"/>
       <c r="M61" s="38"/>
       <c r="N61" s="38"/>
       <c r="O61" s="38"/>
@@ -30228,18 +30240,18 @@
       <c r="R61" s="38"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="79"/>
-      <c r="B62" s="82"/>
-      <c r="C62" s="104"/>
-      <c r="D62" s="105"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="87"/>
-      <c r="G62" s="92"/>
-      <c r="H62" s="93"/>
-      <c r="I62" s="92"/>
-      <c r="J62" s="93"/>
-      <c r="K62" s="98"/>
-      <c r="L62" s="99"/>
+      <c r="A62" s="82"/>
+      <c r="B62" s="85"/>
+      <c r="C62" s="107"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="95"/>
+      <c r="H62" s="96"/>
+      <c r="I62" s="95"/>
+      <c r="J62" s="96"/>
+      <c r="K62" s="101"/>
+      <c r="L62" s="102"/>
       <c r="M62" s="38"/>
       <c r="N62" s="38"/>
       <c r="O62" s="38"/>
@@ -30248,18 +30260,18 @@
       <c r="R62" s="38"/>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="79"/>
-      <c r="B63" s="82"/>
-      <c r="C63" s="104"/>
-      <c r="D63" s="105"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="87"/>
-      <c r="G63" s="92"/>
-      <c r="H63" s="93"/>
-      <c r="I63" s="92"/>
-      <c r="J63" s="93"/>
-      <c r="K63" s="98"/>
-      <c r="L63" s="99"/>
+      <c r="A63" s="82"/>
+      <c r="B63" s="85"/>
+      <c r="C63" s="107"/>
+      <c r="D63" s="108"/>
+      <c r="E63" s="89"/>
+      <c r="F63" s="90"/>
+      <c r="G63" s="95"/>
+      <c r="H63" s="96"/>
+      <c r="I63" s="95"/>
+      <c r="J63" s="96"/>
+      <c r="K63" s="101"/>
+      <c r="L63" s="102"/>
       <c r="M63" s="38"/>
       <c r="N63" s="38"/>
       <c r="O63" s="38"/>
@@ -30268,18 +30280,18 @@
       <c r="R63" s="38"/>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="79"/>
-      <c r="B64" s="82"/>
-      <c r="C64" s="104"/>
-      <c r="D64" s="105"/>
-      <c r="E64" s="86"/>
-      <c r="F64" s="87"/>
-      <c r="G64" s="92"/>
-      <c r="H64" s="93"/>
-      <c r="I64" s="92"/>
-      <c r="J64" s="93"/>
-      <c r="K64" s="98"/>
-      <c r="L64" s="99"/>
+      <c r="A64" s="82"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="107"/>
+      <c r="D64" s="108"/>
+      <c r="E64" s="89"/>
+      <c r="F64" s="90"/>
+      <c r="G64" s="95"/>
+      <c r="H64" s="96"/>
+      <c r="I64" s="95"/>
+      <c r="J64" s="96"/>
+      <c r="K64" s="101"/>
+      <c r="L64" s="102"/>
       <c r="M64" s="38"/>
       <c r="N64" s="38"/>
       <c r="O64" s="38"/>
@@ -30288,18 +30300,18 @@
       <c r="R64" s="38"/>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="79"/>
-      <c r="B65" s="83"/>
-      <c r="C65" s="106"/>
-      <c r="D65" s="107"/>
-      <c r="E65" s="88"/>
-      <c r="F65" s="89"/>
-      <c r="G65" s="94"/>
-      <c r="H65" s="95"/>
-      <c r="I65" s="94"/>
-      <c r="J65" s="95"/>
-      <c r="K65" s="100"/>
-      <c r="L65" s="101"/>
+      <c r="A65" s="82"/>
+      <c r="B65" s="86"/>
+      <c r="C65" s="109"/>
+      <c r="D65" s="110"/>
+      <c r="E65" s="91"/>
+      <c r="F65" s="92"/>
+      <c r="G65" s="97"/>
+      <c r="H65" s="98"/>
+      <c r="I65" s="97"/>
+      <c r="J65" s="98"/>
+      <c r="K65" s="103"/>
+      <c r="L65" s="104"/>
       <c r="M65" s="38"/>
       <c r="N65" s="38"/>
       <c r="O65" s="38"/>
@@ -30308,30 +30320,30 @@
       <c r="R65" s="38"/>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="79"/>
-      <c r="B66" s="81" t="s">
+      <c r="A66" s="82"/>
+      <c r="B66" s="84" t="s">
         <v>1118</v>
       </c>
-      <c r="C66" s="102" t="s">
+      <c r="C66" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="103"/>
-      <c r="E66" s="102" t="s">
+      <c r="D66" s="106"/>
+      <c r="E66" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="103"/>
-      <c r="G66" s="84" t="s">
+      <c r="F66" s="106"/>
+      <c r="G66" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="85"/>
-      <c r="I66" s="84" t="s">
+      <c r="H66" s="88"/>
+      <c r="I66" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="85"/>
-      <c r="K66" s="90" t="s">
+      <c r="J66" s="88"/>
+      <c r="K66" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="91"/>
+      <c r="L66" s="94"/>
       <c r="M66" s="38"/>
       <c r="N66" s="38"/>
       <c r="O66" s="38"/>
@@ -30340,18 +30352,18 @@
       <c r="R66" s="38"/>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="79"/>
-      <c r="B67" s="82"/>
-      <c r="C67" s="104"/>
-      <c r="D67" s="105"/>
-      <c r="E67" s="104"/>
-      <c r="F67" s="105"/>
-      <c r="G67" s="86"/>
-      <c r="H67" s="87"/>
-      <c r="I67" s="86"/>
-      <c r="J67" s="87"/>
-      <c r="K67" s="92"/>
-      <c r="L67" s="93"/>
+      <c r="A67" s="82"/>
+      <c r="B67" s="85"/>
+      <c r="C67" s="107"/>
+      <c r="D67" s="108"/>
+      <c r="E67" s="107"/>
+      <c r="F67" s="108"/>
+      <c r="G67" s="89"/>
+      <c r="H67" s="90"/>
+      <c r="I67" s="89"/>
+      <c r="J67" s="90"/>
+      <c r="K67" s="95"/>
+      <c r="L67" s="96"/>
       <c r="M67" s="38"/>
       <c r="N67" s="38"/>
       <c r="O67" s="38"/>
@@ -30360,18 +30372,18 @@
       <c r="R67" s="38"/>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="79"/>
-      <c r="B68" s="82"/>
-      <c r="C68" s="104"/>
-      <c r="D68" s="105"/>
-      <c r="E68" s="104"/>
-      <c r="F68" s="105"/>
-      <c r="G68" s="86"/>
-      <c r="H68" s="87"/>
-      <c r="I68" s="86"/>
-      <c r="J68" s="87"/>
-      <c r="K68" s="92"/>
-      <c r="L68" s="93"/>
+      <c r="A68" s="82"/>
+      <c r="B68" s="85"/>
+      <c r="C68" s="107"/>
+      <c r="D68" s="108"/>
+      <c r="E68" s="107"/>
+      <c r="F68" s="108"/>
+      <c r="G68" s="89"/>
+      <c r="H68" s="90"/>
+      <c r="I68" s="89"/>
+      <c r="J68" s="90"/>
+      <c r="K68" s="95"/>
+      <c r="L68" s="96"/>
       <c r="M68" s="38"/>
       <c r="N68" s="38"/>
       <c r="O68" s="38"/>
@@ -30380,18 +30392,18 @@
       <c r="R68" s="38"/>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="79"/>
-      <c r="B69" s="82"/>
-      <c r="C69" s="104"/>
-      <c r="D69" s="105"/>
-      <c r="E69" s="104"/>
-      <c r="F69" s="105"/>
-      <c r="G69" s="86"/>
-      <c r="H69" s="87"/>
-      <c r="I69" s="86"/>
-      <c r="J69" s="87"/>
-      <c r="K69" s="92"/>
-      <c r="L69" s="93"/>
+      <c r="A69" s="82"/>
+      <c r="B69" s="85"/>
+      <c r="C69" s="107"/>
+      <c r="D69" s="108"/>
+      <c r="E69" s="107"/>
+      <c r="F69" s="108"/>
+      <c r="G69" s="89"/>
+      <c r="H69" s="90"/>
+      <c r="I69" s="89"/>
+      <c r="J69" s="90"/>
+      <c r="K69" s="95"/>
+      <c r="L69" s="96"/>
       <c r="M69" s="38"/>
       <c r="N69" s="38"/>
       <c r="O69" s="38"/>
@@ -30400,18 +30412,18 @@
       <c r="R69" s="38"/>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="79"/>
-      <c r="B70" s="83"/>
-      <c r="C70" s="106"/>
-      <c r="D70" s="107"/>
-      <c r="E70" s="106"/>
-      <c r="F70" s="107"/>
-      <c r="G70" s="88"/>
-      <c r="H70" s="89"/>
-      <c r="I70" s="88"/>
-      <c r="J70" s="89"/>
-      <c r="K70" s="94"/>
-      <c r="L70" s="95"/>
+      <c r="A70" s="82"/>
+      <c r="B70" s="86"/>
+      <c r="C70" s="109"/>
+      <c r="D70" s="110"/>
+      <c r="E70" s="109"/>
+      <c r="F70" s="110"/>
+      <c r="G70" s="91"/>
+      <c r="H70" s="92"/>
+      <c r="I70" s="91"/>
+      <c r="J70" s="92"/>
+      <c r="K70" s="97"/>
+      <c r="L70" s="98"/>
       <c r="M70" s="38"/>
       <c r="N70" s="38"/>
       <c r="O70" s="38"/>
@@ -30420,30 +30432,30 @@
       <c r="R70" s="38"/>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="79"/>
-      <c r="B71" s="81" t="s">
+      <c r="A71" s="82"/>
+      <c r="B71" s="84" t="s">
         <v>1119</v>
       </c>
-      <c r="C71" s="102" t="s">
+      <c r="C71" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="103"/>
-      <c r="E71" s="102" t="s">
+      <c r="D71" s="106"/>
+      <c r="E71" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="103"/>
-      <c r="G71" s="102" t="s">
+      <c r="F71" s="106"/>
+      <c r="G71" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="H71" s="103"/>
-      <c r="I71" s="102" t="s">
+      <c r="H71" s="106"/>
+      <c r="I71" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="103"/>
-      <c r="K71" s="84" t="s">
+      <c r="J71" s="106"/>
+      <c r="K71" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="85"/>
+      <c r="L71" s="88"/>
       <c r="M71" s="38"/>
       <c r="N71" s="38"/>
       <c r="O71" s="38"/>
@@ -30452,18 +30464,18 @@
       <c r="R71" s="38"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="79"/>
-      <c r="B72" s="82"/>
-      <c r="C72" s="104"/>
-      <c r="D72" s="105"/>
-      <c r="E72" s="104"/>
-      <c r="F72" s="105"/>
-      <c r="G72" s="104"/>
-      <c r="H72" s="105"/>
-      <c r="I72" s="104"/>
-      <c r="J72" s="105"/>
-      <c r="K72" s="86"/>
-      <c r="L72" s="87"/>
+      <c r="A72" s="82"/>
+      <c r="B72" s="85"/>
+      <c r="C72" s="107"/>
+      <c r="D72" s="108"/>
+      <c r="E72" s="107"/>
+      <c r="F72" s="108"/>
+      <c r="G72" s="107"/>
+      <c r="H72" s="108"/>
+      <c r="I72" s="107"/>
+      <c r="J72" s="108"/>
+      <c r="K72" s="89"/>
+      <c r="L72" s="90"/>
       <c r="M72" s="38"/>
       <c r="N72" s="38"/>
       <c r="O72" s="38"/>
@@ -30472,18 +30484,18 @@
       <c r="R72" s="38"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="79"/>
-      <c r="B73" s="82"/>
-      <c r="C73" s="104"/>
-      <c r="D73" s="105"/>
-      <c r="E73" s="104"/>
-      <c r="F73" s="105"/>
-      <c r="G73" s="104"/>
-      <c r="H73" s="105"/>
-      <c r="I73" s="104"/>
-      <c r="J73" s="105"/>
-      <c r="K73" s="86"/>
-      <c r="L73" s="87"/>
+      <c r="A73" s="82"/>
+      <c r="B73" s="85"/>
+      <c r="C73" s="107"/>
+      <c r="D73" s="108"/>
+      <c r="E73" s="107"/>
+      <c r="F73" s="108"/>
+      <c r="G73" s="107"/>
+      <c r="H73" s="108"/>
+      <c r="I73" s="107"/>
+      <c r="J73" s="108"/>
+      <c r="K73" s="89"/>
+      <c r="L73" s="90"/>
       <c r="M73" s="38"/>
       <c r="N73" s="38"/>
       <c r="O73" s="38"/>
@@ -30492,18 +30504,18 @@
       <c r="R73" s="38"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="79"/>
-      <c r="B74" s="82"/>
-      <c r="C74" s="104"/>
-      <c r="D74" s="105"/>
-      <c r="E74" s="104"/>
-      <c r="F74" s="105"/>
-      <c r="G74" s="104"/>
-      <c r="H74" s="105"/>
-      <c r="I74" s="104"/>
-      <c r="J74" s="105"/>
-      <c r="K74" s="86"/>
-      <c r="L74" s="87"/>
+      <c r="A74" s="82"/>
+      <c r="B74" s="85"/>
+      <c r="C74" s="107"/>
+      <c r="D74" s="108"/>
+      <c r="E74" s="107"/>
+      <c r="F74" s="108"/>
+      <c r="G74" s="107"/>
+      <c r="H74" s="108"/>
+      <c r="I74" s="107"/>
+      <c r="J74" s="108"/>
+      <c r="K74" s="89"/>
+      <c r="L74" s="90"/>
       <c r="M74" s="38"/>
       <c r="N74" s="38"/>
       <c r="O74" s="38"/>
@@ -30512,18 +30524,18 @@
       <c r="R74" s="38"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="80"/>
-      <c r="B75" s="83"/>
-      <c r="C75" s="106"/>
-      <c r="D75" s="107"/>
-      <c r="E75" s="106"/>
-      <c r="F75" s="107"/>
-      <c r="G75" s="106"/>
-      <c r="H75" s="107"/>
-      <c r="I75" s="106"/>
-      <c r="J75" s="107"/>
-      <c r="K75" s="88"/>
-      <c r="L75" s="89"/>
+      <c r="A75" s="83"/>
+      <c r="B75" s="86"/>
+      <c r="C75" s="109"/>
+      <c r="D75" s="110"/>
+      <c r="E75" s="109"/>
+      <c r="F75" s="110"/>
+      <c r="G75" s="109"/>
+      <c r="H75" s="110"/>
+      <c r="I75" s="109"/>
+      <c r="J75" s="110"/>
+      <c r="K75" s="91"/>
+      <c r="L75" s="92"/>
       <c r="M75" s="38"/>
       <c r="N75" s="38"/>
       <c r="O75" s="38"/>
@@ -30620,9 +30632,11 @@
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
+      <c r="D1" s="58" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
@@ -30818,7 +30832,7 @@
       <c r="BI3"/>
     </row>
     <row r="4" spans="1:61" ht="15.75">
-      <c r="A4" s="111" t="s">
+      <c r="A4" s="56" t="s">
         <v>680</v>
       </c>
       <c r="B4">
@@ -30893,7 +30907,7 @@
       <c r="BI4"/>
     </row>
     <row r="5" spans="1:61" ht="15.75">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="56" t="s">
         <v>683</v>
       </c>
       <c r="B5">
@@ -30968,7 +30982,7 @@
       <c r="BI5"/>
     </row>
     <row r="6" spans="1:61" ht="15.75" hidden="1">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="56" t="s">
         <v>685</v>
       </c>
       <c r="B6">
@@ -31043,7 +31057,7 @@
       <c r="BI6"/>
     </row>
     <row r="7" spans="1:61" ht="15.75" hidden="1">
-      <c r="A7" s="111" t="s">
+      <c r="A7" s="56" t="s">
         <v>687</v>
       </c>
       <c r="B7">
@@ -31118,7 +31132,7 @@
       <c r="BI7"/>
     </row>
     <row r="8" spans="1:61" ht="15.75" hidden="1">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="56" t="s">
         <v>689</v>
       </c>
       <c r="B8">
@@ -31193,7 +31207,7 @@
       <c r="BI8"/>
     </row>
     <row r="9" spans="1:61" ht="15.75" hidden="1">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="56" t="s">
         <v>691</v>
       </c>
       <c r="B9">
@@ -31268,7 +31282,7 @@
       <c r="BI9"/>
     </row>
     <row r="10" spans="1:61" ht="15.75" hidden="1">
-      <c r="A10" s="111" t="s">
+      <c r="A10" s="56" t="s">
         <v>694</v>
       </c>
       <c r="B10">
@@ -31343,7 +31357,7 @@
       <c r="BI10"/>
     </row>
     <row r="11" spans="1:61" ht="15.75" hidden="1">
-      <c r="A11" s="111" t="s">
+      <c r="A11" s="56" t="s">
         <v>697</v>
       </c>
       <c r="B11">
@@ -31418,7 +31432,7 @@
       <c r="BI11"/>
     </row>
     <row r="12" spans="1:61" ht="15.75" hidden="1">
-      <c r="A12" s="111" t="s">
+      <c r="A12" s="56" t="s">
         <v>699</v>
       </c>
       <c r="B12">
@@ -31493,7 +31507,7 @@
       <c r="BI12"/>
     </row>
     <row r="13" spans="1:61" ht="15.75" hidden="1">
-      <c r="A13" s="111" t="s">
+      <c r="A13" s="56" t="s">
         <v>701</v>
       </c>
       <c r="B13">
@@ -31568,7 +31582,7 @@
       <c r="BI13"/>
     </row>
     <row r="14" spans="1:61" ht="15.75" hidden="1">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="56" t="s">
         <v>703</v>
       </c>
       <c r="B14">
@@ -31644,7 +31658,7 @@
       <c r="BI14"/>
     </row>
     <row r="15" spans="1:61" s="4" customFormat="1" ht="15.75" hidden="1">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="56" t="s">
         <v>705</v>
       </c>
       <c r="B15">
@@ -31719,7 +31733,7 @@
       <c r="BI15"/>
     </row>
     <row r="16" spans="1:61" ht="15.75" hidden="1">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="56" t="s">
         <v>707</v>
       </c>
       <c r="B16">
@@ -31794,7 +31808,7 @@
       <c r="BI16"/>
     </row>
     <row r="17" spans="1:61" ht="15.75" hidden="1">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="56" t="s">
         <v>709</v>
       </c>
       <c r="B17">
@@ -31869,7 +31883,7 @@
       <c r="BI17"/>
     </row>
     <row r="18" spans="1:61" ht="15.75">
-      <c r="A18" s="111" t="s">
+      <c r="A18" s="56" t="s">
         <v>711</v>
       </c>
       <c r="B18">
@@ -31944,7 +31958,7 @@
       <c r="BI18"/>
     </row>
     <row r="19" spans="1:61" ht="15.75">
-      <c r="A19" s="111" t="s">
+      <c r="A19" s="56" t="s">
         <v>714</v>
       </c>
       <c r="B19">
@@ -32019,7 +32033,7 @@
       <c r="BI19"/>
     </row>
     <row r="20" spans="1:61" ht="15.75" hidden="1">
-      <c r="A20" s="111"/>
+      <c r="A20" s="56"/>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -32082,7 +32096,7 @@
       <c r="BI20"/>
     </row>
     <row r="21" spans="1:61" ht="15.75" hidden="1">
-      <c r="A21" s="111" t="s">
+      <c r="A21" s="56" t="s">
         <v>717</v>
       </c>
       <c r="B21" t="s">
@@ -32157,7 +32171,7 @@
       <c r="BI21"/>
     </row>
     <row r="22" spans="1:61" ht="15.75">
-      <c r="A22" s="111" t="s">
+      <c r="A22" s="56" t="s">
         <v>720</v>
       </c>
       <c r="B22">
@@ -32233,7 +32247,7 @@
       <c r="BI22"/>
     </row>
     <row r="23" spans="1:61" ht="15.75">
-      <c r="A23" s="111" t="s">
+      <c r="A23" s="56" t="s">
         <v>722</v>
       </c>
       <c r="B23">
@@ -32309,7 +32323,7 @@
       <c r="BI23"/>
     </row>
     <row r="24" spans="1:61" ht="15.75">
-      <c r="A24" s="111" t="s">
+      <c r="A24" s="56" t="s">
         <v>725</v>
       </c>
       <c r="B24">
@@ -32385,7 +32399,7 @@
       <c r="BI24"/>
     </row>
     <row r="25" spans="1:61" ht="15.75">
-      <c r="A25" s="111" t="s">
+      <c r="A25" s="56" t="s">
         <v>727</v>
       </c>
       <c r="B25">
@@ -32461,7 +32475,7 @@
       <c r="BI25"/>
     </row>
     <row r="26" spans="1:61" ht="15.75">
-      <c r="A26" s="111" t="s">
+      <c r="A26" s="56" t="s">
         <v>729</v>
       </c>
       <c r="B26">
@@ -32537,7 +32551,7 @@
       <c r="BI26"/>
     </row>
     <row r="27" spans="1:61" ht="15.75">
-      <c r="A27" s="111" t="s">
+      <c r="A27" s="56" t="s">
         <v>731</v>
       </c>
       <c r="B27">
@@ -32613,7 +32627,7 @@
       <c r="BI27"/>
     </row>
     <row r="28" spans="1:61" ht="15.75">
-      <c r="A28" s="111" t="s">
+      <c r="A28" s="56" t="s">
         <v>22</v>
       </c>
       <c r="B28">
@@ -32689,7 +32703,7 @@
       <c r="BI28"/>
     </row>
     <row r="29" spans="1:61" ht="15.75">
-      <c r="A29" s="112" t="s">
+      <c r="A29" s="57" t="s">
         <v>246</v>
       </c>
       <c r="B29">
@@ -32764,7 +32778,7 @@
       <c r="BI29"/>
     </row>
     <row r="30" spans="1:61" ht="15.75">
-      <c r="A30" s="111" t="s">
+      <c r="A30" s="56" t="s">
         <v>736</v>
       </c>
       <c r="B30">
@@ -32840,7 +32854,7 @@
       <c r="BI30"/>
     </row>
     <row r="31" spans="1:61" ht="15.75">
-      <c r="A31" s="111" t="s">
+      <c r="A31" s="56" t="s">
         <v>738</v>
       </c>
       <c r="B31" s="16">
@@ -32916,7 +32930,7 @@
       <c r="BI31"/>
     </row>
     <row r="32" spans="1:61" ht="15.75">
-      <c r="A32" s="111" t="s">
+      <c r="A32" s="56" t="s">
         <v>741</v>
       </c>
       <c r="B32" t="str">
@@ -32992,7 +33006,7 @@
       <c r="BI32"/>
     </row>
     <row r="33" spans="1:61" ht="15.75">
-      <c r="A33" s="111" t="s">
+      <c r="A33" s="56" t="s">
         <v>744</v>
       </c>
       <c r="B33" t="str">
@@ -33068,7 +33082,7 @@
       <c r="BI33"/>
     </row>
     <row r="34" spans="1:61" ht="15.75">
-      <c r="A34" s="111"/>
+      <c r="A34" s="56"/>
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -33131,7 +33145,7 @@
       <c r="BI34"/>
     </row>
     <row r="35" spans="1:61" ht="15.75">
-      <c r="A35" s="111" t="s">
+      <c r="A35" s="56" t="s">
         <v>747</v>
       </c>
       <c r="B35">
@@ -33218,7 +33232,7 @@
       <c r="BI35"/>
     </row>
     <row r="36" spans="1:61" ht="15.75">
-      <c r="A36" s="111" t="s">
+      <c r="A36" s="56" t="s">
         <v>748</v>
       </c>
       <c r="B36">
@@ -33316,7 +33330,7 @@
       <c r="BI36"/>
     </row>
     <row r="37" spans="1:61" ht="15.75">
-      <c r="A37" s="111"/>
+      <c r="A37" s="56"/>
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -33379,7 +33393,7 @@
       <c r="BI37"/>
     </row>
     <row r="38" spans="1:61" ht="15.75">
-      <c r="A38" s="111"/>
+      <c r="A38" s="56"/>
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -33442,7 +33456,7 @@
       <c r="BI38"/>
     </row>
     <row r="39" spans="1:61" ht="15.75">
-      <c r="A39" s="111" t="s">
+      <c r="A39" s="56" t="s">
         <v>749</v>
       </c>
       <c r="B39" t="s">
@@ -33517,7 +33531,7 @@
       <c r="BI39"/>
     </row>
     <row r="40" spans="1:61" ht="15.75">
-      <c r="A40" s="111" t="s">
+      <c r="A40" s="56" t="s">
         <v>753</v>
       </c>
       <c r="B40">
@@ -33592,7 +33606,7 @@
       <c r="BI40"/>
     </row>
     <row r="41" spans="1:61" ht="15.75">
-      <c r="A41" s="111" t="s">
+      <c r="A41" s="56" t="s">
         <v>755</v>
       </c>
       <c r="B41">
@@ -33667,7 +33681,7 @@
       <c r="BI41"/>
     </row>
     <row r="42" spans="1:61" ht="15.75">
-      <c r="A42" s="111" t="s">
+      <c r="A42" s="56" t="s">
         <v>757</v>
       </c>
       <c r="B42">
@@ -33745,7 +33759,7 @@
       <c r="BI42"/>
     </row>
     <row r="43" spans="1:61" ht="15.75">
-      <c r="A43" s="111" t="s">
+      <c r="A43" s="56" t="s">
         <v>759</v>
       </c>
       <c r="B43">
@@ -33823,7 +33837,7 @@
       <c r="BI43"/>
     </row>
     <row r="44" spans="1:61" ht="15.75">
-      <c r="A44" s="111" t="s">
+      <c r="A44" s="56" t="s">
         <v>761</v>
       </c>
       <c r="B44" t="s">
@@ -41968,30 +41982,30 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="21">
-      <c r="A33" s="108" t="s">
+      <c r="A33" s="111" t="s">
         <v>1050</v>
       </c>
-      <c r="B33" s="109"/>
-      <c r="C33" s="109"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="109"/>
-      <c r="H33" s="109"/>
-      <c r="I33" s="109"/>
+      <c r="B33" s="112"/>
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="112"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="112"/>
     </row>
     <row r="35" spans="1:9" ht="15.75">
-      <c r="A35" s="110" t="s">
+      <c r="A35" s="113" t="s">
         <v>1051</v>
       </c>
-      <c r="B35" s="109"/>
-      <c r="C35" s="109"/>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="109"/>
-      <c r="G35" s="109"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="109"/>
+      <c r="B35" s="112"/>
+      <c r="C35" s="112"/>
+      <c r="D35" s="112"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="112"/>
+      <c r="H35" s="112"/>
+      <c r="I35" s="112"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="24" t="s">
@@ -42444,11 +42458,11 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75">
-      <c r="A52" s="110" t="s">
+      <c r="A52" s="113" t="s">
         <v>1074</v>
       </c>
-      <c r="B52" s="109"/>
-      <c r="C52" s="109"/>
+      <c r="B52" s="112"/>
+      <c r="C52" s="112"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="24" t="s">
@@ -42546,11 +42560,11 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.75">
-      <c r="A63" s="110" t="s">
+      <c r="A63" s="113" t="s">
         <v>1084</v>
       </c>
-      <c r="B63" s="109"/>
-      <c r="C63" s="109"/>
+      <c r="B63" s="112"/>
+      <c r="C63" s="112"/>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="24" t="s">

--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehrnia\Desktop\Job\AtlasCopco\Business Analysis Project and Stakeholder Management\Excel_PLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2B96CE-AD0B-4DBA-9C1E-623B6B9B74B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD5C59E-FDA5-4513-9571-AEC4DFB9E4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1727,9 +1727,6 @@
     <t>Quarterly audit</t>
   </si>
   <si>
-    <t>RISK MANAGEMENT + NPI ATTRITION — 14 candidate stations to 11 operating assets</t>
-  </si>
-  <si>
     <t>Station</t>
   </si>
   <si>
@@ -2375,9 +2372,6 @@
     <t>Governance rule</t>
   </si>
   <si>
-    <t>EXECUTIVE DASHBOARD — Reverse Pump Energy Recovery PLM Portfolio</t>
-  </si>
-  <si>
     <t>Target / Band</t>
   </si>
   <si>
@@ -2705,9 +2699,6 @@
     <t>Refresh Teamcenter export</t>
   </si>
   <si>
-    <t>EXECUTIVE REPORT — Full Lifecycle Delivery for Underground Reverse Pump Energy Recovery</t>
-  </si>
-  <si>
     <t>Section</t>
   </si>
   <si>
@@ -3443,10 +3434,19 @@
     <t>Related Stakeholders</t>
   </si>
   <si>
-    <t>COST BENEFIT ANALYSIS: CAPEX, OPEX, Payback and IRR Controls</t>
-  </si>
-  <si>
     <t xml:space="preserve">Project: Multi-Site Pressure Reducing &amp; Power Generation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXECUTIVE REPORT — Full Lifecycle Delivery for Multi-Site Pressure Reducing &amp; Power Generation </t>
+  </si>
+  <si>
+    <t>RISK MANAGEMENT + NPI ATTRITION - 14 candidate stations to 11 operating assets</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DASHBOARD: Multi-Site Pressure Reducing &amp; Power Generation PLM Portfolio</t>
+  </si>
+  <si>
+    <t>COST-BENEFIT ANALYSIS: CAPEX, OPEX, ROI &amp; IRR</t>
   </si>
 </sst>
 </file>
@@ -3460,7 +3460,7 @@
     <numFmt numFmtId="166" formatCode="\$#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3551,13 +3551,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3702,8 +3695,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3799,6 +3807,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4003,7 +4017,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -4037,67 +4051,65 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4105,7 +4117,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4118,113 +4130,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4261,6 +4171,33 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4279,13 +4216,97 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -8220,7 +8241,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="37.5">
       <c r="A1" s="13" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -11951,8 +11972,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18.75">
-      <c r="A1" s="18" t="s">
-        <v>1046</v>
+      <c r="A1" s="17" t="s">
+        <v>1043</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -15873,12 +15894,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18.75">
-      <c r="A1" s="23" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B1" s="52"/>
+      <c r="A1" s="21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B1" s="50"/>
       <c r="C1" s="13"/>
-      <c r="D1" s="22"/>
+      <c r="D1" s="20"/>
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
@@ -20731,22 +20752,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="5" customFormat="1" ht="42">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="47" t="s">
         <v>365</v>
       </c>
-      <c r="B1" s="50">
+      <c r="B1" s="48">
         <v>41043</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="49" t="s">
         <v>281</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="49" t="s">
         <v>370</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="49" t="s">
         <v>371</v>
       </c>
       <c r="G1" s="11" t="s">
@@ -24623,19 +24644,19 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="37.5">
-      <c r="A1" s="23" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+    <row r="1" spans="1:26" ht="46.5">
+      <c r="A1" s="115" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
@@ -24977,7 +24998,7 @@
         <v>468</v>
       </c>
       <c r="C9" s="12">
-        <v>42766</v>
+        <v>42400</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>469</v>
@@ -25025,7 +25046,7 @@
         <v>476</v>
       </c>
       <c r="C10" s="12">
-        <v>43546</v>
+        <v>42816</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>477</v>
@@ -28470,74 +28491,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="A1" s="113" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D3" t="s">
         <v>552</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>553</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>554</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>555</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>556</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>557</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>558</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>559</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>560</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>561</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>562</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>563</v>
-      </c>
-      <c r="O3" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D4" s="10">
         <v>42510</v>
       </c>
       <c r="E4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F4">
         <v>0.26</v>
@@ -28553,7 +28579,7 @@
         <v>1.24</v>
       </c>
       <c r="J4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K4" t="s">
         <v>443</v>
@@ -28568,24 +28594,24 @@
         <v>13</v>
       </c>
       <c r="O4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D5" s="10">
         <v>42531</v>
       </c>
       <c r="E5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F5">
         <v>0.24</v>
@@ -28601,7 +28627,7 @@
         <v>1.18</v>
       </c>
       <c r="J5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K5" t="s">
         <v>443</v>
@@ -28616,24 +28642,24 @@
         <v>13</v>
       </c>
       <c r="O5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D6" s="10">
         <v>42559</v>
       </c>
       <c r="E6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F6">
         <v>0.25</v>
@@ -28649,7 +28675,7 @@
         <v>1.25</v>
       </c>
       <c r="J6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K6" t="s">
         <v>443</v>
@@ -28664,24 +28690,24 @@
         <v>13</v>
       </c>
       <c r="O6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D7" s="10">
         <v>42594</v>
       </c>
       <c r="E7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F7">
         <v>0.28000000000000003</v>
@@ -28697,7 +28723,7 @@
         <v>1.3</v>
       </c>
       <c r="J7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K7" t="s">
         <v>443</v>
@@ -28712,24 +28738,24 @@
         <v>12</v>
       </c>
       <c r="O7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D8" s="10">
         <v>42629</v>
       </c>
       <c r="E8" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F8">
         <v>0.23</v>
@@ -28745,7 +28771,7 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="J8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K8" t="s">
         <v>443</v>
@@ -28760,24 +28786,24 @@
         <v>12</v>
       </c>
       <c r="O8" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D9" s="10">
         <v>42657</v>
       </c>
       <c r="E9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F9">
         <v>0.25</v>
@@ -28793,7 +28819,7 @@
         <v>1.22</v>
       </c>
       <c r="J9" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K9" t="s">
         <v>443</v>
@@ -28808,24 +28834,24 @@
         <v>13</v>
       </c>
       <c r="O9" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -28840,10 +28866,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
+        <v>587</v>
+      </c>
+      <c r="K10" t="s">
         <v>588</v>
-      </c>
-      <c r="K10" t="s">
-        <v>589</v>
       </c>
       <c r="L10" t="s">
         <v>29</v>
@@ -28855,24 +28881,24 @@
         <v>380</v>
       </c>
       <c r="O10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B11" t="s">
         <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D11" s="10">
         <v>42692</v>
       </c>
       <c r="E11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F11">
         <v>0.27</v>
@@ -28888,7 +28914,7 @@
         <v>1.29</v>
       </c>
       <c r="J11" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K11" t="s">
         <v>443</v>
@@ -28903,7 +28929,7 @@
         <v>12</v>
       </c>
       <c r="O11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -28914,13 +28940,13 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D12" s="10">
         <v>42755</v>
       </c>
       <c r="E12" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F12">
         <v>0.25</v>
@@ -28935,7 +28961,7 @@
         <v>1.08</v>
       </c>
       <c r="J12" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="K12" t="s">
         <v>443</v>
@@ -28944,30 +28970,30 @@
         <v>443</v>
       </c>
       <c r="M12" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N12" t="s">
         <v>380</v>
       </c>
       <c r="O12" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B13" t="s">
         <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D13" s="10">
         <v>42783</v>
       </c>
       <c r="E13" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F13">
         <v>0.24</v>
@@ -28983,7 +29009,7 @@
         <v>1.21</v>
       </c>
       <c r="J13" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K13" t="s">
         <v>443</v>
@@ -28998,24 +29024,24 @@
         <v>13</v>
       </c>
       <c r="O13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B14" t="s">
         <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D14" s="10">
         <v>42811</v>
       </c>
       <c r="E14" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F14">
         <v>0.26</v>
@@ -29031,7 +29057,7 @@
         <v>1.26</v>
       </c>
       <c r="J14" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K14" t="s">
         <v>443</v>
@@ -29046,24 +29072,24 @@
         <v>12</v>
       </c>
       <c r="O14" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B15" t="s">
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -29078,10 +29104,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K15" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L15" t="s">
         <v>29</v>
@@ -29093,24 +29119,24 @@
         <v>380</v>
       </c>
       <c r="O15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B16" t="s">
         <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D16" s="10">
         <v>42846</v>
       </c>
       <c r="E16" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F16">
         <v>0.24</v>
@@ -29126,7 +29152,7 @@
         <v>1.2</v>
       </c>
       <c r="J16" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K16" t="s">
         <v>443</v>
@@ -29141,24 +29167,24 @@
         <v>13</v>
       </c>
       <c r="O16" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B17" t="s">
         <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D17" s="10">
         <v>42874</v>
       </c>
       <c r="E17" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F17">
         <v>0.23</v>
@@ -29174,7 +29200,7 @@
         <v>1.19</v>
       </c>
       <c r="J17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K17" t="s">
         <v>443</v>
@@ -29189,7 +29215,7 @@
         <v>13</v>
       </c>
       <c r="O17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -29197,34 +29223,34 @@
         <v>35</v>
       </c>
       <c r="B20" t="s">
+        <v>611</v>
+      </c>
+      <c r="C20" t="s">
         <v>612</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>613</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>614</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>615</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>616</v>
-      </c>
-      <c r="G20" t="s">
-        <v>617</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
       </c>
       <c r="J20" t="s">
+        <v>661</v>
+      </c>
+      <c r="K20" t="s">
         <v>662</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>663</v>
-      </c>
-      <c r="L20" t="s">
-        <v>664</v>
       </c>
       <c r="M20" t="s">
         <v>8</v>
@@ -29235,10 +29261,10 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
+        <v>617</v>
+      </c>
+      <c r="C21" t="s">
         <v>618</v>
-      </c>
-      <c r="C21" t="s">
-        <v>619</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
@@ -29250,19 +29276,19 @@
         <v>11</v>
       </c>
       <c r="G21" t="s">
+        <v>619</v>
+      </c>
+      <c r="H21" t="s">
         <v>620</v>
       </c>
-      <c r="H21" t="s">
-        <v>621</v>
-      </c>
       <c r="J21" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K21">
         <v>14</v>
       </c>
       <c r="L21" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="M21" t="s">
         <v>267</v>
@@ -29276,7 +29302,7 @@
         <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
@@ -29288,19 +29314,19 @@
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H22" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J22" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K22">
         <v>2</v>
       </c>
       <c r="L22" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="M22" t="s">
         <v>267</v>
@@ -29314,7 +29340,7 @@
         <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -29326,20 +29352,20 @@
         <v>12</v>
       </c>
       <c r="G23" t="s">
+        <v>624</v>
+      </c>
+      <c r="H23" t="s">
         <v>625</v>
       </c>
-      <c r="H23" t="s">
-        <v>626</v>
-      </c>
       <c r="J23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K23">
         <f>K21-K22</f>
         <v>12</v>
       </c>
       <c r="L23" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="M23" t="s">
         <v>267</v>
@@ -29353,7 +29379,7 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
@@ -29365,13 +29391,13 @@
         <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H24" t="s">
         <v>380</v>
       </c>
       <c r="J24" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -29391,7 +29417,7 @@
         <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D25" t="s">
         <v>13</v>
@@ -29403,20 +29429,20 @@
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J25" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K25">
         <f>COUNTIF(E4:E17,"Active")</f>
         <v>11</v>
       </c>
       <c r="L25" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M25" t="s">
         <v>19</v>
@@ -29430,7 +29456,7 @@
         <v>285</v>
       </c>
       <c r="C26" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
@@ -29442,19 +29468,19 @@
         <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H26" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J26" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="K26">
         <v>11</v>
       </c>
       <c r="L26" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="M26" t="s">
         <v>19</v>
@@ -29468,7 +29494,7 @@
         <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
@@ -29480,20 +29506,20 @@
         <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H27" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J27" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="K27">
         <f>K25-K26</f>
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="M27" t="s">
         <v>19</v>
@@ -29507,7 +29533,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
@@ -29519,10 +29545,10 @@
         <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H28" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -29533,7 +29559,7 @@
         <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -29545,10 +29571,10 @@
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H29" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -29559,7 +29585,7 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
@@ -29571,7 +29597,7 @@
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H30" t="s">
         <v>380</v>
@@ -29579,13 +29605,13 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B31" t="s">
         <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
@@ -29597,21 +29623,21 @@
         <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H31" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
+        <v>643</v>
+      </c>
+      <c r="B32" t="s">
         <v>644</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>645</v>
-      </c>
-      <c r="C32" t="s">
-        <v>646</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -29623,7 +29649,7 @@
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H32" t="s">
         <v>380</v>
@@ -29631,13 +29657,13 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B33" t="s">
         <v>530</v>
       </c>
       <c r="C33" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D33" t="s">
         <v>13</v>
@@ -29649,21 +29675,21 @@
         <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H33" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
+        <v>650</v>
+      </c>
+      <c r="B34" t="s">
         <v>651</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>652</v>
-      </c>
-      <c r="C34" t="s">
-        <v>653</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
@@ -29675,21 +29701,21 @@
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H34" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
+        <v>654</v>
+      </c>
+      <c r="B35" t="s">
         <v>655</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>656</v>
-      </c>
-      <c r="C35" t="s">
-        <v>657</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -29701,21 +29727,21 @@
         <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H35" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
@@ -29727,844 +29753,872 @@
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H36" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="38"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
-      <c r="J40" s="38"/>
-      <c r="K40" s="38"/>
-      <c r="L40" s="38"/>
-      <c r="M40" s="38"/>
-      <c r="N40" s="38"/>
-      <c r="O40" s="38"/>
-      <c r="P40" s="38"/>
-      <c r="Q40" s="38"/>
-      <c r="R40" s="38"/>
+      <c r="A40" s="36"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="59" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B41" s="59"/>
-      <c r="C41" s="59" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D41" s="59"/>
-      <c r="E41" s="39" t="s">
+      <c r="A41" s="87" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B41" s="87"/>
+      <c r="C41" s="87" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D41" s="87"/>
+      <c r="E41" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="38"/>
-      <c r="M41" s="38"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="41" t="s">
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="39" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
+    </row>
+    <row r="42" spans="1:18" ht="18.75">
+      <c r="A42" s="88"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="36"/>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="43" t="s">
+        <v>1088</v>
+      </c>
+      <c r="P42" s="44"/>
+      <c r="Q42" s="44"/>
+      <c r="R42" s="45"/>
+    </row>
+    <row r="43" spans="1:18" ht="18.75">
+      <c r="A43" s="36"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="36"/>
+      <c r="K43" s="36"/>
+      <c r="L43" s="36"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="36"/>
+      <c r="O43" s="46" t="s">
+        <v>1089</v>
+      </c>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
+    </row>
+    <row r="44" spans="1:18" ht="18.75">
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="46" t="s">
         <v>1090</v>
       </c>
-      <c r="P41" s="42"/>
-      <c r="Q41" s="42"/>
-      <c r="R41" s="43"/>
-    </row>
-    <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="60"/>
-      <c r="B42" s="60"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="38"/>
-      <c r="K42" s="38"/>
-      <c r="L42" s="38"/>
-      <c r="M42" s="38"/>
-      <c r="N42" s="38"/>
-      <c r="O42" s="45" t="s">
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
+    </row>
+    <row r="45" spans="1:18" ht="18.75">
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="36"/>
+      <c r="M45" s="36"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="46" t="s">
         <v>1091</v>
       </c>
-      <c r="P42" s="46"/>
-      <c r="Q42" s="46"/>
-      <c r="R42" s="47"/>
-    </row>
-    <row r="43" spans="1:18" ht="18.75">
-      <c r="A43" s="38"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="38"/>
-      <c r="K43" s="38"/>
-      <c r="L43" s="38"/>
-      <c r="M43" s="38"/>
-      <c r="N43" s="38"/>
-      <c r="O43" s="48" t="s">
+      <c r="P45" s="40"/>
+      <c r="Q45" s="40"/>
+      <c r="R45" s="41"/>
+    </row>
+    <row r="46" spans="1:18" ht="18.75">
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="36"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="43" t="s">
         <v>1092</v>
       </c>
-      <c r="P43" s="42"/>
-      <c r="Q43" s="42"/>
-      <c r="R43" s="43"/>
-    </row>
-    <row r="44" spans="1:18" ht="18.75">
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="38"/>
-      <c r="L44" s="38"/>
-      <c r="M44" s="38"/>
-      <c r="N44" s="38"/>
-      <c r="O44" s="48" t="s">
+      <c r="P46" s="44"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="45"/>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="89" t="s">
         <v>1093</v>
       </c>
-      <c r="P44" s="42"/>
-      <c r="Q44" s="42"/>
-      <c r="R44" s="43"/>
-    </row>
-    <row r="45" spans="1:18" ht="18.75">
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="38"/>
-      <c r="L45" s="38"/>
-      <c r="M45" s="38"/>
-      <c r="N45" s="38"/>
-      <c r="O45" s="48" t="s">
+      <c r="B47" s="90"/>
+      <c r="C47" s="95" t="s">
         <v>1094</v>
       </c>
-      <c r="P45" s="42"/>
-      <c r="Q45" s="42"/>
-      <c r="R45" s="43"/>
-    </row>
-    <row r="46" spans="1:18" ht="18.75">
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="38"/>
-      <c r="L46" s="38"/>
-      <c r="M46" s="38"/>
-      <c r="N46" s="40"/>
-      <c r="O46" s="45" t="s">
+      <c r="D47" s="96"/>
+      <c r="E47" s="96"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="96"/>
+      <c r="H47" s="96"/>
+      <c r="I47" s="96"/>
+      <c r="J47" s="96"/>
+      <c r="K47" s="96"/>
+      <c r="L47" s="97"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="91"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="98"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="99"/>
+      <c r="I48" s="99"/>
+      <c r="J48" s="99"/>
+      <c r="K48" s="99"/>
+      <c r="L48" s="100"/>
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="39" t="s">
         <v>1095</v>
       </c>
-      <c r="P46" s="46"/>
-      <c r="Q46" s="46"/>
-      <c r="R46" s="47"/>
-    </row>
-    <row r="47" spans="1:18">
-      <c r="A47" s="61" t="s">
+      <c r="P48" s="40"/>
+      <c r="Q48" s="40"/>
+      <c r="R48" s="41"/>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="91"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="101" t="s">
         <v>1096</v>
       </c>
-      <c r="B47" s="62"/>
-      <c r="C47" s="67" t="s">
+      <c r="D49" s="102"/>
+      <c r="E49" s="101" t="s">
         <v>1097</v>
       </c>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="68"/>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="69"/>
-      <c r="M47" s="38"/>
-      <c r="N47" s="38"/>
-    </row>
-    <row r="48" spans="1:18">
-      <c r="A48" s="63"/>
-      <c r="B48" s="64"/>
-      <c r="C48" s="70"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="71"/>
-      <c r="F48" s="71"/>
-      <c r="G48" s="71"/>
-      <c r="H48" s="71"/>
-      <c r="I48" s="71"/>
-      <c r="J48" s="71"/>
-      <c r="K48" s="71"/>
-      <c r="L48" s="72"/>
-      <c r="M48" s="38"/>
-      <c r="N48" s="38"/>
-      <c r="O48" s="41" t="s">
+      <c r="F49" s="102"/>
+      <c r="G49" s="101" t="s">
         <v>1098</v>
       </c>
-      <c r="P48" s="42"/>
-      <c r="Q48" s="42"/>
-      <c r="R48" s="43"/>
-    </row>
-    <row r="49" spans="1:18">
-      <c r="A49" s="63"/>
-      <c r="B49" s="64"/>
-      <c r="C49" s="73" t="s">
+      <c r="H49" s="102"/>
+      <c r="I49" s="105" t="s">
         <v>1099</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="73" t="s">
+      <c r="J49" s="106"/>
+      <c r="K49" s="101" t="s">
         <v>1100</v>
       </c>
-      <c r="F49" s="74"/>
-      <c r="G49" s="73" t="s">
+      <c r="L49" s="102"/>
+      <c r="M49" s="36"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="46" t="s">
         <v>1101</v>
       </c>
-      <c r="H49" s="74"/>
-      <c r="I49" s="77" t="s">
+      <c r="P49" s="40"/>
+      <c r="Q49" s="40"/>
+      <c r="R49" s="41"/>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" s="93"/>
+      <c r="B50" s="94"/>
+      <c r="C50" s="103"/>
+      <c r="D50" s="104"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="107"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="103"/>
+      <c r="L50" s="104"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="36"/>
+      <c r="O50" s="46" t="s">
         <v>1102</v>
       </c>
-      <c r="J49" s="78"/>
-      <c r="K49" s="73" t="s">
+      <c r="P50" s="40"/>
+      <c r="Q50" s="40"/>
+      <c r="R50" s="41"/>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" s="84" t="s">
         <v>1103</v>
       </c>
-      <c r="L49" s="74"/>
-      <c r="M49" s="38"/>
-      <c r="N49" s="38"/>
-      <c r="O49" s="48" t="s">
+      <c r="B51" s="75" t="s">
         <v>1104</v>
       </c>
-      <c r="P49" s="42"/>
-      <c r="Q49" s="42"/>
-      <c r="R49" s="43"/>
-    </row>
-    <row r="50" spans="1:18">
-      <c r="A50" s="65"/>
-      <c r="B50" s="66"/>
-      <c r="C50" s="75"/>
-      <c r="D50" s="76"/>
-      <c r="E50" s="75"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="75"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="79"/>
-      <c r="J50" s="80"/>
-      <c r="K50" s="75"/>
-      <c r="L50" s="76"/>
-      <c r="M50" s="38"/>
-      <c r="N50" s="38"/>
-      <c r="O50" s="48" t="s">
+      <c r="C51" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="70"/>
+      <c r="E51" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="58"/>
+      <c r="G51" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="64"/>
+      <c r="I51" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" s="64"/>
+      <c r="K51" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" s="64"/>
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="46" t="s">
         <v>1105</v>
       </c>
-      <c r="P50" s="42"/>
-      <c r="Q50" s="42"/>
-      <c r="R50" s="43"/>
-    </row>
-    <row r="51" spans="1:18">
-      <c r="A51" s="81" t="s">
+      <c r="P51" s="40"/>
+      <c r="Q51" s="40"/>
+      <c r="R51" s="41"/>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" s="85"/>
+      <c r="B52" s="76"/>
+      <c r="C52" s="71"/>
+      <c r="D52" s="72"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="60"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="66"/>
+      <c r="I52" s="65"/>
+      <c r="J52" s="66"/>
+      <c r="K52" s="65"/>
+      <c r="L52" s="66"/>
+      <c r="M52" s="36"/>
+      <c r="N52" s="36"/>
+      <c r="O52" s="46" t="s">
         <v>1106</v>
       </c>
-      <c r="B51" s="84" t="s">
+      <c r="P52" s="40"/>
+      <c r="Q52" s="40"/>
+      <c r="R52" s="41"/>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" s="85"/>
+      <c r="B53" s="76"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="60"/>
+      <c r="G53" s="65"/>
+      <c r="H53" s="66"/>
+      <c r="I53" s="65"/>
+      <c r="J53" s="66"/>
+      <c r="K53" s="65"/>
+      <c r="L53" s="66"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="43" t="s">
         <v>1107</v>
       </c>
-      <c r="C51" s="87" t="s">
+      <c r="P53" s="44"/>
+      <c r="Q53" s="44"/>
+      <c r="R53" s="45"/>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" s="85"/>
+      <c r="B54" s="76"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="60"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="65"/>
+      <c r="J54" s="66"/>
+      <c r="K54" s="65"/>
+      <c r="L54" s="66"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" s="85"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="62"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="67"/>
+      <c r="J55" s="68"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="68"/>
+      <c r="M55" s="36"/>
+      <c r="N55" s="36"/>
+      <c r="O55" s="39" t="s">
+        <v>1108</v>
+      </c>
+      <c r="P55" s="40"/>
+      <c r="Q55" s="40"/>
+      <c r="R55" s="41"/>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" s="85"/>
+      <c r="B56" s="75" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C56" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="88"/>
-      <c r="E51" s="93" t="s">
+      <c r="D56" s="70"/>
+      <c r="E56" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="94"/>
-      <c r="G51" s="99" t="s">
+      <c r="F56" s="58"/>
+      <c r="G56" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="58"/>
+      <c r="I56" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="100"/>
-      <c r="I51" s="99" t="s">
+      <c r="J56" s="64"/>
+      <c r="K56" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="100"/>
-      <c r="K51" s="99" t="s">
+      <c r="L56" s="64"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="46" t="s">
+        <v>1110</v>
+      </c>
+      <c r="P56" s="40"/>
+      <c r="Q56" s="40"/>
+      <c r="R56" s="41"/>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" s="85"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="60"/>
+      <c r="I57" s="65"/>
+      <c r="J57" s="66"/>
+      <c r="K57" s="65"/>
+      <c r="L57" s="66"/>
+      <c r="M57" s="36"/>
+      <c r="N57" s="36"/>
+      <c r="O57" s="46" t="s">
+        <v>1111</v>
+      </c>
+      <c r="P57" s="40"/>
+      <c r="Q57" s="40"/>
+      <c r="R57" s="41"/>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" s="85"/>
+      <c r="B58" s="76"/>
+      <c r="C58" s="71"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="60"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="65"/>
+      <c r="J58" s="66"/>
+      <c r="K58" s="65"/>
+      <c r="L58" s="66"/>
+      <c r="M58" s="36"/>
+      <c r="N58" s="36"/>
+      <c r="O58" s="46" t="s">
+        <v>1112</v>
+      </c>
+      <c r="P58" s="40"/>
+      <c r="Q58" s="40"/>
+      <c r="R58" s="41"/>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" s="85"/>
+      <c r="B59" s="76"/>
+      <c r="C59" s="71"/>
+      <c r="D59" s="72"/>
+      <c r="E59" s="59"/>
+      <c r="F59" s="60"/>
+      <c r="G59" s="59"/>
+      <c r="H59" s="60"/>
+      <c r="I59" s="65"/>
+      <c r="J59" s="66"/>
+      <c r="K59" s="65"/>
+      <c r="L59" s="66"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36"/>
+      <c r="O59" s="43" t="s">
+        <v>1113</v>
+      </c>
+      <c r="P59" s="44"/>
+      <c r="Q59" s="44"/>
+      <c r="R59" s="45"/>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" s="85"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="62"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="62"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="68"/>
+      <c r="K60" s="67"/>
+      <c r="L60" s="68"/>
+      <c r="M60" s="36"/>
+      <c r="N60" s="36"/>
+      <c r="O60" s="36"/>
+      <c r="P60" s="36"/>
+      <c r="Q60" s="36"/>
+      <c r="R60" s="36"/>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" s="85"/>
+      <c r="B61" s="75" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C61" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="79"/>
+      <c r="E61" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="70"/>
+      <c r="G61" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="58"/>
+      <c r="I61" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="J61" s="58"/>
+      <c r="K61" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="100"/>
-      <c r="M51" s="38"/>
-      <c r="N51" s="38"/>
-      <c r="O51" s="48" t="s">
-        <v>1108</v>
-      </c>
-      <c r="P51" s="42"/>
-      <c r="Q51" s="42"/>
-      <c r="R51" s="43"/>
-    </row>
-    <row r="52" spans="1:18">
-      <c r="A52" s="82"/>
-      <c r="B52" s="85"/>
-      <c r="C52" s="89"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="95"/>
-      <c r="F52" s="96"/>
-      <c r="G52" s="101"/>
-      <c r="H52" s="102"/>
-      <c r="I52" s="101"/>
-      <c r="J52" s="102"/>
-      <c r="K52" s="101"/>
-      <c r="L52" s="102"/>
-      <c r="M52" s="38"/>
-      <c r="N52" s="38"/>
-      <c r="O52" s="48" t="s">
-        <v>1109</v>
-      </c>
-      <c r="P52" s="42"/>
-      <c r="Q52" s="42"/>
-      <c r="R52" s="43"/>
-    </row>
-    <row r="53" spans="1:18">
-      <c r="A53" s="82"/>
-      <c r="B53" s="85"/>
-      <c r="C53" s="89"/>
-      <c r="D53" s="90"/>
-      <c r="E53" s="95"/>
-      <c r="F53" s="96"/>
-      <c r="G53" s="101"/>
-      <c r="H53" s="102"/>
-      <c r="I53" s="101"/>
-      <c r="J53" s="102"/>
-      <c r="K53" s="101"/>
-      <c r="L53" s="102"/>
-      <c r="M53" s="38"/>
-      <c r="N53" s="38"/>
-      <c r="O53" s="45" t="s">
-        <v>1110</v>
-      </c>
-      <c r="P53" s="46"/>
-      <c r="Q53" s="46"/>
-      <c r="R53" s="47"/>
-    </row>
-    <row r="54" spans="1:18">
-      <c r="A54" s="82"/>
-      <c r="B54" s="85"/>
-      <c r="C54" s="89"/>
-      <c r="D54" s="90"/>
-      <c r="E54" s="95"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="101"/>
-      <c r="H54" s="102"/>
-      <c r="I54" s="101"/>
-      <c r="J54" s="102"/>
-      <c r="K54" s="101"/>
-      <c r="L54" s="102"/>
-      <c r="M54" s="38"/>
-      <c r="N54" s="38"/>
-    </row>
-    <row r="55" spans="1:18">
-      <c r="A55" s="82"/>
-      <c r="B55" s="86"/>
-      <c r="C55" s="91"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="97"/>
-      <c r="F55" s="98"/>
-      <c r="G55" s="103"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="103"/>
-      <c r="J55" s="104"/>
-      <c r="K55" s="103"/>
-      <c r="L55" s="104"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="41" t="s">
-        <v>1111</v>
-      </c>
-      <c r="P55" s="42"/>
-      <c r="Q55" s="42"/>
-      <c r="R55" s="43"/>
-    </row>
-    <row r="56" spans="1:18">
-      <c r="A56" s="82"/>
-      <c r="B56" s="84" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C56" s="87" t="s">
+      <c r="L61" s="64"/>
+      <c r="M61" s="36"/>
+      <c r="N61" s="36"/>
+      <c r="O61" s="36"/>
+      <c r="P61" s="36"/>
+      <c r="Q61" s="36"/>
+      <c r="R61" s="36"/>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62" s="85"/>
+      <c r="B62" s="76"/>
+      <c r="C62" s="80"/>
+      <c r="D62" s="81"/>
+      <c r="E62" s="71"/>
+      <c r="F62" s="72"/>
+      <c r="G62" s="59"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="59"/>
+      <c r="J62" s="60"/>
+      <c r="K62" s="65"/>
+      <c r="L62" s="66"/>
+      <c r="M62" s="36"/>
+      <c r="N62" s="36"/>
+      <c r="O62" s="36"/>
+      <c r="P62" s="36"/>
+      <c r="Q62" s="36"/>
+      <c r="R62" s="36"/>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" s="85"/>
+      <c r="B63" s="76"/>
+      <c r="C63" s="80"/>
+      <c r="D63" s="81"/>
+      <c r="E63" s="71"/>
+      <c r="F63" s="72"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="59"/>
+      <c r="J63" s="60"/>
+      <c r="K63" s="65"/>
+      <c r="L63" s="66"/>
+      <c r="M63" s="36"/>
+      <c r="N63" s="36"/>
+      <c r="O63" s="36"/>
+      <c r="P63" s="36"/>
+      <c r="Q63" s="36"/>
+      <c r="R63" s="36"/>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" s="85"/>
+      <c r="B64" s="76"/>
+      <c r="C64" s="80"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="71"/>
+      <c r="F64" s="72"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="60"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="60"/>
+      <c r="K64" s="65"/>
+      <c r="L64" s="66"/>
+      <c r="M64" s="36"/>
+      <c r="N64" s="36"/>
+      <c r="O64" s="36"/>
+      <c r="P64" s="36"/>
+      <c r="Q64" s="36"/>
+      <c r="R64" s="36"/>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" s="85"/>
+      <c r="B65" s="77"/>
+      <c r="C65" s="82"/>
+      <c r="D65" s="83"/>
+      <c r="E65" s="73"/>
+      <c r="F65" s="74"/>
+      <c r="G65" s="61"/>
+      <c r="H65" s="62"/>
+      <c r="I65" s="61"/>
+      <c r="J65" s="62"/>
+      <c r="K65" s="67"/>
+      <c r="L65" s="68"/>
+      <c r="M65" s="36"/>
+      <c r="N65" s="36"/>
+      <c r="O65" s="36"/>
+      <c r="P65" s="36"/>
+      <c r="Q65" s="36"/>
+      <c r="R65" s="36"/>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" s="85"/>
+      <c r="B66" s="75" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C66" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="79"/>
+      <c r="E66" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="79"/>
+      <c r="G66" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="88"/>
-      <c r="E56" s="93" t="s">
+      <c r="H66" s="70"/>
+      <c r="I66" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="J66" s="70"/>
+      <c r="K66" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="94"/>
-      <c r="G56" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="H56" s="94"/>
-      <c r="I56" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="J56" s="100"/>
-      <c r="K56" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="L56" s="100"/>
-      <c r="M56" s="38"/>
-      <c r="N56" s="38"/>
-      <c r="O56" s="48" t="s">
-        <v>1113</v>
-      </c>
-      <c r="P56" s="42"/>
-      <c r="Q56" s="42"/>
-      <c r="R56" s="43"/>
-    </row>
-    <row r="57" spans="1:18">
-      <c r="A57" s="82"/>
-      <c r="B57" s="85"/>
-      <c r="C57" s="89"/>
-      <c r="D57" s="90"/>
-      <c r="E57" s="95"/>
-      <c r="F57" s="96"/>
-      <c r="G57" s="95"/>
-      <c r="H57" s="96"/>
-      <c r="I57" s="101"/>
-      <c r="J57" s="102"/>
-      <c r="K57" s="101"/>
-      <c r="L57" s="102"/>
-      <c r="M57" s="38"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="48" t="s">
-        <v>1114</v>
-      </c>
-      <c r="P57" s="42"/>
-      <c r="Q57" s="42"/>
-      <c r="R57" s="43"/>
-    </row>
-    <row r="58" spans="1:18">
-      <c r="A58" s="82"/>
-      <c r="B58" s="85"/>
-      <c r="C58" s="89"/>
-      <c r="D58" s="90"/>
-      <c r="E58" s="95"/>
-      <c r="F58" s="96"/>
-      <c r="G58" s="95"/>
-      <c r="H58" s="96"/>
-      <c r="I58" s="101"/>
-      <c r="J58" s="102"/>
-      <c r="K58" s="101"/>
-      <c r="L58" s="102"/>
-      <c r="M58" s="38"/>
-      <c r="N58" s="38"/>
-      <c r="O58" s="48" t="s">
-        <v>1115</v>
-      </c>
-      <c r="P58" s="42"/>
-      <c r="Q58" s="42"/>
-      <c r="R58" s="43"/>
-    </row>
-    <row r="59" spans="1:18">
-      <c r="A59" s="82"/>
-      <c r="B59" s="85"/>
-      <c r="C59" s="89"/>
-      <c r="D59" s="90"/>
-      <c r="E59" s="95"/>
-      <c r="F59" s="96"/>
-      <c r="G59" s="95"/>
-      <c r="H59" s="96"/>
-      <c r="I59" s="101"/>
-      <c r="J59" s="102"/>
-      <c r="K59" s="101"/>
-      <c r="L59" s="102"/>
-      <c r="M59" s="38"/>
-      <c r="N59" s="38"/>
-      <c r="O59" s="45" t="s">
+      <c r="L66" s="58"/>
+      <c r="M66" s="36"/>
+      <c r="N66" s="36"/>
+      <c r="O66" s="36"/>
+      <c r="P66" s="36"/>
+      <c r="Q66" s="36"/>
+      <c r="R66" s="36"/>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" s="85"/>
+      <c r="B67" s="76"/>
+      <c r="C67" s="80"/>
+      <c r="D67" s="81"/>
+      <c r="E67" s="80"/>
+      <c r="F67" s="81"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="72"/>
+      <c r="I67" s="71"/>
+      <c r="J67" s="72"/>
+      <c r="K67" s="59"/>
+      <c r="L67" s="60"/>
+      <c r="M67" s="36"/>
+      <c r="N67" s="36"/>
+      <c r="O67" s="36"/>
+      <c r="P67" s="36"/>
+      <c r="Q67" s="36"/>
+      <c r="R67" s="36"/>
+    </row>
+    <row r="68" spans="1:18">
+      <c r="A68" s="85"/>
+      <c r="B68" s="76"/>
+      <c r="C68" s="80"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="80"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="71"/>
+      <c r="H68" s="72"/>
+      <c r="I68" s="71"/>
+      <c r="J68" s="72"/>
+      <c r="K68" s="59"/>
+      <c r="L68" s="60"/>
+      <c r="M68" s="36"/>
+      <c r="N68" s="36"/>
+      <c r="O68" s="36"/>
+      <c r="P68" s="36"/>
+      <c r="Q68" s="36"/>
+      <c r="R68" s="36"/>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="A69" s="85"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="80"/>
+      <c r="D69" s="81"/>
+      <c r="E69" s="80"/>
+      <c r="F69" s="81"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="72"/>
+      <c r="I69" s="71"/>
+      <c r="J69" s="72"/>
+      <c r="K69" s="59"/>
+      <c r="L69" s="60"/>
+      <c r="M69" s="36"/>
+      <c r="N69" s="36"/>
+      <c r="O69" s="36"/>
+      <c r="P69" s="36"/>
+      <c r="Q69" s="36"/>
+      <c r="R69" s="36"/>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="A70" s="85"/>
+      <c r="B70" s="77"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="83"/>
+      <c r="E70" s="82"/>
+      <c r="F70" s="83"/>
+      <c r="G70" s="73"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="73"/>
+      <c r="J70" s="74"/>
+      <c r="K70" s="61"/>
+      <c r="L70" s="62"/>
+      <c r="M70" s="36"/>
+      <c r="N70" s="36"/>
+      <c r="O70" s="36"/>
+      <c r="P70" s="36"/>
+      <c r="Q70" s="36"/>
+      <c r="R70" s="36"/>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="A71" s="85"/>
+      <c r="B71" s="75" t="s">
         <v>1116</v>
       </c>
-      <c r="P59" s="46"/>
-      <c r="Q59" s="46"/>
-      <c r="R59" s="47"/>
-    </row>
-    <row r="60" spans="1:18">
-      <c r="A60" s="82"/>
-      <c r="B60" s="86"/>
-      <c r="C60" s="91"/>
-      <c r="D60" s="92"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="98"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="98"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="103"/>
-      <c r="L60" s="104"/>
-      <c r="M60" s="38"/>
-      <c r="N60" s="38"/>
-      <c r="O60" s="38"/>
-      <c r="P60" s="38"/>
-      <c r="Q60" s="38"/>
-      <c r="R60" s="38"/>
-    </row>
-    <row r="61" spans="1:18">
-      <c r="A61" s="82"/>
-      <c r="B61" s="84" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C61" s="105" t="s">
+      <c r="C71" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="106"/>
-      <c r="E61" s="87" t="s">
+      <c r="D71" s="79"/>
+      <c r="E71" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="79"/>
+      <c r="G71" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="79"/>
+      <c r="I71" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="79"/>
+      <c r="K71" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="88"/>
-      <c r="G61" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="H61" s="94"/>
-      <c r="I61" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="J61" s="94"/>
-      <c r="K61" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="L61" s="100"/>
-      <c r="M61" s="38"/>
-      <c r="N61" s="38"/>
-      <c r="O61" s="38"/>
-      <c r="P61" s="38"/>
-      <c r="Q61" s="38"/>
-      <c r="R61" s="38"/>
-    </row>
-    <row r="62" spans="1:18">
-      <c r="A62" s="82"/>
-      <c r="B62" s="85"/>
-      <c r="C62" s="107"/>
-      <c r="D62" s="108"/>
-      <c r="E62" s="89"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="95"/>
-      <c r="H62" s="96"/>
-      <c r="I62" s="95"/>
-      <c r="J62" s="96"/>
-      <c r="K62" s="101"/>
-      <c r="L62" s="102"/>
-      <c r="M62" s="38"/>
-      <c r="N62" s="38"/>
-      <c r="O62" s="38"/>
-      <c r="P62" s="38"/>
-      <c r="Q62" s="38"/>
-      <c r="R62" s="38"/>
-    </row>
-    <row r="63" spans="1:18">
-      <c r="A63" s="82"/>
-      <c r="B63" s="85"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="108"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="95"/>
-      <c r="H63" s="96"/>
-      <c r="I63" s="95"/>
-      <c r="J63" s="96"/>
-      <c r="K63" s="101"/>
-      <c r="L63" s="102"/>
-      <c r="M63" s="38"/>
-      <c r="N63" s="38"/>
-      <c r="O63" s="38"/>
-      <c r="P63" s="38"/>
-      <c r="Q63" s="38"/>
-      <c r="R63" s="38"/>
-    </row>
-    <row r="64" spans="1:18">
-      <c r="A64" s="82"/>
-      <c r="B64" s="85"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="108"/>
-      <c r="E64" s="89"/>
-      <c r="F64" s="90"/>
-      <c r="G64" s="95"/>
-      <c r="H64" s="96"/>
-      <c r="I64" s="95"/>
-      <c r="J64" s="96"/>
-      <c r="K64" s="101"/>
-      <c r="L64" s="102"/>
-      <c r="M64" s="38"/>
-      <c r="N64" s="38"/>
-      <c r="O64" s="38"/>
-      <c r="P64" s="38"/>
-      <c r="Q64" s="38"/>
-      <c r="R64" s="38"/>
-    </row>
-    <row r="65" spans="1:18">
-      <c r="A65" s="82"/>
-      <c r="B65" s="86"/>
-      <c r="C65" s="109"/>
-      <c r="D65" s="110"/>
-      <c r="E65" s="91"/>
-      <c r="F65" s="92"/>
-      <c r="G65" s="97"/>
-      <c r="H65" s="98"/>
-      <c r="I65" s="97"/>
-      <c r="J65" s="98"/>
-      <c r="K65" s="103"/>
-      <c r="L65" s="104"/>
-      <c r="M65" s="38"/>
-      <c r="N65" s="38"/>
-      <c r="O65" s="38"/>
-      <c r="P65" s="38"/>
-      <c r="Q65" s="38"/>
-      <c r="R65" s="38"/>
-    </row>
-    <row r="66" spans="1:18">
-      <c r="A66" s="82"/>
-      <c r="B66" s="84" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C66" s="105" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="106"/>
-      <c r="E66" s="105" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="106"/>
-      <c r="G66" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="H66" s="88"/>
-      <c r="I66" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="J66" s="88"/>
-      <c r="K66" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="L66" s="94"/>
-      <c r="M66" s="38"/>
-      <c r="N66" s="38"/>
-      <c r="O66" s="38"/>
-      <c r="P66" s="38"/>
-      <c r="Q66" s="38"/>
-      <c r="R66" s="38"/>
-    </row>
-    <row r="67" spans="1:18">
-      <c r="A67" s="82"/>
-      <c r="B67" s="85"/>
-      <c r="C67" s="107"/>
-      <c r="D67" s="108"/>
-      <c r="E67" s="107"/>
-      <c r="F67" s="108"/>
-      <c r="G67" s="89"/>
-      <c r="H67" s="90"/>
-      <c r="I67" s="89"/>
-      <c r="J67" s="90"/>
-      <c r="K67" s="95"/>
-      <c r="L67" s="96"/>
-      <c r="M67" s="38"/>
-      <c r="N67" s="38"/>
-      <c r="O67" s="38"/>
-      <c r="P67" s="38"/>
-      <c r="Q67" s="38"/>
-      <c r="R67" s="38"/>
-    </row>
-    <row r="68" spans="1:18">
-      <c r="A68" s="82"/>
-      <c r="B68" s="85"/>
-      <c r="C68" s="107"/>
-      <c r="D68" s="108"/>
-      <c r="E68" s="107"/>
-      <c r="F68" s="108"/>
-      <c r="G68" s="89"/>
-      <c r="H68" s="90"/>
-      <c r="I68" s="89"/>
-      <c r="J68" s="90"/>
-      <c r="K68" s="95"/>
-      <c r="L68" s="96"/>
-      <c r="M68" s="38"/>
-      <c r="N68" s="38"/>
-      <c r="O68" s="38"/>
-      <c r="P68" s="38"/>
-      <c r="Q68" s="38"/>
-      <c r="R68" s="38"/>
-    </row>
-    <row r="69" spans="1:18">
-      <c r="A69" s="82"/>
-      <c r="B69" s="85"/>
-      <c r="C69" s="107"/>
-      <c r="D69" s="108"/>
-      <c r="E69" s="107"/>
-      <c r="F69" s="108"/>
-      <c r="G69" s="89"/>
-      <c r="H69" s="90"/>
-      <c r="I69" s="89"/>
-      <c r="J69" s="90"/>
-      <c r="K69" s="95"/>
-      <c r="L69" s="96"/>
-      <c r="M69" s="38"/>
-      <c r="N69" s="38"/>
-      <c r="O69" s="38"/>
-      <c r="P69" s="38"/>
-      <c r="Q69" s="38"/>
-      <c r="R69" s="38"/>
-    </row>
-    <row r="70" spans="1:18">
-      <c r="A70" s="82"/>
-      <c r="B70" s="86"/>
-      <c r="C70" s="109"/>
-      <c r="D70" s="110"/>
-      <c r="E70" s="109"/>
-      <c r="F70" s="110"/>
-      <c r="G70" s="91"/>
-      <c r="H70" s="92"/>
-      <c r="I70" s="91"/>
-      <c r="J70" s="92"/>
-      <c r="K70" s="97"/>
-      <c r="L70" s="98"/>
-      <c r="M70" s="38"/>
-      <c r="N70" s="38"/>
-      <c r="O70" s="38"/>
-      <c r="P70" s="38"/>
-      <c r="Q70" s="38"/>
-      <c r="R70" s="38"/>
-    </row>
-    <row r="71" spans="1:18">
-      <c r="A71" s="82"/>
-      <c r="B71" s="84" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C71" s="105" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" s="106"/>
-      <c r="E71" s="105" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="106"/>
-      <c r="G71" s="105" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" s="106"/>
-      <c r="I71" s="105" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="106"/>
-      <c r="K71" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="L71" s="88"/>
-      <c r="M71" s="38"/>
-      <c r="N71" s="38"/>
-      <c r="O71" s="38"/>
-      <c r="P71" s="38"/>
-      <c r="Q71" s="38"/>
-      <c r="R71" s="38"/>
+      <c r="L71" s="70"/>
+      <c r="M71" s="36"/>
+      <c r="N71" s="36"/>
+      <c r="O71" s="36"/>
+      <c r="P71" s="36"/>
+      <c r="Q71" s="36"/>
+      <c r="R71" s="36"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="82"/>
-      <c r="B72" s="85"/>
-      <c r="C72" s="107"/>
-      <c r="D72" s="108"/>
-      <c r="E72" s="107"/>
-      <c r="F72" s="108"/>
-      <c r="G72" s="107"/>
-      <c r="H72" s="108"/>
-      <c r="I72" s="107"/>
-      <c r="J72" s="108"/>
-      <c r="K72" s="89"/>
-      <c r="L72" s="90"/>
-      <c r="M72" s="38"/>
-      <c r="N72" s="38"/>
-      <c r="O72" s="38"/>
-      <c r="P72" s="38"/>
-      <c r="Q72" s="38"/>
-      <c r="R72" s="38"/>
+      <c r="A72" s="85"/>
+      <c r="B72" s="76"/>
+      <c r="C72" s="80"/>
+      <c r="D72" s="81"/>
+      <c r="E72" s="80"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="80"/>
+      <c r="H72" s="81"/>
+      <c r="I72" s="80"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="71"/>
+      <c r="L72" s="72"/>
+      <c r="M72" s="36"/>
+      <c r="N72" s="36"/>
+      <c r="O72" s="36"/>
+      <c r="P72" s="36"/>
+      <c r="Q72" s="36"/>
+      <c r="R72" s="36"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="82"/>
-      <c r="B73" s="85"/>
-      <c r="C73" s="107"/>
-      <c r="D73" s="108"/>
-      <c r="E73" s="107"/>
-      <c r="F73" s="108"/>
-      <c r="G73" s="107"/>
-      <c r="H73" s="108"/>
-      <c r="I73" s="107"/>
-      <c r="J73" s="108"/>
-      <c r="K73" s="89"/>
-      <c r="L73" s="90"/>
-      <c r="M73" s="38"/>
-      <c r="N73" s="38"/>
-      <c r="O73" s="38"/>
-      <c r="P73" s="38"/>
-      <c r="Q73" s="38"/>
-      <c r="R73" s="38"/>
+      <c r="A73" s="85"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="80"/>
+      <c r="D73" s="81"/>
+      <c r="E73" s="80"/>
+      <c r="F73" s="81"/>
+      <c r="G73" s="80"/>
+      <c r="H73" s="81"/>
+      <c r="I73" s="80"/>
+      <c r="J73" s="81"/>
+      <c r="K73" s="71"/>
+      <c r="L73" s="72"/>
+      <c r="M73" s="36"/>
+      <c r="N73" s="36"/>
+      <c r="O73" s="36"/>
+      <c r="P73" s="36"/>
+      <c r="Q73" s="36"/>
+      <c r="R73" s="36"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="82"/>
-      <c r="B74" s="85"/>
-      <c r="C74" s="107"/>
-      <c r="D74" s="108"/>
-      <c r="E74" s="107"/>
-      <c r="F74" s="108"/>
-      <c r="G74" s="107"/>
-      <c r="H74" s="108"/>
-      <c r="I74" s="107"/>
-      <c r="J74" s="108"/>
-      <c r="K74" s="89"/>
-      <c r="L74" s="90"/>
-      <c r="M74" s="38"/>
-      <c r="N74" s="38"/>
-      <c r="O74" s="38"/>
-      <c r="P74" s="38"/>
-      <c r="Q74" s="38"/>
-      <c r="R74" s="38"/>
+      <c r="A74" s="85"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="80"/>
+      <c r="D74" s="81"/>
+      <c r="E74" s="80"/>
+      <c r="F74" s="81"/>
+      <c r="G74" s="80"/>
+      <c r="H74" s="81"/>
+      <c r="I74" s="80"/>
+      <c r="J74" s="81"/>
+      <c r="K74" s="71"/>
+      <c r="L74" s="72"/>
+      <c r="M74" s="36"/>
+      <c r="N74" s="36"/>
+      <c r="O74" s="36"/>
+      <c r="P74" s="36"/>
+      <c r="Q74" s="36"/>
+      <c r="R74" s="36"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="83"/>
-      <c r="B75" s="86"/>
-      <c r="C75" s="109"/>
-      <c r="D75" s="110"/>
-      <c r="E75" s="109"/>
-      <c r="F75" s="110"/>
-      <c r="G75" s="109"/>
-      <c r="H75" s="110"/>
-      <c r="I75" s="109"/>
-      <c r="J75" s="110"/>
-      <c r="K75" s="91"/>
-      <c r="L75" s="92"/>
-      <c r="M75" s="38"/>
-      <c r="N75" s="38"/>
-      <c r="O75" s="38"/>
-      <c r="P75" s="38"/>
-      <c r="Q75" s="38"/>
-      <c r="R75" s="38"/>
+      <c r="A75" s="86"/>
+      <c r="B75" s="77"/>
+      <c r="C75" s="82"/>
+      <c r="D75" s="83"/>
+      <c r="E75" s="82"/>
+      <c r="F75" s="83"/>
+      <c r="G75" s="82"/>
+      <c r="H75" s="83"/>
+      <c r="I75" s="82"/>
+      <c r="J75" s="83"/>
+      <c r="K75" s="73"/>
+      <c r="L75" s="74"/>
+      <c r="M75" s="36"/>
+      <c r="N75" s="36"/>
+      <c r="O75" s="36"/>
+      <c r="P75" s="36"/>
+      <c r="Q75" s="36"/>
+      <c r="R75" s="36"/>
     </row>
     <row r="76" spans="1:18">
-      <c r="A76" s="38"/>
-      <c r="B76" s="38"/>
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="38"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
-      <c r="L76" s="38"/>
-      <c r="M76" s="38"/>
-      <c r="N76" s="38"/>
-      <c r="O76" s="38"/>
-      <c r="P76" s="38"/>
-      <c r="Q76" s="38"/>
-      <c r="R76" s="38"/>
+      <c r="A76" s="36"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
+      <c r="J76" s="36"/>
+      <c r="K76" s="36"/>
+      <c r="L76" s="36"/>
+      <c r="M76" s="36"/>
+      <c r="N76" s="36"/>
+      <c r="O76" s="36"/>
+      <c r="P76" s="36"/>
+      <c r="Q76" s="36"/>
+      <c r="R76" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A47:B50"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A51:A75"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:D55"/>
+    <mergeCell ref="E51:F55"/>
+    <mergeCell ref="G51:H55"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:D65"/>
+    <mergeCell ref="E61:F65"/>
+    <mergeCell ref="G61:H65"/>
+    <mergeCell ref="I51:J55"/>
+    <mergeCell ref="K51:L55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:D60"/>
+    <mergeCell ref="E56:F60"/>
+    <mergeCell ref="G56:H60"/>
+    <mergeCell ref="I56:J60"/>
+    <mergeCell ref="K56:L60"/>
     <mergeCell ref="I61:J65"/>
     <mergeCell ref="K61:L65"/>
     <mergeCell ref="K71:L75"/>
@@ -30579,34 +30633,6 @@
     <mergeCell ref="E71:F75"/>
     <mergeCell ref="G71:H75"/>
     <mergeCell ref="I71:J75"/>
-    <mergeCell ref="I51:J55"/>
-    <mergeCell ref="K51:L55"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:D60"/>
-    <mergeCell ref="E56:F60"/>
-    <mergeCell ref="G56:H60"/>
-    <mergeCell ref="I56:J60"/>
-    <mergeCell ref="K56:L60"/>
-    <mergeCell ref="A51:A75"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:D55"/>
-    <mergeCell ref="E51:F55"/>
-    <mergeCell ref="G51:H55"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:D65"/>
-    <mergeCell ref="E61:F65"/>
-    <mergeCell ref="G61:H65"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A47:B50"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30627,16 +30653,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" s="1" customFormat="1" ht="33.75">
-      <c r="A1" s="54" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="58" t="s">
+      <c r="A1" s="52" t="s">
         <v>1123</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="56" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
@@ -30757,22 +30783,22 @@
       <c r="BI2"/>
     </row>
     <row r="3" spans="1:61">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="51" t="s">
+        <v>677</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="51" t="s">
         <v>678</v>
       </c>
-      <c r="B3" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="53" t="s">
-        <v>679</v>
-      </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="51" t="s">
         <v>8</v>
       </c>
       <c r="G3"/>
@@ -30832,8 +30858,8 @@
       <c r="BI3"/>
     </row>
     <row r="4" spans="1:61" ht="15.75">
-      <c r="A4" s="56" t="s">
-        <v>680</v>
+      <c r="A4" s="54" t="s">
+        <v>679</v>
       </c>
       <c r="B4">
         <v>14</v>
@@ -30842,10 +30868,10 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
+        <v>680</v>
+      </c>
+      <c r="E4" t="s">
         <v>681</v>
-      </c>
-      <c r="E4" t="s">
-        <v>682</v>
       </c>
       <c r="F4" t="s">
         <v>267</v>
@@ -30907,8 +30933,8 @@
       <c r="BI4"/>
     </row>
     <row r="5" spans="1:61" ht="15.75">
-      <c r="A5" s="56" t="s">
-        <v>683</v>
+      <c r="A5" s="54" t="s">
+        <v>682</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -30917,10 +30943,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F5" t="s">
         <v>267</v>
@@ -30982,8 +31008,8 @@
       <c r="BI5"/>
     </row>
     <row r="6" spans="1:61" ht="15.75" hidden="1">
-      <c r="A6" s="56" t="s">
-        <v>685</v>
+      <c r="A6" s="54" t="s">
+        <v>684</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -30992,10 +31018,10 @@
         <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F6" t="s">
         <v>267</v>
@@ -31057,8 +31083,8 @@
       <c r="BI6"/>
     </row>
     <row r="7" spans="1:61" ht="15.75" hidden="1">
-      <c r="A7" s="56" t="s">
-        <v>687</v>
+      <c r="A7" s="54" t="s">
+        <v>686</v>
       </c>
       <c r="B7">
         <v>0.13</v>
@@ -31067,10 +31093,10 @@
         <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F7" t="s">
         <v>267</v>
@@ -31132,8 +31158,8 @@
       <c r="BI7"/>
     </row>
     <row r="8" spans="1:61" ht="15.75" hidden="1">
-      <c r="A8" s="56" t="s">
-        <v>689</v>
+      <c r="A8" s="54" t="s">
+        <v>688</v>
       </c>
       <c r="B8">
         <v>0.75</v>
@@ -31142,10 +31168,10 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E8" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F8" t="s">
         <v>267</v>
@@ -31207,20 +31233,20 @@
       <c r="BI8"/>
     </row>
     <row r="9" spans="1:61" ht="15.75" hidden="1">
-      <c r="A9" s="56" t="s">
-        <v>691</v>
+      <c r="A9" s="54" t="s">
+        <v>690</v>
       </c>
       <c r="B9">
         <v>0.25</v>
       </c>
       <c r="C9" t="s">
+        <v>691</v>
+      </c>
+      <c r="D9" t="s">
+        <v>680</v>
+      </c>
+      <c r="E9" t="s">
         <v>692</v>
-      </c>
-      <c r="D9" t="s">
-        <v>681</v>
-      </c>
-      <c r="E9" t="s">
-        <v>693</v>
       </c>
       <c r="F9" t="s">
         <v>267</v>
@@ -31282,20 +31308,20 @@
       <c r="BI9"/>
     </row>
     <row r="10" spans="1:61" ht="15.75" hidden="1">
-      <c r="A10" s="56" t="s">
-        <v>694</v>
+      <c r="A10" s="54" t="s">
+        <v>693</v>
       </c>
       <c r="B10">
         <v>18</v>
       </c>
       <c r="C10" t="s">
+        <v>694</v>
+      </c>
+      <c r="D10" t="s">
+        <v>680</v>
+      </c>
+      <c r="E10" t="s">
         <v>695</v>
-      </c>
-      <c r="D10" t="s">
-        <v>681</v>
-      </c>
-      <c r="E10" t="s">
-        <v>696</v>
       </c>
       <c r="F10" t="s">
         <v>267</v>
@@ -31357,8 +31383,8 @@
       <c r="BI10"/>
     </row>
     <row r="11" spans="1:61" ht="15.75" hidden="1">
-      <c r="A11" s="56" t="s">
-        <v>697</v>
+      <c r="A11" s="54" t="s">
+        <v>696</v>
       </c>
       <c r="B11">
         <v>14</v>
@@ -31367,10 +31393,10 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E11" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F11" t="s">
         <v>267</v>
@@ -31432,8 +31458,8 @@
       <c r="BI11"/>
     </row>
     <row r="12" spans="1:61" ht="15.75" hidden="1">
-      <c r="A12" s="56" t="s">
-        <v>699</v>
+      <c r="A12" s="54" t="s">
+        <v>698</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -31442,10 +31468,10 @@
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E12" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F12" t="s">
         <v>267</v>
@@ -31507,8 +31533,8 @@
       <c r="BI12"/>
     </row>
     <row r="13" spans="1:61" ht="15.75" hidden="1">
-      <c r="A13" s="56" t="s">
-        <v>701</v>
+      <c r="A13" s="54" t="s">
+        <v>700</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -31517,10 +31543,10 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F13" t="s">
         <v>267</v>
@@ -31582,8 +31608,8 @@
       <c r="BI13"/>
     </row>
     <row r="14" spans="1:61" ht="15.75" hidden="1">
-      <c r="A14" s="56" t="s">
-        <v>703</v>
+      <c r="A14" s="54" t="s">
+        <v>702</v>
       </c>
       <c r="B14">
         <f>B11-B12-B13</f>
@@ -31596,7 +31622,7 @@
         <v>264</v>
       </c>
       <c r="E14" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -31658,20 +31684,20 @@
       <c r="BI14"/>
     </row>
     <row r="15" spans="1:61" s="4" customFormat="1" ht="15.75" hidden="1">
-      <c r="A15" s="56" t="s">
-        <v>705</v>
+      <c r="A15" s="54" t="s">
+        <v>704</v>
       </c>
       <c r="B15">
         <v>0.25</v>
       </c>
       <c r="C15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F15" t="s">
         <v>267</v>
@@ -31733,8 +31759,8 @@
       <c r="BI15"/>
     </row>
     <row r="16" spans="1:61" ht="15.75" hidden="1">
-      <c r="A16" s="56" t="s">
-        <v>707</v>
+      <c r="A16" s="54" t="s">
+        <v>706</v>
       </c>
       <c r="B16">
         <v>0.97499999999999998</v>
@@ -31743,10 +31769,10 @@
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E16" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F16" t="s">
         <v>267</v>
@@ -31808,8 +31834,8 @@
       <c r="BI16"/>
     </row>
     <row r="17" spans="1:61" ht="15.75" hidden="1">
-      <c r="A17" s="56" t="s">
-        <v>709</v>
+      <c r="A17" s="54" t="s">
+        <v>708</v>
       </c>
       <c r="B17">
         <v>0.17499999999999999</v>
@@ -31818,10 +31844,10 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E17" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F17" t="s">
         <v>267</v>
@@ -31883,20 +31909,20 @@
       <c r="BI17"/>
     </row>
     <row r="18" spans="1:61" ht="15.75">
-      <c r="A18" s="56" t="s">
-        <v>711</v>
+      <c r="A18" s="54" t="s">
+        <v>710</v>
       </c>
       <c r="B18">
         <v>0.64900000000000002</v>
       </c>
       <c r="C18" t="s">
+        <v>711</v>
+      </c>
+      <c r="D18" t="s">
+        <v>680</v>
+      </c>
+      <c r="E18" t="s">
         <v>712</v>
-      </c>
-      <c r="D18" t="s">
-        <v>681</v>
-      </c>
-      <c r="E18" t="s">
-        <v>713</v>
       </c>
       <c r="F18" t="s">
         <v>267</v>
@@ -31958,20 +31984,20 @@
       <c r="BI18"/>
     </row>
     <row r="19" spans="1:61" ht="15.75">
-      <c r="A19" s="56" t="s">
-        <v>714</v>
+      <c r="A19" s="54" t="s">
+        <v>713</v>
       </c>
       <c r="B19">
         <v>2.8150000000000001E-2</v>
       </c>
       <c r="C19" t="s">
+        <v>714</v>
+      </c>
+      <c r="D19" t="s">
+        <v>680</v>
+      </c>
+      <c r="E19" t="s">
         <v>715</v>
-      </c>
-      <c r="D19" t="s">
-        <v>681</v>
-      </c>
-      <c r="E19" t="s">
-        <v>716</v>
       </c>
       <c r="F19" t="s">
         <v>267</v>
@@ -32033,7 +32059,7 @@
       <c r="BI19"/>
     </row>
     <row r="20" spans="1:61" ht="15.75" hidden="1">
-      <c r="A20" s="56"/>
+      <c r="A20" s="54"/>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -32096,8 +32122,8 @@
       <c r="BI20"/>
     </row>
     <row r="21" spans="1:61" ht="15.75" hidden="1">
-      <c r="A21" s="56" t="s">
-        <v>717</v>
+      <c r="A21" s="54" t="s">
+        <v>716</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
@@ -32106,10 +32132,10 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
+        <v>717</v>
+      </c>
+      <c r="E21" t="s">
         <v>718</v>
-      </c>
-      <c r="E21" t="s">
-        <v>719</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -32171,18 +32197,18 @@
       <c r="BI21"/>
     </row>
     <row r="22" spans="1:61" ht="15.75">
-      <c r="A22" s="56" t="s">
-        <v>720</v>
+      <c r="A22" s="54" t="s">
+        <v>719</v>
       </c>
       <c r="B22">
         <f>B14*B15</f>
         <v>2.75</v>
       </c>
       <c r="C22" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D22" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -32247,18 +32273,18 @@
       <c r="BI22"/>
     </row>
     <row r="23" spans="1:61" ht="15.75">
-      <c r="A23" s="56" t="s">
-        <v>722</v>
+      <c r="A23" s="54" t="s">
+        <v>721</v>
       </c>
       <c r="B23">
         <f>B22*8760*B16/1000</f>
         <v>23.487749999999998</v>
       </c>
       <c r="C23" t="s">
+        <v>722</v>
+      </c>
+      <c r="D23" t="s">
         <v>723</v>
-      </c>
-      <c r="D23" t="s">
-        <v>724</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
@@ -32323,18 +32349,18 @@
       <c r="BI23"/>
     </row>
     <row r="24" spans="1:61" ht="15.75">
-      <c r="A24" s="56" t="s">
-        <v>725</v>
+      <c r="A24" s="54" t="s">
+        <v>724</v>
       </c>
       <c r="B24">
         <f>B23*B17</f>
         <v>4.1103562499999997</v>
       </c>
       <c r="C24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D24" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -32399,18 +32425,18 @@
       <c r="BI24"/>
     </row>
     <row r="25" spans="1:61" ht="15.75">
-      <c r="A25" s="56" t="s">
-        <v>727</v>
+      <c r="A25" s="54" t="s">
+        <v>726</v>
       </c>
       <c r="B25">
         <f>B23*B19</f>
         <v>0.6611801625</v>
       </c>
       <c r="C25" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D25" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -32475,18 +32501,18 @@
       <c r="BI25"/>
     </row>
     <row r="26" spans="1:61" ht="15.75">
-      <c r="A26" s="56" t="s">
-        <v>729</v>
+      <c r="A26" s="54" t="s">
+        <v>728</v>
       </c>
       <c r="B26">
         <f>B18+B25</f>
         <v>1.3101801625</v>
       </c>
       <c r="C26" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D26" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -32551,18 +32577,18 @@
       <c r="BI26"/>
     </row>
     <row r="27" spans="1:61" ht="15.75">
-      <c r="A27" s="56" t="s">
-        <v>731</v>
+      <c r="A27" s="54" t="s">
+        <v>730</v>
       </c>
       <c r="B27">
         <f>B24-B26</f>
         <v>2.8001760874999997</v>
       </c>
       <c r="C27" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D27" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -32627,7 +32653,7 @@
       <c r="BI27"/>
     </row>
     <row r="28" spans="1:61" ht="15.75">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="54" t="s">
         <v>22</v>
       </c>
       <c r="B28">
@@ -32638,10 +32664,10 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
+        <v>732</v>
+      </c>
+      <c r="E28" t="s">
         <v>733</v>
-      </c>
-      <c r="E28" t="s">
-        <v>734</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
@@ -32703,17 +32729,17 @@
       <c r="BI28"/>
     </row>
     <row r="29" spans="1:61" ht="15.75">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="55" t="s">
         <v>246</v>
       </c>
       <c r="B29">
         <v>0.3</v>
       </c>
       <c r="C29" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D29" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -32778,18 +32804,18 @@
       <c r="BI29"/>
     </row>
     <row r="30" spans="1:61" ht="15.75">
-      <c r="A30" s="56" t="s">
-        <v>736</v>
+      <c r="A30" s="54" t="s">
+        <v>735</v>
       </c>
       <c r="B30">
         <f>B27-B29</f>
         <v>2.5001760874999999</v>
       </c>
       <c r="C30" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D30" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -32854,8 +32880,8 @@
       <c r="BI30"/>
     </row>
     <row r="31" spans="1:61" ht="15.75">
-      <c r="A31" s="56" t="s">
-        <v>738</v>
+      <c r="A31" s="54" t="s">
+        <v>737</v>
       </c>
       <c r="B31" s="16">
         <f>IRR(B36:L36)</f>
@@ -32865,10 +32891,10 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
+        <v>738</v>
+      </c>
+      <c r="E31" t="s">
         <v>739</v>
-      </c>
-      <c r="E31" t="s">
-        <v>740</v>
       </c>
       <c r="F31" t="s">
         <v>19</v>
@@ -32930,21 +32956,21 @@
       <c r="BI31"/>
     </row>
     <row r="32" spans="1:61" ht="15.75">
-      <c r="A32" s="56" t="s">
-        <v>741</v>
+      <c r="A32" s="54" t="s">
+        <v>740</v>
       </c>
       <c r="B32" t="str">
         <f>IF(AND(B31&gt;=B6,B31&lt;=B7),"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
       <c r="C32" t="s">
+        <v>741</v>
+      </c>
+      <c r="D32" t="s">
         <v>742</v>
       </c>
-      <c r="D32" t="s">
-        <v>743</v>
-      </c>
       <c r="E32" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -33006,21 +33032,21 @@
       <c r="BI32"/>
     </row>
     <row r="33" spans="1:61" ht="15.75">
-      <c r="A33" s="56" t="s">
-        <v>744</v>
+      <c r="A33" s="54" t="s">
+        <v>743</v>
       </c>
       <c r="B33" t="str">
         <f>IF(B28&lt;=B5,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
       <c r="C33" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D33" t="s">
+        <v>744</v>
+      </c>
+      <c r="E33" t="s">
         <v>745</v>
-      </c>
-      <c r="E33" t="s">
-        <v>746</v>
       </c>
       <c r="F33" t="s">
         <v>19</v>
@@ -33082,7 +33108,7 @@
       <c r="BI33"/>
     </row>
     <row r="34" spans="1:61" ht="15.75">
-      <c r="A34" s="56"/>
+      <c r="A34" s="54"/>
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -33145,8 +33171,8 @@
       <c r="BI34"/>
     </row>
     <row r="35" spans="1:61" ht="15.75">
-      <c r="A35" s="56" t="s">
-        <v>747</v>
+      <c r="A35" s="54" t="s">
+        <v>746</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -33232,8 +33258,8 @@
       <c r="BI35"/>
     </row>
     <row r="36" spans="1:61" ht="15.75">
-      <c r="A36" s="56" t="s">
-        <v>748</v>
+      <c r="A36" s="54" t="s">
+        <v>747</v>
       </c>
       <c r="B36">
         <f xml:space="preserve"> -B4</f>
@@ -33330,7 +33356,7 @@
       <c r="BI36"/>
     </row>
     <row r="37" spans="1:61" ht="15.75">
-      <c r="A37" s="56"/>
+      <c r="A37" s="54"/>
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -33393,7 +33419,7 @@
       <c r="BI37"/>
     </row>
     <row r="38" spans="1:61" ht="15.75">
-      <c r="A38" s="56"/>
+      <c r="A38" s="54"/>
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -33456,17 +33482,17 @@
       <c r="BI38"/>
     </row>
     <row r="39" spans="1:61" ht="15.75">
-      <c r="A39" s="56" t="s">
+      <c r="A39" s="54" t="s">
+        <v>748</v>
+      </c>
+      <c r="B39" t="s">
         <v>749</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>750</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>751</v>
-      </c>
-      <c r="D39" t="s">
-        <v>752</v>
       </c>
       <c r="E39" t="s">
         <v>2</v>
@@ -33531,8 +33557,8 @@
       <c r="BI39"/>
     </row>
     <row r="40" spans="1:61" ht="15.75">
-      <c r="A40" s="56" t="s">
-        <v>753</v>
+      <c r="A40" s="54" t="s">
+        <v>752</v>
       </c>
       <c r="B40">
         <v>0.155</v>
@@ -33544,7 +33570,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="E40" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F40" t="s">
         <v>507</v>
@@ -33606,8 +33632,8 @@
       <c r="BI40"/>
     </row>
     <row r="41" spans="1:61" ht="15.75">
-      <c r="A41" s="56" t="s">
-        <v>755</v>
+      <c r="A41" s="54" t="s">
+        <v>754</v>
       </c>
       <c r="B41">
         <v>0.96</v>
@@ -33619,7 +33645,7 @@
         <v>0.99</v>
       </c>
       <c r="E41" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F41" t="s">
         <v>19</v>
@@ -33681,8 +33707,8 @@
       <c r="BI41"/>
     </row>
     <row r="42" spans="1:61" ht="15.75">
-      <c r="A42" s="56" t="s">
-        <v>757</v>
+      <c r="A42" s="54" t="s">
+        <v>756</v>
       </c>
       <c r="B42">
         <f>$B$22*8760*B41/1000*B40-($B$18+($B$22*8760*B41/1000)*$B$19)</f>
@@ -33697,7 +33723,7 @@
         <v>3.3302223350000002</v>
       </c>
       <c r="E42" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F42" t="s">
         <v>267</v>
@@ -33759,8 +33785,8 @@
       <c r="BI42"/>
     </row>
     <row r="43" spans="1:61" ht="15.75">
-      <c r="A43" s="56" t="s">
-        <v>759</v>
+      <c r="A43" s="54" t="s">
+        <v>758</v>
       </c>
       <c r="B43">
         <f>$B$4/B42</f>
@@ -33775,7 +33801,7 @@
         <v>4.2039235197189919</v>
       </c>
       <c r="E43" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F43" t="s">
         <v>267</v>
@@ -33837,20 +33863,20 @@
       <c r="BI43"/>
     </row>
     <row r="44" spans="1:61" ht="15.75">
-      <c r="A44" s="56" t="s">
+      <c r="A44" s="54" t="s">
+        <v>760</v>
+      </c>
+      <c r="B44" t="s">
         <v>761</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>762</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>763</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>764</v>
-      </c>
-      <c r="E44" t="s">
-        <v>765</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -41241,47 +41267,47 @@
     <col min="8" max="10" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:10" ht="18.75">
+      <c r="A1" s="116" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B1" s="116"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>765</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>766</v>
       </c>
-      <c r="B1" s="17"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="21" t="s">
+      <c r="G3" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="H3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="I3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>767</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>768</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B4">
         <f>'Cost Benefit Analysis'!B4</f>
@@ -41291,16 +41317,16 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G4" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="H4">
         <f>'Cost Benefit Analysis'!B14</f>
@@ -41325,16 +41351,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H5" s="16">
         <f>'Cost Benefit Analysis'!B31</f>
@@ -41356,7 +41382,7 @@
         <v>23.487749999999998</v>
       </c>
       <c r="C6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -41365,7 +41391,7 @@
         <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G6" t="s">
         <v>525</v>
@@ -41383,14 +41409,14 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B7">
         <f>'Cost Benefit Analysis'!B24</f>
         <v>4.1103562499999997</v>
       </c>
       <c r="C7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
@@ -41399,17 +41425,17 @@
         <v>267</v>
       </c>
       <c r="F7" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G7" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="H7">
         <f>'Cost Benefit Analysis'!B26</f>
         <v>1.3101801625</v>
       </c>
       <c r="I7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="J7" t="s">
         <v>267</v>
@@ -41417,7 +41443,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B8">
         <v>14</v>
@@ -41432,10 +41458,10 @@
         <v>267</v>
       </c>
       <c r="F8" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G8" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -41449,7 +41475,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B9">
         <v>12</v>
@@ -41464,10 +41490,10 @@
         <v>267</v>
       </c>
       <c r="F9" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -41481,31 +41507,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
+        <v>779</v>
+      </c>
+      <c r="B10" t="s">
+        <v>780</v>
+      </c>
+      <c r="C10" t="s">
         <v>781</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>782</v>
-      </c>
-      <c r="C10" t="s">
-        <v>783</v>
-      </c>
-      <c r="D10" t="s">
-        <v>784</v>
       </c>
       <c r="E10" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
+        <v>783</v>
+      </c>
+      <c r="G10" t="s">
+        <v>784</v>
+      </c>
+      <c r="H10" t="s">
         <v>785</v>
       </c>
-      <c r="G10" t="s">
-        <v>786</v>
-      </c>
-      <c r="H10" t="s">
-        <v>787</v>
-      </c>
       <c r="I10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -41519,19 +41545,19 @@
         <v>367</v>
       </c>
       <c r="C13" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D13" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="H13" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="I13" t="s">
         <v>75</v>
@@ -41548,54 +41574,54 @@
         <v>368</v>
       </c>
       <c r="C14" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D14" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E14" t="s">
         <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="H14" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="I14">
         <v>14</v>
       </c>
       <c r="J14" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B15" t="s">
         <v>374</v>
       </c>
       <c r="C15" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D15" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E15" t="s">
         <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="H15" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -41606,25 +41632,25 @@
         <v>385</v>
       </c>
       <c r="C16" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D16" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E16" t="s">
         <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H16" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I16">
         <v>12</v>
       </c>
       <c r="J16" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -41635,19 +41661,19 @@
         <v>397</v>
       </c>
       <c r="C17" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D17" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E17" t="s">
         <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="H17" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -41664,25 +41690,25 @@
         <v>405</v>
       </c>
       <c r="C18" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D18" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E18" t="s">
         <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="H18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="I18">
         <v>11</v>
       </c>
       <c r="J18" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -41693,27 +41719,27 @@
         <v>414</v>
       </c>
       <c r="C19" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D19" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B20" t="s">
         <v>475</v>
       </c>
       <c r="C20" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D20" t="s">
         <v>380</v>
@@ -41722,15 +41748,15 @@
         <v>380</v>
       </c>
       <c r="F20" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B23" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
@@ -41739,115 +41765,115 @@
         <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
       </c>
       <c r="G23" t="s">
+        <v>822</v>
+      </c>
+      <c r="H23" t="s">
+        <v>823</v>
+      </c>
+      <c r="I23" t="s">
         <v>824</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
         <v>825</v>
-      </c>
-      <c r="I23" t="s">
-        <v>826</v>
-      </c>
-      <c r="J23" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B24" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C24" t="s">
         <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E24" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
       </c>
       <c r="G24" t="s">
+        <v>830</v>
+      </c>
+      <c r="H24" t="s">
+        <v>831</v>
+      </c>
+      <c r="I24" t="s">
         <v>832</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
         <v>833</v>
-      </c>
-      <c r="I24" t="s">
-        <v>834</v>
-      </c>
-      <c r="J24" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B25" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C25" t="s">
         <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E25" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
       </c>
       <c r="G25" t="s">
+        <v>838</v>
+      </c>
+      <c r="H25" t="s">
+        <v>839</v>
+      </c>
+      <c r="I25" t="s">
         <v>840</v>
       </c>
-      <c r="H25" t="s">
-        <v>841</v>
-      </c>
-      <c r="I25" t="s">
-        <v>842</v>
-      </c>
       <c r="J25" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B26" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E26" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F26" t="s">
         <v>19</v>
       </c>
       <c r="G26" t="s">
+        <v>844</v>
+      </c>
+      <c r="H26" t="s">
+        <v>845</v>
+      </c>
+      <c r="I26" t="s">
         <v>846</v>
-      </c>
-      <c r="H26" t="s">
-        <v>847</v>
-      </c>
-      <c r="I26" t="s">
-        <v>848</v>
       </c>
       <c r="J26" t="s">
         <v>380</v>
@@ -41855,772 +41881,772 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B27" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C27" t="s">
         <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E27" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
       </c>
       <c r="G27" t="s">
+        <v>850</v>
+      </c>
+      <c r="H27" t="s">
+        <v>851</v>
+      </c>
+      <c r="I27" t="s">
         <v>852</v>
       </c>
-      <c r="H27" t="s">
-        <v>853</v>
-      </c>
-      <c r="I27" t="s">
-        <v>854</v>
-      </c>
       <c r="J27" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B28" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C28" t="s">
         <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E28" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
       </c>
       <c r="G28" t="s">
+        <v>857</v>
+      </c>
+      <c r="H28" t="s">
+        <v>858</v>
+      </c>
+      <c r="I28" t="s">
         <v>859</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>860</v>
-      </c>
-      <c r="I28" t="s">
-        <v>861</v>
-      </c>
-      <c r="J28" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B29" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C29" t="s">
         <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E29" t="s">
+        <v>863</v>
+      </c>
+      <c r="F29" t="s">
+        <v>864</v>
+      </c>
+      <c r="G29" t="s">
         <v>865</v>
       </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
         <v>866</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>867</v>
       </c>
-      <c r="H29" t="s">
-        <v>868</v>
-      </c>
-      <c r="I29" t="s">
-        <v>869</v>
-      </c>
       <c r="J29" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B30" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C30" t="s">
         <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E30" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
       </c>
       <c r="G30" t="s">
+        <v>871</v>
+      </c>
+      <c r="H30" t="s">
+        <v>872</v>
+      </c>
+      <c r="I30" t="s">
         <v>873</v>
       </c>
-      <c r="H30" t="s">
-        <v>874</v>
-      </c>
-      <c r="I30" t="s">
-        <v>875</v>
-      </c>
       <c r="J30" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="21">
-      <c r="A33" s="111" t="s">
+      <c r="A33" s="109" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B33" s="110"/>
+      <c r="C33" s="110"/>
+      <c r="D33" s="110"/>
+      <c r="E33" s="110"/>
+      <c r="F33" s="110"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="110"/>
+      <c r="I33" s="110"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75">
+      <c r="A35" s="111" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B35" s="110"/>
+      <c r="C35" s="110"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="110"/>
+      <c r="H35" s="110"/>
+      <c r="I35" s="110"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="22" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B36" s="22" t="s">
         <v>1050</v>
       </c>
-      <c r="B33" s="112"/>
-      <c r="C33" s="112"/>
-      <c r="D33" s="112"/>
-      <c r="E33" s="112"/>
-      <c r="F33" s="112"/>
-      <c r="G33" s="112"/>
-      <c r="H33" s="112"/>
-      <c r="I33" s="112"/>
-    </row>
-    <row r="35" spans="1:9" ht="15.75">
-      <c r="A35" s="113" t="s">
+      <c r="C36" s="22" t="s">
         <v>1051</v>
       </c>
-      <c r="B35" s="112"/>
-      <c r="C35" s="112"/>
-      <c r="D35" s="112"/>
-      <c r="E35" s="112"/>
-      <c r="F35" s="112"/>
-      <c r="G35" s="112"/>
-      <c r="H35" s="112"/>
-      <c r="I35" s="112"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="24" t="s">
+      <c r="D36" s="22" t="s">
         <v>1052</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="E36" s="22" t="s">
         <v>1053</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="F36" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="D36" s="24" t="s">
+      <c r="G36" s="22" t="s">
         <v>1055</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="H36" s="22" t="s">
         <v>1056</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="I36" s="22" t="s">
         <v>1057</v>
       </c>
-      <c r="G36" s="24" t="s">
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="23" t="s">
         <v>1058</v>
       </c>
-      <c r="H36" s="24" t="s">
-        <v>1059</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="25" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B37" s="26">
+      <c r="B37" s="24">
         <v>285000</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="24">
         <v>119700</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="25">
         <f t="shared" ref="D37:F48" si="0">B37-C37</f>
         <v>165300</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="24">
         <v>95000</v>
       </c>
-      <c r="F37" s="27">
+      <c r="F37" s="25">
         <f t="shared" si="0"/>
         <v>70300</v>
       </c>
-      <c r="G37" s="26">
+      <c r="G37" s="24">
         <v>300000</v>
       </c>
-      <c r="H37" s="28">
+      <c r="H37" s="26">
         <v>142</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="25">
         <f t="shared" ref="I37:I48" si="1">B37/H37</f>
         <v>2007.0422535211267</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="29" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B38" s="30">
+      <c r="A38" s="27" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B38" s="28">
         <v>310000</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="28">
         <v>127100</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="29">
         <f t="shared" si="0"/>
         <v>182900</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="28">
         <v>98000</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="29">
         <f t="shared" si="0"/>
         <v>84900</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="28">
         <v>320000</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="30">
         <v>155</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="29">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="25" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B39" s="26">
+      <c r="A39" s="23" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B39" s="24">
         <v>340000</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="24">
         <v>136000</v>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="25">
         <f t="shared" si="0"/>
         <v>204000</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="24">
         <v>102000</v>
       </c>
-      <c r="F39" s="27">
+      <c r="F39" s="25">
         <f t="shared" si="0"/>
         <v>102000</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="24">
         <v>340000</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="26">
         <v>170</v>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="25">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="29" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B40" s="30">
+      <c r="A40" s="27" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B40" s="28">
         <v>325000</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="28">
         <v>136500</v>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="29">
         <f t="shared" si="0"/>
         <v>188500</v>
       </c>
-      <c r="E40" s="30">
+      <c r="E40" s="28">
         <v>100000</v>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="29">
         <f t="shared" si="0"/>
         <v>88500</v>
       </c>
-      <c r="G40" s="30">
+      <c r="G40" s="28">
         <v>360000</v>
       </c>
-      <c r="H40" s="32">
+      <c r="H40" s="30">
         <v>163</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="29">
         <f t="shared" si="1"/>
         <v>1993.8650306748466</v>
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="25" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B41" s="26">
+      <c r="A41" s="23" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B41" s="24">
         <v>365000</v>
       </c>
-      <c r="C41" s="26">
+      <c r="C41" s="24">
         <v>146000</v>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="25">
         <f t="shared" si="0"/>
         <v>219000</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="24">
         <v>105000</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F41" s="25">
         <f t="shared" si="0"/>
         <v>114000</v>
       </c>
-      <c r="G41" s="26">
+      <c r="G41" s="24">
         <v>380000</v>
       </c>
-      <c r="H41" s="28">
+      <c r="H41" s="26">
         <v>182</v>
       </c>
-      <c r="I41" s="27">
+      <c r="I41" s="25">
         <f t="shared" si="1"/>
         <v>2005.4945054945056</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="29" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B42" s="30">
+      <c r="A42" s="27" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B42" s="28">
         <v>390000</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="28">
         <v>152100</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="29">
         <f t="shared" si="0"/>
         <v>237900</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="28">
         <v>108000</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="29">
         <f t="shared" si="0"/>
         <v>129900</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G42" s="28">
         <v>400000</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="30">
         <v>195</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="29">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="25" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B43" s="26">
+      <c r="A43" s="23" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B43" s="24">
         <v>375000</v>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="24">
         <v>153750</v>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="25">
         <f t="shared" si="0"/>
         <v>221250</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="24">
         <v>106000</v>
       </c>
-      <c r="F43" s="27">
+      <c r="F43" s="25">
         <f t="shared" si="0"/>
         <v>115250</v>
       </c>
-      <c r="G43" s="26">
+      <c r="G43" s="24">
         <v>400000</v>
       </c>
-      <c r="H43" s="28">
+      <c r="H43" s="26">
         <v>188</v>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="25">
         <f t="shared" si="1"/>
         <v>1994.6808510638298</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="29" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B44" s="30">
+      <c r="A44" s="27" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B44" s="28">
         <v>410000</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="28">
         <v>159900</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="29">
         <f t="shared" si="0"/>
         <v>250100</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="28">
         <v>112000</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="29">
         <f t="shared" si="0"/>
         <v>138100</v>
       </c>
-      <c r="G44" s="30">
+      <c r="G44" s="28">
         <v>420000</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="30">
         <v>205</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="29">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="25" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B45" s="26">
+      <c r="A45" s="23" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B45" s="24">
         <v>425000</v>
       </c>
-      <c r="C45" s="26">
+      <c r="C45" s="24">
         <v>161500</v>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="25">
         <f t="shared" si="0"/>
         <v>263500</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="24">
         <v>115000</v>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="25">
         <f t="shared" si="0"/>
         <v>148500</v>
       </c>
-      <c r="G45" s="26">
+      <c r="G45" s="24">
         <v>440000</v>
       </c>
-      <c r="H45" s="28">
+      <c r="H45" s="26">
         <v>213</v>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="25">
         <f t="shared" si="1"/>
         <v>1995.3051643192489</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="29" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B46" s="30">
+      <c r="A46" s="27" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B46" s="28">
         <v>450000</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="28">
         <v>171000</v>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="29">
         <f t="shared" si="0"/>
         <v>279000</v>
       </c>
-      <c r="E46" s="30">
+      <c r="E46" s="28">
         <v>118000</v>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="29">
         <f t="shared" si="0"/>
         <v>161000</v>
       </c>
-      <c r="G46" s="30">
+      <c r="G46" s="28">
         <v>460000</v>
       </c>
-      <c r="H46" s="32">
+      <c r="H46" s="30">
         <v>225</v>
       </c>
-      <c r="I46" s="31">
+      <c r="I46" s="29">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="25" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B47" s="26">
+      <c r="A47" s="23" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B47" s="24">
         <v>470000</v>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="24">
         <v>173900</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="25">
         <f t="shared" si="0"/>
         <v>296100</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="24">
         <v>120000</v>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="25">
         <f t="shared" si="0"/>
         <v>176100</v>
       </c>
-      <c r="G47" s="26">
+      <c r="G47" s="24">
         <v>480000</v>
       </c>
-      <c r="H47" s="28">
+      <c r="H47" s="26">
         <v>235</v>
       </c>
-      <c r="I47" s="27">
+      <c r="I47" s="25">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="29" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B48" s="30">
+      <c r="A48" s="27" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B48" s="28">
         <v>520000</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="28">
         <v>187200</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="29">
         <f t="shared" si="0"/>
         <v>332800</v>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="28">
         <v>125000</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="29">
         <f t="shared" si="0"/>
         <v>207800</v>
       </c>
-      <c r="G48" s="30">
+      <c r="G48" s="28">
         <v>500000</v>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="30">
         <v>260</v>
       </c>
-      <c r="I48" s="31">
+      <c r="I48" s="29">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="33" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B49" s="34">
+      <c r="A49" s="31" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B49" s="32">
         <f t="shared" ref="B49:H49" si="2">SUM(B37:B48)</f>
         <v>4665000</v>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="32">
         <f t="shared" si="2"/>
         <v>1824650</v>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="32">
         <f t="shared" si="2"/>
         <v>2840350</v>
       </c>
-      <c r="E49" s="34">
+      <c r="E49" s="32">
         <f t="shared" si="2"/>
         <v>1304000</v>
       </c>
-      <c r="F49" s="34">
+      <c r="F49" s="32">
         <f t="shared" si="2"/>
         <v>1536350</v>
       </c>
-      <c r="G49" s="34">
+      <c r="G49" s="32">
         <f t="shared" si="2"/>
         <v>4800000</v>
       </c>
-      <c r="H49" s="35">
+      <c r="H49" s="33">
         <f t="shared" si="2"/>
         <v>2333</v>
       </c>
-      <c r="I49" s="34">
+      <c r="I49" s="32">
         <f>AVERAGE(I37:I48)</f>
         <v>1999.6989837561298</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75">
-      <c r="A52" s="113" t="s">
+      <c r="A52" s="111" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B52" s="110"/>
+      <c r="C52" s="110"/>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="22" t="s">
+        <v>611</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="34" t="s">
         <v>1074</v>
       </c>
-      <c r="B52" s="112"/>
-      <c r="C52" s="112"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="24" t="s">
-        <v>612</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="36" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B54" s="26">
+      <c r="B54" s="24">
         <v>720000</v>
       </c>
-      <c r="C54" s="37" t="e">
+      <c r="C54" s="35" t="e">
         <f t="shared" ref="C54:C60" si="3">B54/SUM(B$23:B$29)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="36" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B55" s="26">
+      <c r="A55" s="34" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B55" s="24">
         <v>180000</v>
       </c>
-      <c r="C55" s="37" t="e">
+      <c r="C55" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="36" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B56" s="26">
+      <c r="A56" s="34" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B56" s="24">
         <v>144000</v>
       </c>
-      <c r="C56" s="37" t="e">
+      <c r="C56" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="36" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B57" s="26">
+      <c r="A57" s="34" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B57" s="24">
         <v>96000</v>
       </c>
-      <c r="C57" s="37" t="e">
+      <c r="C57" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="36" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B58" s="26">
+      <c r="A58" s="34" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B58" s="24">
         <v>72000</v>
       </c>
-      <c r="C58" s="37" t="e">
+      <c r="C58" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="36" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B59" s="26">
+      <c r="A59" s="34" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B59" s="24">
         <v>48000</v>
       </c>
-      <c r="C59" s="37" t="e">
+      <c r="C59" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="36" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B60" s="26">
+      <c r="A60" s="34" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B60" s="24">
         <v>44000</v>
       </c>
-      <c r="C60" s="37" t="e">
+      <c r="C60" s="35" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.75">
-      <c r="A63" s="113" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B63" s="112"/>
-      <c r="C63" s="112"/>
+      <c r="A63" s="111" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B63" s="110"/>
+      <c r="C63" s="110"/>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="24" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B64" s="24" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>1076</v>
+      <c r="A64" s="22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>1073</v>
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="36" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B65" s="26">
+      <c r="A65" s="34" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B65" s="24">
         <v>2680000</v>
       </c>
-      <c r="C65" s="37">
+      <c r="C65" s="35">
         <f t="shared" ref="C65:C68" si="4">B65/SUM(B$34:B$37)</f>
         <v>9.4035087719298254</v>
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="36" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B66" s="26">
+      <c r="A66" s="34" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B66" s="24">
         <v>1180000</v>
       </c>
-      <c r="C66" s="37">
+      <c r="C66" s="35">
         <f t="shared" si="4"/>
         <v>4.1403508771929829</v>
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="36" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B67" s="26">
+      <c r="A67" s="34" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B67" s="24">
         <v>620000</v>
       </c>
-      <c r="C67" s="37">
+      <c r="C67" s="35">
         <f t="shared" si="4"/>
         <v>2.1754385964912282</v>
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="36" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B68" s="26">
+      <c r="A68" s="34" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B68" s="24">
         <v>185000</v>
       </c>
-      <c r="C68" s="37">
+      <c r="C68" s="35">
         <f t="shared" si="4"/>
         <v>0.64912280701754388</v>
       </c>
@@ -42728,7 +42754,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="37.5">
       <c r="A1" s="13" t="s">
-        <v>876</v>
+        <v>1120</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -42750,10 +42776,10 @@
     </row>
     <row r="3" spans="1:8" ht="26.25">
       <c r="A3" s="14" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>435</v>
@@ -42765,7 +42791,7 @@
         <v>437</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>32</v>
@@ -42776,22 +42802,22 @@
     </row>
     <row r="4" spans="1:8" ht="64.5">
       <c r="A4" s="11" t="s">
+        <v>877</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>879</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>880</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>881</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>882</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>883</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>884</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>27</v>
@@ -42802,22 +42828,22 @@
     </row>
     <row r="5" spans="1:8" ht="64.5">
       <c r="A5" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>884</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>885</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>887</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>888</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>889</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>890</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>369</v>
@@ -42828,22 +42854,22 @@
     </row>
     <row r="6" spans="1:8" ht="64.5">
       <c r="A6" s="11" t="s">
+        <v>888</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>889</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>890</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>891</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>892</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>893</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>894</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>896</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>27</v>
@@ -42854,22 +42880,22 @@
     </row>
     <row r="7" spans="1:8" ht="64.5">
       <c r="A7" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>897</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>898</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>899</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>900</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>901</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>902</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>72</v>
@@ -42880,19 +42906,19 @@
     </row>
     <row r="8" spans="1:8" ht="39">
       <c r="A8" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>903</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>904</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>905</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>906</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>907</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>481</v>
@@ -42906,22 +42932,22 @@
     </row>
     <row r="9" spans="1:8" ht="51.75">
       <c r="A9" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>906</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>907</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>908</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>909</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>910</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>911</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>912</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>913</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>110</v>
@@ -42932,22 +42958,22 @@
     </row>
     <row r="10" spans="1:8" ht="64.5">
       <c r="A10" s="11" t="s">
+        <v>911</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>912</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>913</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="F10" s="11" t="s">
         <v>916</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>917</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>918</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>919</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>27</v>
@@ -42958,22 +42984,22 @@
     </row>
     <row r="11" spans="1:8" ht="51.75">
       <c r="A11" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>918</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>919</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>920</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>921</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="F11" s="11" t="s">
         <v>922</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>923</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>924</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>925</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>47</v>
@@ -42984,22 +43010,22 @@
     </row>
     <row r="12" spans="1:8" ht="51.75">
       <c r="A12" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>924</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>925</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>926</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>927</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>928</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>929</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>930</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>931</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>70</v>
@@ -43010,25 +43036,25 @@
     </row>
     <row r="13" spans="1:8" ht="64.5">
       <c r="A13" s="11" t="s">
+        <v>929</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>930</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>931</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>932</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>933</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="F13" s="11" t="s">
         <v>934</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>935</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>936</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>937</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>938</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>19</v>
@@ -43036,22 +43062,22 @@
     </row>
     <row r="14" spans="1:8" ht="51.75">
       <c r="A14" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>937</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>938</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>939</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>941</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>942</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>943</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>70</v>
@@ -43062,22 +43088,22 @@
     </row>
     <row r="15" spans="1:8" ht="39">
       <c r="A15" s="11" t="s">
+        <v>941</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>942</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>944</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>945</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="F15" s="11" t="s">
         <v>946</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>947</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>948</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>949</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>53</v>
@@ -43088,19 +43114,19 @@
     </row>
     <row r="16" spans="1:8" ht="39">
       <c r="A16" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>948</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>950</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>951</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>952</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>953</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>954</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>457</v>
@@ -43114,22 +43140,22 @@
     </row>
     <row r="17" spans="1:8" ht="39">
       <c r="A17" s="11" t="s">
+        <v>952</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>953</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>954</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>955</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="F17" s="11" t="s">
         <v>957</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>958</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>959</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>960</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>124</v>
@@ -43140,22 +43166,22 @@
     </row>
     <row r="18" spans="1:8" ht="39">
       <c r="A18" s="11" t="s">
+        <v>958</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>960</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>961</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="E18" s="11" t="s">
         <v>962</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>963</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>964</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>965</v>
-      </c>
       <c r="F18" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>27</v>
@@ -43166,48 +43192,48 @@
     </row>
     <row r="19" spans="1:8" ht="51.75">
       <c r="A19" s="11" t="s">
+        <v>963</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>964</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>965</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="E19" s="11" t="s">
         <v>967</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>968</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>969</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>970</v>
-      </c>
       <c r="F19" s="11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39">
       <c r="A20" s="11" t="s">
+        <v>968</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>969</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>970</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>971</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>972</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="F20" s="11" t="s">
         <v>973</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>974</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>975</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>976</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>53</v>
@@ -43218,22 +43244,22 @@
     </row>
     <row r="21" spans="1:8" ht="64.5">
       <c r="A21" s="11" t="s">
+        <v>974</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>975</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>976</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>977</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="F21" s="11" t="s">
         <v>979</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>980</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>981</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>982</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>53</v>
@@ -43244,22 +43270,22 @@
     </row>
     <row r="22" spans="1:8" ht="39">
       <c r="A22" s="11" t="s">
+        <v>980</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>981</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>985</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>986</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>987</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>988</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>37</v>
@@ -43270,22 +43296,22 @@
     </row>
     <row r="23" spans="1:8" ht="39">
       <c r="A23" s="11" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>986</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>987</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>988</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="F23" s="11" t="s">
         <v>990</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>991</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>992</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>993</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>55</v>
@@ -43296,22 +43322,22 @@
     </row>
     <row r="24" spans="1:8" ht="51.75">
       <c r="A24" s="11" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>991</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>992</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>993</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>994</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="F24" s="11" t="s">
         <v>995</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>996</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>997</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>998</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>56</v>
@@ -43322,19 +43348,19 @@
     </row>
     <row r="25" spans="1:8" ht="51.75">
       <c r="A25" s="11" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>996</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>997</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>998</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>999</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>1002</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>457</v>
@@ -43348,22 +43374,22 @@
     </row>
     <row r="26" spans="1:8" ht="39">
       <c r="A26" s="11" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>1003</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>1004</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="F26" s="11" t="s">
         <v>1005</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>1008</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>70</v>
@@ -43374,22 +43400,22 @@
     </row>
     <row r="27" spans="1:8" ht="39">
       <c r="A27" s="11" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B27" s="11" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>1009</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="F27" s="11" t="s">
         <v>1010</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>1013</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>70</v>
@@ -43400,22 +43426,22 @@
     </row>
     <row r="28" spans="1:8" ht="51.75">
       <c r="A28" s="11" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>1014</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>1015</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="F28" s="11" t="s">
         <v>1016</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>1019</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>7</v>
@@ -43426,22 +43452,22 @@
     </row>
     <row r="29" spans="1:8" ht="51.75">
       <c r="A29" s="11" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>1021</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="F29" s="11" t="s">
         <v>1022</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>1025</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>27</v>
@@ -43452,48 +43478,48 @@
     </row>
     <row r="30" spans="1:8" ht="77.25">
       <c r="A30" s="11" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>1026</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>1027</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="F30" s="11" t="s">
         <v>1028</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>1031</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>53</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="39">
       <c r="A31" s="11" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>1033</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>1034</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="F31" s="11" t="s">
         <v>1035</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>1038</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>27</v>
@@ -43504,22 +43530,22 @@
     </row>
     <row r="32" spans="1:8" ht="39">
       <c r="A32" s="11" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>1039</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C32" s="11" t="s">
+      <c r="F32" s="11" t="s">
         <v>1040</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>1043</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>53</v>

--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehrnia\Desktop\Job\AtlasCopco\Business Analysis Project and Stakeholder Management\Excel_PLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD5C59E-FDA5-4513-9571-AEC4DFB9E4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46202E08-6134-4361-AA30-A0B7CB16795D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3434,9 +3434,6 @@
     <t>Related Stakeholders</t>
   </si>
   <si>
-    <t xml:space="preserve">Project: Multi-Site Pressure Reducing &amp; Power Generation </t>
-  </si>
-  <si>
     <t xml:space="preserve">EXECUTIVE REPORT — Full Lifecycle Delivery for Multi-Site Pressure Reducing &amp; Power Generation </t>
   </si>
   <si>
@@ -3447,6 +3444,9 @@
   </si>
   <si>
     <t>COST-BENEFIT ANALYSIS: CAPEX, OPEX, ROI &amp; IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT: Multi-Site Pressure Reducing &amp; Power Generation </t>
   </si>
 </sst>
 </file>
@@ -3667,14 +3667,6 @@
     </font>
     <font>
       <b/>
-      <sz val="22"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="26"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -3706,6 +3698,14 @@
       <b/>
       <sz val="18"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4117,9 +4117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4130,101 +4127,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4291,6 +4207,96 @@
     <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4298,15 +4304,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -15897,7 +15897,7 @@
       <c r="A1" s="21" t="s">
         <v>1046</v>
       </c>
-      <c r="B1" s="50"/>
+      <c r="B1" s="49"/>
       <c r="C1" s="13"/>
       <c r="D1" s="20"/>
       <c r="E1" s="13"/>
@@ -20751,23 +20751,23 @@
     <col min="16144" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="5" customFormat="1" ht="42">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:26" s="5" customFormat="1" ht="40.5">
+      <c r="A1" s="116" t="s">
         <v>365</v>
       </c>
-      <c r="B1" s="48">
+      <c r="B1" s="47">
         <v>41043</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="48" t="s">
         <v>281</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="48" t="s">
         <v>370</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="48" t="s">
         <v>371</v>
       </c>
       <c r="G1" s="11" t="s">
@@ -21368,7 +21368,7 @@
         <v>174</v>
       </c>
       <c r="B11" s="15">
-        <v>43546</v>
+        <v>42766</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>333</v>
@@ -21430,7 +21430,7 @@
         <v>223</v>
       </c>
       <c r="B12" s="15">
-        <v>45240</v>
+        <v>42766</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>345</v>
@@ -21492,7 +21492,7 @@
         <v>230</v>
       </c>
       <c r="B13" s="15">
-        <v>46183</v>
+        <v>42766</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>353</v>
@@ -21554,7 +21554,7 @@
         <v>249</v>
       </c>
       <c r="B14" s="15">
-        <v>46183</v>
+        <v>42766</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>353</v>
@@ -24645,18 +24645,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="59" t="s">
         <v>1044</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
@@ -28491,16 +28491,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="113" t="s">
-        <v>1121</v>
-      </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
+      <c r="A1" s="57" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
@@ -29780,14 +29780,14 @@
       <c r="R40" s="36"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="87" t="s">
+      <c r="A41" s="61" t="s">
         <v>1117</v>
       </c>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87" t="s">
+      <c r="B41" s="61"/>
+      <c r="C41" s="61" t="s">
         <v>1118</v>
       </c>
-      <c r="D41" s="87"/>
+      <c r="D41" s="61"/>
       <c r="E41" s="37" t="s">
         <v>9</v>
       </c>
@@ -29808,10 +29808,10 @@
       <c r="R41" s="41"/>
     </row>
     <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="88"/>
-      <c r="B42" s="88"/>
-      <c r="C42" s="88"/>
-      <c r="D42" s="88"/>
+      <c r="A42" s="62"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
       <c r="E42" s="42"/>
       <c r="F42" s="36"/>
       <c r="G42" s="36"/>
@@ -29900,38 +29900,38 @@
       <c r="R46" s="45"/>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="89" t="s">
+      <c r="A47" s="63" t="s">
         <v>1093</v>
       </c>
-      <c r="B47" s="90"/>
-      <c r="C47" s="95" t="s">
+      <c r="B47" s="64"/>
+      <c r="C47" s="69" t="s">
         <v>1094</v>
       </c>
-      <c r="D47" s="96"/>
-      <c r="E47" s="96"/>
-      <c r="F47" s="96"/>
-      <c r="G47" s="96"/>
-      <c r="H47" s="96"/>
-      <c r="I47" s="96"/>
-      <c r="J47" s="96"/>
-      <c r="K47" s="96"/>
-      <c r="L47" s="97"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="71"/>
       <c r="M47" s="36"/>
       <c r="N47" s="36"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="91"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="98"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="99"/>
-      <c r="I48" s="99"/>
-      <c r="J48" s="99"/>
-      <c r="K48" s="99"/>
-      <c r="L48" s="100"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73"/>
+      <c r="J48" s="73"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="74"/>
       <c r="M48" s="36"/>
       <c r="N48" s="36"/>
       <c r="O48" s="39" t="s">
@@ -29942,28 +29942,28 @@
       <c r="R48" s="41"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="91"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="101" t="s">
+      <c r="A49" s="65"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="75" t="s">
         <v>1096</v>
       </c>
-      <c r="D49" s="102"/>
-      <c r="E49" s="101" t="s">
+      <c r="D49" s="76"/>
+      <c r="E49" s="75" t="s">
         <v>1097</v>
       </c>
-      <c r="F49" s="102"/>
-      <c r="G49" s="101" t="s">
+      <c r="F49" s="76"/>
+      <c r="G49" s="75" t="s">
         <v>1098</v>
       </c>
-      <c r="H49" s="102"/>
-      <c r="I49" s="105" t="s">
+      <c r="H49" s="76"/>
+      <c r="I49" s="79" t="s">
         <v>1099</v>
       </c>
-      <c r="J49" s="106"/>
-      <c r="K49" s="101" t="s">
+      <c r="J49" s="80"/>
+      <c r="K49" s="75" t="s">
         <v>1100</v>
       </c>
-      <c r="L49" s="102"/>
+      <c r="L49" s="76"/>
       <c r="M49" s="36"/>
       <c r="N49" s="36"/>
       <c r="O49" s="46" t="s">
@@ -29974,18 +29974,18 @@
       <c r="R49" s="41"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="93"/>
-      <c r="B50" s="94"/>
-      <c r="C50" s="103"/>
-      <c r="D50" s="104"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="104"/>
-      <c r="G50" s="103"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="107"/>
-      <c r="J50" s="108"/>
-      <c r="K50" s="103"/>
-      <c r="L50" s="104"/>
+      <c r="A50" s="67"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="78"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="78"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="78"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="82"/>
+      <c r="K50" s="77"/>
+      <c r="L50" s="78"/>
       <c r="M50" s="36"/>
       <c r="N50" s="36"/>
       <c r="O50" s="46" t="s">
@@ -29996,32 +29996,32 @@
       <c r="R50" s="41"/>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="84" t="s">
+      <c r="A51" s="83" t="s">
         <v>1103</v>
       </c>
-      <c r="B51" s="75" t="s">
+      <c r="B51" s="86" t="s">
         <v>1104</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="70"/>
-      <c r="E51" s="57" t="s">
+      <c r="D51" s="90"/>
+      <c r="E51" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="58"/>
-      <c r="G51" s="63" t="s">
+      <c r="F51" s="96"/>
+      <c r="G51" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="64"/>
-      <c r="I51" s="63" t="s">
+      <c r="H51" s="102"/>
+      <c r="I51" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="64"/>
-      <c r="K51" s="63" t="s">
+      <c r="J51" s="102"/>
+      <c r="K51" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="64"/>
+      <c r="L51" s="102"/>
       <c r="M51" s="36"/>
       <c r="N51" s="36"/>
       <c r="O51" s="46" t="s">
@@ -30032,18 +30032,18 @@
       <c r="R51" s="41"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="85"/>
-      <c r="B52" s="76"/>
-      <c r="C52" s="71"/>
-      <c r="D52" s="72"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="60"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="66"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="66"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="66"/>
+      <c r="A52" s="84"/>
+      <c r="B52" s="87"/>
+      <c r="C52" s="91"/>
+      <c r="D52" s="92"/>
+      <c r="E52" s="97"/>
+      <c r="F52" s="98"/>
+      <c r="G52" s="103"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="103"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="103"/>
+      <c r="L52" s="104"/>
       <c r="M52" s="36"/>
       <c r="N52" s="36"/>
       <c r="O52" s="46" t="s">
@@ -30054,18 +30054,18 @@
       <c r="R52" s="41"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="85"/>
-      <c r="B53" s="76"/>
-      <c r="C53" s="71"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="59"/>
-      <c r="F53" s="60"/>
-      <c r="G53" s="65"/>
-      <c r="H53" s="66"/>
-      <c r="I53" s="65"/>
-      <c r="J53" s="66"/>
-      <c r="K53" s="65"/>
-      <c r="L53" s="66"/>
+      <c r="A53" s="84"/>
+      <c r="B53" s="87"/>
+      <c r="C53" s="91"/>
+      <c r="D53" s="92"/>
+      <c r="E53" s="97"/>
+      <c r="F53" s="98"/>
+      <c r="G53" s="103"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="103"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="103"/>
+      <c r="L53" s="104"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36"/>
       <c r="O53" s="43" t="s">
@@ -30076,34 +30076,34 @@
       <c r="R53" s="45"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="85"/>
-      <c r="B54" s="76"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="59"/>
-      <c r="F54" s="60"/>
-      <c r="G54" s="65"/>
-      <c r="H54" s="66"/>
-      <c r="I54" s="65"/>
-      <c r="J54" s="66"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="66"/>
+      <c r="A54" s="84"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="91"/>
+      <c r="D54" s="92"/>
+      <c r="E54" s="97"/>
+      <c r="F54" s="98"/>
+      <c r="G54" s="103"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="103"/>
+      <c r="J54" s="104"/>
+      <c r="K54" s="103"/>
+      <c r="L54" s="104"/>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="85"/>
-      <c r="B55" s="77"/>
-      <c r="C55" s="73"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="62"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="68"/>
-      <c r="I55" s="67"/>
-      <c r="J55" s="68"/>
-      <c r="K55" s="67"/>
-      <c r="L55" s="68"/>
+      <c r="A55" s="84"/>
+      <c r="B55" s="88"/>
+      <c r="C55" s="93"/>
+      <c r="D55" s="94"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="100"/>
+      <c r="G55" s="105"/>
+      <c r="H55" s="106"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="106"/>
+      <c r="K55" s="105"/>
+      <c r="L55" s="106"/>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
       <c r="O55" s="39" t="s">
@@ -30114,30 +30114,30 @@
       <c r="R55" s="41"/>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="85"/>
-      <c r="B56" s="75" t="s">
+      <c r="A56" s="84"/>
+      <c r="B56" s="86" t="s">
         <v>1109</v>
       </c>
-      <c r="C56" s="69" t="s">
+      <c r="C56" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="70"/>
-      <c r="E56" s="57" t="s">
+      <c r="D56" s="90"/>
+      <c r="E56" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="58"/>
-      <c r="G56" s="57" t="s">
+      <c r="F56" s="96"/>
+      <c r="G56" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="58"/>
-      <c r="I56" s="63" t="s">
+      <c r="H56" s="96"/>
+      <c r="I56" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="64"/>
-      <c r="K56" s="63" t="s">
+      <c r="J56" s="102"/>
+      <c r="K56" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="64"/>
+      <c r="L56" s="102"/>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
       <c r="O56" s="46" t="s">
@@ -30148,18 +30148,18 @@
       <c r="R56" s="41"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="85"/>
-      <c r="B57" s="76"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="59"/>
-      <c r="F57" s="60"/>
-      <c r="G57" s="59"/>
-      <c r="H57" s="60"/>
-      <c r="I57" s="65"/>
-      <c r="J57" s="66"/>
-      <c r="K57" s="65"/>
-      <c r="L57" s="66"/>
+      <c r="A57" s="84"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="91"/>
+      <c r="D57" s="92"/>
+      <c r="E57" s="97"/>
+      <c r="F57" s="98"/>
+      <c r="G57" s="97"/>
+      <c r="H57" s="98"/>
+      <c r="I57" s="103"/>
+      <c r="J57" s="104"/>
+      <c r="K57" s="103"/>
+      <c r="L57" s="104"/>
       <c r="M57" s="36"/>
       <c r="N57" s="36"/>
       <c r="O57" s="46" t="s">
@@ -30170,18 +30170,18 @@
       <c r="R57" s="41"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="85"/>
-      <c r="B58" s="76"/>
-      <c r="C58" s="71"/>
-      <c r="D58" s="72"/>
-      <c r="E58" s="59"/>
-      <c r="F58" s="60"/>
-      <c r="G58" s="59"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="65"/>
-      <c r="J58" s="66"/>
-      <c r="K58" s="65"/>
-      <c r="L58" s="66"/>
+      <c r="A58" s="84"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="91"/>
+      <c r="D58" s="92"/>
+      <c r="E58" s="97"/>
+      <c r="F58" s="98"/>
+      <c r="G58" s="97"/>
+      <c r="H58" s="98"/>
+      <c r="I58" s="103"/>
+      <c r="J58" s="104"/>
+      <c r="K58" s="103"/>
+      <c r="L58" s="104"/>
       <c r="M58" s="36"/>
       <c r="N58" s="36"/>
       <c r="O58" s="46" t="s">
@@ -30192,18 +30192,18 @@
       <c r="R58" s="41"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="85"/>
-      <c r="B59" s="76"/>
-      <c r="C59" s="71"/>
-      <c r="D59" s="72"/>
-      <c r="E59" s="59"/>
-      <c r="F59" s="60"/>
-      <c r="G59" s="59"/>
-      <c r="H59" s="60"/>
-      <c r="I59" s="65"/>
-      <c r="J59" s="66"/>
-      <c r="K59" s="65"/>
-      <c r="L59" s="66"/>
+      <c r="A59" s="84"/>
+      <c r="B59" s="87"/>
+      <c r="C59" s="91"/>
+      <c r="D59" s="92"/>
+      <c r="E59" s="97"/>
+      <c r="F59" s="98"/>
+      <c r="G59" s="97"/>
+      <c r="H59" s="98"/>
+      <c r="I59" s="103"/>
+      <c r="J59" s="104"/>
+      <c r="K59" s="103"/>
+      <c r="L59" s="104"/>
       <c r="M59" s="36"/>
       <c r="N59" s="36"/>
       <c r="O59" s="43" t="s">
@@ -30214,18 +30214,18 @@
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="85"/>
-      <c r="B60" s="77"/>
-      <c r="C60" s="73"/>
-      <c r="D60" s="74"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="62"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="62"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="68"/>
-      <c r="K60" s="67"/>
-      <c r="L60" s="68"/>
+      <c r="A60" s="84"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="93"/>
+      <c r="D60" s="94"/>
+      <c r="E60" s="99"/>
+      <c r="F60" s="100"/>
+      <c r="G60" s="99"/>
+      <c r="H60" s="100"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="105"/>
+      <c r="L60" s="106"/>
       <c r="M60" s="36"/>
       <c r="N60" s="36"/>
       <c r="O60" s="36"/>
@@ -30234,30 +30234,30 @@
       <c r="R60" s="36"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="85"/>
-      <c r="B61" s="75" t="s">
+      <c r="A61" s="84"/>
+      <c r="B61" s="86" t="s">
         <v>1114</v>
       </c>
-      <c r="C61" s="78" t="s">
+      <c r="C61" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="79"/>
-      <c r="E61" s="69" t="s">
+      <c r="D61" s="108"/>
+      <c r="E61" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="70"/>
-      <c r="G61" s="57" t="s">
+      <c r="F61" s="90"/>
+      <c r="G61" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="58"/>
-      <c r="I61" s="57" t="s">
+      <c r="H61" s="96"/>
+      <c r="I61" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="58"/>
-      <c r="K61" s="63" t="s">
+      <c r="J61" s="96"/>
+      <c r="K61" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="64"/>
+      <c r="L61" s="102"/>
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
       <c r="O61" s="36"/>
@@ -30266,18 +30266,18 @@
       <c r="R61" s="36"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="85"/>
-      <c r="B62" s="76"/>
-      <c r="C62" s="80"/>
-      <c r="D62" s="81"/>
-      <c r="E62" s="71"/>
-      <c r="F62" s="72"/>
-      <c r="G62" s="59"/>
-      <c r="H62" s="60"/>
-      <c r="I62" s="59"/>
-      <c r="J62" s="60"/>
-      <c r="K62" s="65"/>
-      <c r="L62" s="66"/>
+      <c r="A62" s="84"/>
+      <c r="B62" s="87"/>
+      <c r="C62" s="109"/>
+      <c r="D62" s="110"/>
+      <c r="E62" s="91"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="97"/>
+      <c r="H62" s="98"/>
+      <c r="I62" s="97"/>
+      <c r="J62" s="98"/>
+      <c r="K62" s="103"/>
+      <c r="L62" s="104"/>
       <c r="M62" s="36"/>
       <c r="N62" s="36"/>
       <c r="O62" s="36"/>
@@ -30286,18 +30286,18 @@
       <c r="R62" s="36"/>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="85"/>
-      <c r="B63" s="76"/>
-      <c r="C63" s="80"/>
-      <c r="D63" s="81"/>
-      <c r="E63" s="71"/>
-      <c r="F63" s="72"/>
-      <c r="G63" s="59"/>
-      <c r="H63" s="60"/>
-      <c r="I63" s="59"/>
-      <c r="J63" s="60"/>
-      <c r="K63" s="65"/>
-      <c r="L63" s="66"/>
+      <c r="A63" s="84"/>
+      <c r="B63" s="87"/>
+      <c r="C63" s="109"/>
+      <c r="D63" s="110"/>
+      <c r="E63" s="91"/>
+      <c r="F63" s="92"/>
+      <c r="G63" s="97"/>
+      <c r="H63" s="98"/>
+      <c r="I63" s="97"/>
+      <c r="J63" s="98"/>
+      <c r="K63" s="103"/>
+      <c r="L63" s="104"/>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
       <c r="O63" s="36"/>
@@ -30306,18 +30306,18 @@
       <c r="R63" s="36"/>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="85"/>
-      <c r="B64" s="76"/>
-      <c r="C64" s="80"/>
-      <c r="D64" s="81"/>
-      <c r="E64" s="71"/>
-      <c r="F64" s="72"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="60"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="60"/>
-      <c r="K64" s="65"/>
-      <c r="L64" s="66"/>
+      <c r="A64" s="84"/>
+      <c r="B64" s="87"/>
+      <c r="C64" s="109"/>
+      <c r="D64" s="110"/>
+      <c r="E64" s="91"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="97"/>
+      <c r="H64" s="98"/>
+      <c r="I64" s="97"/>
+      <c r="J64" s="98"/>
+      <c r="K64" s="103"/>
+      <c r="L64" s="104"/>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
       <c r="O64" s="36"/>
@@ -30326,18 +30326,18 @@
       <c r="R64" s="36"/>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="85"/>
-      <c r="B65" s="77"/>
-      <c r="C65" s="82"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="73"/>
-      <c r="F65" s="74"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="62"/>
-      <c r="I65" s="61"/>
-      <c r="J65" s="62"/>
-      <c r="K65" s="67"/>
-      <c r="L65" s="68"/>
+      <c r="A65" s="84"/>
+      <c r="B65" s="88"/>
+      <c r="C65" s="111"/>
+      <c r="D65" s="112"/>
+      <c r="E65" s="93"/>
+      <c r="F65" s="94"/>
+      <c r="G65" s="99"/>
+      <c r="H65" s="100"/>
+      <c r="I65" s="99"/>
+      <c r="J65" s="100"/>
+      <c r="K65" s="105"/>
+      <c r="L65" s="106"/>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
       <c r="O65" s="36"/>
@@ -30346,30 +30346,30 @@
       <c r="R65" s="36"/>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="85"/>
-      <c r="B66" s="75" t="s">
+      <c r="A66" s="84"/>
+      <c r="B66" s="86" t="s">
         <v>1115</v>
       </c>
-      <c r="C66" s="78" t="s">
+      <c r="C66" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="79"/>
-      <c r="E66" s="78" t="s">
+      <c r="D66" s="108"/>
+      <c r="E66" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="79"/>
-      <c r="G66" s="69" t="s">
+      <c r="F66" s="108"/>
+      <c r="G66" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="70"/>
-      <c r="I66" s="69" t="s">
+      <c r="H66" s="90"/>
+      <c r="I66" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="70"/>
-      <c r="K66" s="57" t="s">
+      <c r="J66" s="90"/>
+      <c r="K66" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="58"/>
+      <c r="L66" s="96"/>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
       <c r="O66" s="36"/>
@@ -30378,18 +30378,18 @@
       <c r="R66" s="36"/>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="85"/>
-      <c r="B67" s="76"/>
-      <c r="C67" s="80"/>
-      <c r="D67" s="81"/>
-      <c r="E67" s="80"/>
-      <c r="F67" s="81"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="72"/>
-      <c r="I67" s="71"/>
-      <c r="J67" s="72"/>
-      <c r="K67" s="59"/>
-      <c r="L67" s="60"/>
+      <c r="A67" s="84"/>
+      <c r="B67" s="87"/>
+      <c r="C67" s="109"/>
+      <c r="D67" s="110"/>
+      <c r="E67" s="109"/>
+      <c r="F67" s="110"/>
+      <c r="G67" s="91"/>
+      <c r="H67" s="92"/>
+      <c r="I67" s="91"/>
+      <c r="J67" s="92"/>
+      <c r="K67" s="97"/>
+      <c r="L67" s="98"/>
       <c r="M67" s="36"/>
       <c r="N67" s="36"/>
       <c r="O67" s="36"/>
@@ -30398,18 +30398,18 @@
       <c r="R67" s="36"/>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="85"/>
-      <c r="B68" s="76"/>
-      <c r="C68" s="80"/>
-      <c r="D68" s="81"/>
-      <c r="E68" s="80"/>
-      <c r="F68" s="81"/>
-      <c r="G68" s="71"/>
-      <c r="H68" s="72"/>
-      <c r="I68" s="71"/>
-      <c r="J68" s="72"/>
-      <c r="K68" s="59"/>
-      <c r="L68" s="60"/>
+      <c r="A68" s="84"/>
+      <c r="B68" s="87"/>
+      <c r="C68" s="109"/>
+      <c r="D68" s="110"/>
+      <c r="E68" s="109"/>
+      <c r="F68" s="110"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="92"/>
+      <c r="I68" s="91"/>
+      <c r="J68" s="92"/>
+      <c r="K68" s="97"/>
+      <c r="L68" s="98"/>
       <c r="M68" s="36"/>
       <c r="N68" s="36"/>
       <c r="O68" s="36"/>
@@ -30418,18 +30418,18 @@
       <c r="R68" s="36"/>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="85"/>
-      <c r="B69" s="76"/>
-      <c r="C69" s="80"/>
-      <c r="D69" s="81"/>
-      <c r="E69" s="80"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="71"/>
-      <c r="H69" s="72"/>
-      <c r="I69" s="71"/>
-      <c r="J69" s="72"/>
-      <c r="K69" s="59"/>
-      <c r="L69" s="60"/>
+      <c r="A69" s="84"/>
+      <c r="B69" s="87"/>
+      <c r="C69" s="109"/>
+      <c r="D69" s="110"/>
+      <c r="E69" s="109"/>
+      <c r="F69" s="110"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="92"/>
+      <c r="I69" s="91"/>
+      <c r="J69" s="92"/>
+      <c r="K69" s="97"/>
+      <c r="L69" s="98"/>
       <c r="M69" s="36"/>
       <c r="N69" s="36"/>
       <c r="O69" s="36"/>
@@ -30438,18 +30438,18 @@
       <c r="R69" s="36"/>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="85"/>
-      <c r="B70" s="77"/>
-      <c r="C70" s="82"/>
-      <c r="D70" s="83"/>
-      <c r="E70" s="82"/>
-      <c r="F70" s="83"/>
-      <c r="G70" s="73"/>
-      <c r="H70" s="74"/>
-      <c r="I70" s="73"/>
-      <c r="J70" s="74"/>
-      <c r="K70" s="61"/>
-      <c r="L70" s="62"/>
+      <c r="A70" s="84"/>
+      <c r="B70" s="88"/>
+      <c r="C70" s="111"/>
+      <c r="D70" s="112"/>
+      <c r="E70" s="111"/>
+      <c r="F70" s="112"/>
+      <c r="G70" s="93"/>
+      <c r="H70" s="94"/>
+      <c r="I70" s="93"/>
+      <c r="J70" s="94"/>
+      <c r="K70" s="99"/>
+      <c r="L70" s="100"/>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="36"/>
@@ -30458,30 +30458,30 @@
       <c r="R70" s="36"/>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="85"/>
-      <c r="B71" s="75" t="s">
+      <c r="A71" s="84"/>
+      <c r="B71" s="86" t="s">
         <v>1116</v>
       </c>
-      <c r="C71" s="78" t="s">
+      <c r="C71" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="79"/>
-      <c r="E71" s="78" t="s">
+      <c r="D71" s="108"/>
+      <c r="E71" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="79"/>
-      <c r="G71" s="78" t="s">
+      <c r="F71" s="108"/>
+      <c r="G71" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="H71" s="79"/>
-      <c r="I71" s="78" t="s">
+      <c r="H71" s="108"/>
+      <c r="I71" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="79"/>
-      <c r="K71" s="69" t="s">
+      <c r="J71" s="108"/>
+      <c r="K71" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="70"/>
+      <c r="L71" s="90"/>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="36"/>
@@ -30490,18 +30490,18 @@
       <c r="R71" s="36"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="85"/>
-      <c r="B72" s="76"/>
-      <c r="C72" s="80"/>
-      <c r="D72" s="81"/>
-      <c r="E72" s="80"/>
-      <c r="F72" s="81"/>
-      <c r="G72" s="80"/>
-      <c r="H72" s="81"/>
-      <c r="I72" s="80"/>
-      <c r="J72" s="81"/>
-      <c r="K72" s="71"/>
-      <c r="L72" s="72"/>
+      <c r="A72" s="84"/>
+      <c r="B72" s="87"/>
+      <c r="C72" s="109"/>
+      <c r="D72" s="110"/>
+      <c r="E72" s="109"/>
+      <c r="F72" s="110"/>
+      <c r="G72" s="109"/>
+      <c r="H72" s="110"/>
+      <c r="I72" s="109"/>
+      <c r="J72" s="110"/>
+      <c r="K72" s="91"/>
+      <c r="L72" s="92"/>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="36"/>
@@ -30510,18 +30510,18 @@
       <c r="R72" s="36"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="85"/>
-      <c r="B73" s="76"/>
-      <c r="C73" s="80"/>
-      <c r="D73" s="81"/>
-      <c r="E73" s="80"/>
-      <c r="F73" s="81"/>
-      <c r="G73" s="80"/>
-      <c r="H73" s="81"/>
-      <c r="I73" s="80"/>
-      <c r="J73" s="81"/>
-      <c r="K73" s="71"/>
-      <c r="L73" s="72"/>
+      <c r="A73" s="84"/>
+      <c r="B73" s="87"/>
+      <c r="C73" s="109"/>
+      <c r="D73" s="110"/>
+      <c r="E73" s="109"/>
+      <c r="F73" s="110"/>
+      <c r="G73" s="109"/>
+      <c r="H73" s="110"/>
+      <c r="I73" s="109"/>
+      <c r="J73" s="110"/>
+      <c r="K73" s="91"/>
+      <c r="L73" s="92"/>
       <c r="M73" s="36"/>
       <c r="N73" s="36"/>
       <c r="O73" s="36"/>
@@ -30530,18 +30530,18 @@
       <c r="R73" s="36"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="85"/>
-      <c r="B74" s="76"/>
-      <c r="C74" s="80"/>
-      <c r="D74" s="81"/>
-      <c r="E74" s="80"/>
-      <c r="F74" s="81"/>
-      <c r="G74" s="80"/>
-      <c r="H74" s="81"/>
-      <c r="I74" s="80"/>
-      <c r="J74" s="81"/>
-      <c r="K74" s="71"/>
-      <c r="L74" s="72"/>
+      <c r="A74" s="84"/>
+      <c r="B74" s="87"/>
+      <c r="C74" s="109"/>
+      <c r="D74" s="110"/>
+      <c r="E74" s="109"/>
+      <c r="F74" s="110"/>
+      <c r="G74" s="109"/>
+      <c r="H74" s="110"/>
+      <c r="I74" s="109"/>
+      <c r="J74" s="110"/>
+      <c r="K74" s="91"/>
+      <c r="L74" s="92"/>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="36"/>
@@ -30550,18 +30550,18 @@
       <c r="R74" s="36"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="86"/>
-      <c r="B75" s="77"/>
-      <c r="C75" s="82"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="82"/>
-      <c r="F75" s="83"/>
-      <c r="G75" s="82"/>
-      <c r="H75" s="83"/>
-      <c r="I75" s="82"/>
-      <c r="J75" s="83"/>
-      <c r="K75" s="73"/>
-      <c r="L75" s="74"/>
+      <c r="A75" s="85"/>
+      <c r="B75" s="88"/>
+      <c r="C75" s="111"/>
+      <c r="D75" s="112"/>
+      <c r="E75" s="111"/>
+      <c r="F75" s="112"/>
+      <c r="G75" s="111"/>
+      <c r="H75" s="112"/>
+      <c r="I75" s="111"/>
+      <c r="J75" s="112"/>
+      <c r="K75" s="93"/>
+      <c r="L75" s="94"/>
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="36"/>
@@ -30591,34 +30591,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A47:B50"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
-    <mergeCell ref="A51:A75"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:D55"/>
-    <mergeCell ref="E51:F55"/>
-    <mergeCell ref="G51:H55"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:D65"/>
-    <mergeCell ref="E61:F65"/>
-    <mergeCell ref="G61:H65"/>
-    <mergeCell ref="I51:J55"/>
-    <mergeCell ref="K51:L55"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:D60"/>
-    <mergeCell ref="E56:F60"/>
-    <mergeCell ref="G56:H60"/>
-    <mergeCell ref="I56:J60"/>
-    <mergeCell ref="K56:L60"/>
     <mergeCell ref="I61:J65"/>
     <mergeCell ref="K61:L65"/>
     <mergeCell ref="K71:L75"/>
@@ -30633,6 +30605,34 @@
     <mergeCell ref="E71:F75"/>
     <mergeCell ref="G71:H75"/>
     <mergeCell ref="I71:J75"/>
+    <mergeCell ref="I51:J55"/>
+    <mergeCell ref="K51:L55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:D60"/>
+    <mergeCell ref="E56:F60"/>
+    <mergeCell ref="G56:H60"/>
+    <mergeCell ref="I56:J60"/>
+    <mergeCell ref="K56:L60"/>
+    <mergeCell ref="A51:A75"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:D55"/>
+    <mergeCell ref="E51:F55"/>
+    <mergeCell ref="G51:H55"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:D65"/>
+    <mergeCell ref="E61:F65"/>
+    <mergeCell ref="G61:H65"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A47:B50"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30653,16 +30653,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" s="1" customFormat="1" ht="33.75">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="51" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="55" t="s">
         <v>1123</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="56" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
@@ -30783,22 +30783,22 @@
       <c r="BI2"/>
     </row>
     <row r="3" spans="1:61">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="50" t="s">
         <v>677</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="50" t="s">
         <v>678</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="50" t="s">
         <v>8</v>
       </c>
       <c r="G3"/>
@@ -30858,7 +30858,7 @@
       <c r="BI3"/>
     </row>
     <row r="4" spans="1:61" ht="15.75">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="53" t="s">
         <v>679</v>
       </c>
       <c r="B4">
@@ -30933,7 +30933,7 @@
       <c r="BI4"/>
     </row>
     <row r="5" spans="1:61" ht="15.75">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="53" t="s">
         <v>682</v>
       </c>
       <c r="B5">
@@ -31008,7 +31008,7 @@
       <c r="BI5"/>
     </row>
     <row r="6" spans="1:61" ht="15.75" hidden="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="53" t="s">
         <v>684</v>
       </c>
       <c r="B6">
@@ -31083,7 +31083,7 @@
       <c r="BI6"/>
     </row>
     <row r="7" spans="1:61" ht="15.75" hidden="1">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="53" t="s">
         <v>686</v>
       </c>
       <c r="B7">
@@ -31158,7 +31158,7 @@
       <c r="BI7"/>
     </row>
     <row r="8" spans="1:61" ht="15.75" hidden="1">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>688</v>
       </c>
       <c r="B8">
@@ -31233,7 +31233,7 @@
       <c r="BI8"/>
     </row>
     <row r="9" spans="1:61" ht="15.75" hidden="1">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="53" t="s">
         <v>690</v>
       </c>
       <c r="B9">
@@ -31308,7 +31308,7 @@
       <c r="BI9"/>
     </row>
     <row r="10" spans="1:61" ht="15.75" hidden="1">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="53" t="s">
         <v>693</v>
       </c>
       <c r="B10">
@@ -31383,7 +31383,7 @@
       <c r="BI10"/>
     </row>
     <row r="11" spans="1:61" ht="15.75" hidden="1">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="53" t="s">
         <v>696</v>
       </c>
       <c r="B11">
@@ -31458,7 +31458,7 @@
       <c r="BI11"/>
     </row>
     <row r="12" spans="1:61" ht="15.75" hidden="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="53" t="s">
         <v>698</v>
       </c>
       <c r="B12">
@@ -31533,7 +31533,7 @@
       <c r="BI12"/>
     </row>
     <row r="13" spans="1:61" ht="15.75" hidden="1">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="53" t="s">
         <v>700</v>
       </c>
       <c r="B13">
@@ -31608,7 +31608,7 @@
       <c r="BI13"/>
     </row>
     <row r="14" spans="1:61" ht="15.75" hidden="1">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="53" t="s">
         <v>702</v>
       </c>
       <c r="B14">
@@ -31684,7 +31684,7 @@
       <c r="BI14"/>
     </row>
     <row r="15" spans="1:61" s="4" customFormat="1" ht="15.75" hidden="1">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="53" t="s">
         <v>704</v>
       </c>
       <c r="B15">
@@ -31759,7 +31759,7 @@
       <c r="BI15"/>
     </row>
     <row r="16" spans="1:61" ht="15.75" hidden="1">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="53" t="s">
         <v>706</v>
       </c>
       <c r="B16">
@@ -31834,7 +31834,7 @@
       <c r="BI16"/>
     </row>
     <row r="17" spans="1:61" ht="15.75" hidden="1">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="53" t="s">
         <v>708</v>
       </c>
       <c r="B17">
@@ -31909,7 +31909,7 @@
       <c r="BI17"/>
     </row>
     <row r="18" spans="1:61" ht="15.75">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="53" t="s">
         <v>710</v>
       </c>
       <c r="B18">
@@ -31984,7 +31984,7 @@
       <c r="BI18"/>
     </row>
     <row r="19" spans="1:61" ht="15.75">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="53" t="s">
         <v>713</v>
       </c>
       <c r="B19">
@@ -32059,7 +32059,7 @@
       <c r="BI19"/>
     </row>
     <row r="20" spans="1:61" ht="15.75" hidden="1">
-      <c r="A20" s="54"/>
+      <c r="A20" s="53"/>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -32122,7 +32122,7 @@
       <c r="BI20"/>
     </row>
     <row r="21" spans="1:61" ht="15.75" hidden="1">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="53" t="s">
         <v>716</v>
       </c>
       <c r="B21" t="s">
@@ -32197,7 +32197,7 @@
       <c r="BI21"/>
     </row>
     <row r="22" spans="1:61" ht="15.75">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="53" t="s">
         <v>719</v>
       </c>
       <c r="B22">
@@ -32273,7 +32273,7 @@
       <c r="BI22"/>
     </row>
     <row r="23" spans="1:61" ht="15.75">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="53" t="s">
         <v>721</v>
       </c>
       <c r="B23">
@@ -32349,7 +32349,7 @@
       <c r="BI23"/>
     </row>
     <row r="24" spans="1:61" ht="15.75">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="53" t="s">
         <v>724</v>
       </c>
       <c r="B24">
@@ -32425,7 +32425,7 @@
       <c r="BI24"/>
     </row>
     <row r="25" spans="1:61" ht="15.75">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="53" t="s">
         <v>726</v>
       </c>
       <c r="B25">
@@ -32501,7 +32501,7 @@
       <c r="BI25"/>
     </row>
     <row r="26" spans="1:61" ht="15.75">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="53" t="s">
         <v>728</v>
       </c>
       <c r="B26">
@@ -32577,7 +32577,7 @@
       <c r="BI26"/>
     </row>
     <row r="27" spans="1:61" ht="15.75">
-      <c r="A27" s="54" t="s">
+      <c r="A27" s="53" t="s">
         <v>730</v>
       </c>
       <c r="B27">
@@ -32653,7 +32653,7 @@
       <c r="BI27"/>
     </row>
     <row r="28" spans="1:61" ht="15.75">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="53" t="s">
         <v>22</v>
       </c>
       <c r="B28">
@@ -32729,7 +32729,7 @@
       <c r="BI28"/>
     </row>
     <row r="29" spans="1:61" ht="15.75">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="54" t="s">
         <v>246</v>
       </c>
       <c r="B29">
@@ -32804,7 +32804,7 @@
       <c r="BI29"/>
     </row>
     <row r="30" spans="1:61" ht="15.75">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="53" t="s">
         <v>735</v>
       </c>
       <c r="B30">
@@ -32880,7 +32880,7 @@
       <c r="BI30"/>
     </row>
     <row r="31" spans="1:61" ht="15.75">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="53" t="s">
         <v>737</v>
       </c>
       <c r="B31" s="16">
@@ -32956,7 +32956,7 @@
       <c r="BI31"/>
     </row>
     <row r="32" spans="1:61" ht="15.75">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="53" t="s">
         <v>740</v>
       </c>
       <c r="B32" t="str">
@@ -33032,7 +33032,7 @@
       <c r="BI32"/>
     </row>
     <row r="33" spans="1:61" ht="15.75">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="53" t="s">
         <v>743</v>
       </c>
       <c r="B33" t="str">
@@ -33108,7 +33108,7 @@
       <c r="BI33"/>
     </row>
     <row r="34" spans="1:61" ht="15.75">
-      <c r="A34" s="54"/>
+      <c r="A34" s="53"/>
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -33171,7 +33171,7 @@
       <c r="BI34"/>
     </row>
     <row r="35" spans="1:61" ht="15.75">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="53" t="s">
         <v>746</v>
       </c>
       <c r="B35">
@@ -33258,7 +33258,7 @@
       <c r="BI35"/>
     </row>
     <row r="36" spans="1:61" ht="15.75">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="53" t="s">
         <v>747</v>
       </c>
       <c r="B36">
@@ -33356,7 +33356,7 @@
       <c r="BI36"/>
     </row>
     <row r="37" spans="1:61" ht="15.75">
-      <c r="A37" s="54"/>
+      <c r="A37" s="53"/>
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -33419,7 +33419,7 @@
       <c r="BI37"/>
     </row>
     <row r="38" spans="1:61" ht="15.75">
-      <c r="A38" s="54"/>
+      <c r="A38" s="53"/>
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -33482,7 +33482,7 @@
       <c r="BI38"/>
     </row>
     <row r="39" spans="1:61" ht="15.75">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="53" t="s">
         <v>748</v>
       </c>
       <c r="B39" t="s">
@@ -33557,7 +33557,7 @@
       <c r="BI39"/>
     </row>
     <row r="40" spans="1:61" ht="15.75">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="53" t="s">
         <v>752</v>
       </c>
       <c r="B40">
@@ -33632,7 +33632,7 @@
       <c r="BI40"/>
     </row>
     <row r="41" spans="1:61" ht="15.75">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="53" t="s">
         <v>754</v>
       </c>
       <c r="B41">
@@ -33707,7 +33707,7 @@
       <c r="BI41"/>
     </row>
     <row r="42" spans="1:61" ht="15.75">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="53" t="s">
         <v>756</v>
       </c>
       <c r="B42">
@@ -33785,7 +33785,7 @@
       <c r="BI42"/>
     </row>
     <row r="43" spans="1:61" ht="15.75">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="53" t="s">
         <v>758</v>
       </c>
       <c r="B43">
@@ -33863,7 +33863,7 @@
       <c r="BI43"/>
     </row>
     <row r="44" spans="1:61" ht="15.75">
-      <c r="A44" s="54" t="s">
+      <c r="A44" s="53" t="s">
         <v>760</v>
       </c>
       <c r="B44" t="s">
@@ -41268,10 +41268,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75">
-      <c r="A1" s="116" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B1" s="116"/>
+      <c r="A1" s="60" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B1" s="60"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="19" t="s">
@@ -42008,30 +42008,30 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="21">
-      <c r="A33" s="109" t="s">
+      <c r="A33" s="113" t="s">
         <v>1047</v>
       </c>
-      <c r="B33" s="110"/>
-      <c r="C33" s="110"/>
-      <c r="D33" s="110"/>
-      <c r="E33" s="110"/>
-      <c r="F33" s="110"/>
-      <c r="G33" s="110"/>
-      <c r="H33" s="110"/>
-      <c r="I33" s="110"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="114"/>
+      <c r="E33" s="114"/>
+      <c r="F33" s="114"/>
+      <c r="G33" s="114"/>
+      <c r="H33" s="114"/>
+      <c r="I33" s="114"/>
     </row>
     <row r="35" spans="1:9" ht="15.75">
-      <c r="A35" s="111" t="s">
+      <c r="A35" s="115" t="s">
         <v>1048</v>
       </c>
-      <c r="B35" s="110"/>
-      <c r="C35" s="110"/>
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
-      <c r="F35" s="110"/>
-      <c r="G35" s="110"/>
-      <c r="H35" s="110"/>
-      <c r="I35" s="110"/>
+      <c r="B35" s="114"/>
+      <c r="C35" s="114"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="114"/>
+      <c r="G35" s="114"/>
+      <c r="H35" s="114"/>
+      <c r="I35" s="114"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="22" t="s">
@@ -42484,11 +42484,11 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75">
-      <c r="A52" s="111" t="s">
+      <c r="A52" s="115" t="s">
         <v>1071</v>
       </c>
-      <c r="B52" s="110"/>
-      <c r="C52" s="110"/>
+      <c r="B52" s="114"/>
+      <c r="C52" s="114"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="22" t="s">
@@ -42586,11 +42586,11 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.75">
-      <c r="A63" s="111" t="s">
+      <c r="A63" s="115" t="s">
         <v>1081</v>
       </c>
-      <c r="B63" s="110"/>
-      <c r="C63" s="110"/>
+      <c r="B63" s="114"/>
+      <c r="C63" s="114"/>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="22" t="s">
@@ -42754,7 +42754,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="37.5">
       <c r="A1" s="13" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>

--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehrnia\Desktop\Job\AtlasCopco\Business Analysis Project and Stakeholder Management\Excel_PLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46202E08-6134-4361-AA30-A0B7CB16795D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CC2D02-1BB8-42F2-911C-FE1289BF981D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents Management" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,13 @@
     <sheet name="Change Management (ECN)" sheetId="11" r:id="rId4"/>
     <sheet name="Validation &amp; Release Management" sheetId="13" r:id="rId5"/>
     <sheet name="Risk Management" sheetId="12" r:id="rId6"/>
-    <sheet name="Cost Benefit Analysis" sheetId="10" r:id="rId7"/>
+    <sheet name="Financial Evaluation" sheetId="10" r:id="rId7"/>
     <sheet name="Dashboard" sheetId="9" r:id="rId8"/>
     <sheet name="Executive Report" sheetId="14" r:id="rId9"/>
+    <sheet name="Read.me" sheetId="15" r:id="rId10"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
     <definedName name="_Toc11120784" localSheetId="0">'Documents Management'!$A$3</definedName>
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="1129">
   <si>
     <t>Description</t>
   </si>
@@ -3447,6 +3448,21 @@
   </si>
   <si>
     <t xml:space="preserve">PROJECT: Multi-Site Pressure Reducing &amp; Power Generation </t>
+  </si>
+  <si>
+    <t>PLM-Enabled Process Alignment</t>
+  </si>
+  <si>
+    <t>CONFIDENTIALITY NOTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This document contains sections of the Multi-Site Pressure Reducing &amp; Power Generation project. </t>
+  </si>
+  <si>
+    <t>For data protection reasons, certain project details have been omitted. Readers are strictly prohibited from using or</t>
+  </si>
+  <si>
+    <t>reproducing this data without prior written permission.</t>
   </si>
 </sst>
 </file>
@@ -3460,7 +3476,7 @@
     <numFmt numFmtId="166" formatCode="\$#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3710,8 +3726,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3813,6 +3858,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4017,7 +4068,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -4141,6 +4192,99 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4207,96 +4351,6 @@
     <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4304,9 +4358,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -7596,6 +7657,811 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>75962</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18586</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06232614-F908-4C10-E469-7BF70592FFD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2209800"/>
+          <a:ext cx="1904762" cy="3714286"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>28576</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>120739</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15F92EE9-0E03-C798-07ED-347C52072153}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1876426" y="2143125"/>
+          <a:ext cx="7296150" cy="3692614"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr lvl="0">
+            <a:defRPr lang="de-DE"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" lvl="1" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="432008" lvl="2" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="864017" lvl="3" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1296025" lvl="4" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1728033" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2160041" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2592050" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3024058" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3456066" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="180975" indent="-180975" algn="just">
+            <a:buFont typeface="+mj-lt"/>
+            <a:buAutoNum type="romanLcPeriod"/>
+            <a:tabLst>
+              <a:tab pos="180975" algn="l"/>
+            </a:tabLst>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Requirements Definition, Technical Feasibility &amp; Candidate Selection </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="just"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Processed site-specific flow and pressure data, urban consumption profiles, and physical space constraints to screen and rank all candidate stations for optimal energy recovery</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="just"/>
+          <a:endParaRPr lang="en-GB" sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="265113" indent="-265113" algn="just">
+            <a:buFont typeface="+mj-lt"/>
+            <a:buAutoNum type="romanLcPeriod" startAt="2"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Lifecycle Cost Analysis &amp; Financial Gate</a:t>
+          </a:r>
+          <a:endParaRPr lang="fa-IR" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="just"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Developed detailed CapEx and OpEx models to conduct precise ROI evaluations, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>as a </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>financial gate before moving into execution</a:t>
+          </a:r>
+          <a:endParaRPr lang="fa-IR" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="just"/>
+          <a:endParaRPr lang="fa-IR" sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="265113" indent="-265113" algn="just">
+            <a:buFont typeface="+mj-lt"/>
+            <a:buAutoNum type="romanLcPeriod" startAt="3"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Configuration, Change Management &amp; Design Validation</a:t>
+          </a:r>
+          <a:endParaRPr lang="fa-IR" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="just"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Enforced requirements traceability and engineering change management within the PLM workflow, followed by formal technical reviews to validate the final design</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="just"/>
+          <a:endParaRPr lang="en-GB" sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="265113" indent="-265113" algn="just">
+            <a:buFont typeface="+mj-lt"/>
+            <a:buAutoNum type="romanLcPeriod" startAt="4"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Aftermarket Engineering &amp; Field Feedback</a:t>
+          </a:r>
+          <a:endParaRPr lang="de-DE" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="182563" indent="-182563" algn="just">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="§"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>eployed optimized Cr-Ni-based alloy coatings to mitigate corrosion risks and ensure a product lifecycle exceeding 10 years</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="182563" indent="-182563" algn="just">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="§"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Transitioned core engineering data into operations for preventive maintenance, while cycling field reliability and failure data back into the PLM workflow</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>122705</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>168344</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>66680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E3D15A8-49CB-35B2-2057-F2C162EE9B3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9266705" y="1181100"/>
+          <a:ext cx="5532039" cy="3267080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>9202</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>355599</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>148902</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="table">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBB8615E-7A4F-04DD-4A80-66B64C859756}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9134475" y="4390702"/>
+          <a:ext cx="7680324" cy="1854200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>592454</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>40377</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1E2CA65-D289-4608-9A31-13DF296835BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1819275" y="1152525"/>
+          <a:ext cx="7307579" cy="992877"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx2">
+              <a:lumMod val="95000"/>
+              <a:lumOff val="5000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="72000" tIns="72000" rIns="72000" bIns="72000" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr lvl="0">
+            <a:defRPr lang="de-DE"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" lvl="1" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="432008" lvl="2" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="864017" lvl="3" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1296025" lvl="4" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1728033" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2160041" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2592050" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3024058" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3456066" algn="l" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1701" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Full Lifecycle Delivery </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1800" b="1" i="0">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Project Proposal → Design → Validation &amp; Testing → Commissioning → O&amp;M</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr" defTabSz="864017" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="200"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1200" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Under stage-gate governance</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>490325</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{164172CB-4ACF-EF6E-0A1F-E54DC1B11E6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="276225" y="800100"/>
+          <a:ext cx="1433300" cy="1428750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -11951,6 +12817,106 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C298399-6CA6-4D49-BB8B-AFA2834BF9AF}">
+  <dimension ref="A1:Y4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="45">
+      <c r="A1" s="117" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="119" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="15.75">
+      <c r="A2" s="120" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="121"/>
+      <c r="M2" s="122" t="s">
+        <v>1126</v>
+      </c>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="122"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="118"/>
+      <c r="Y2" s="118"/>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="M3" s="122" t="s">
+        <v>1127</v>
+      </c>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="122"/>
+      <c r="U3" s="122"/>
+      <c r="V3" s="122"/>
+      <c r="W3" s="122"/>
+      <c r="X3" s="118"/>
+      <c r="Y3" s="118"/>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="M4" s="122" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="M2:W2"/>
+    <mergeCell ref="M3:W3"/>
+    <mergeCell ref="M4:W4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -20752,7 +21718,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="5" customFormat="1" ht="40.5">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="61" t="s">
         <v>365</v>
       </c>
       <c r="B1" s="47">
@@ -29780,14 +30746,14 @@
       <c r="R40" s="36"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="61" t="s">
+      <c r="A41" s="92" t="s">
         <v>1117</v>
       </c>
-      <c r="B41" s="61"/>
-      <c r="C41" s="61" t="s">
+      <c r="B41" s="92"/>
+      <c r="C41" s="92" t="s">
         <v>1118</v>
       </c>
-      <c r="D41" s="61"/>
+      <c r="D41" s="92"/>
       <c r="E41" s="37" t="s">
         <v>9</v>
       </c>
@@ -29808,10 +30774,10 @@
       <c r="R41" s="41"/>
     </row>
     <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="62"/>
-      <c r="B42" s="62"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
+      <c r="A42" s="93"/>
+      <c r="B42" s="93"/>
+      <c r="C42" s="93"/>
+      <c r="D42" s="93"/>
       <c r="E42" s="42"/>
       <c r="F42" s="36"/>
       <c r="G42" s="36"/>
@@ -29900,38 +30866,38 @@
       <c r="R46" s="45"/>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="63" t="s">
+      <c r="A47" s="94" t="s">
         <v>1093</v>
       </c>
-      <c r="B47" s="64"/>
-      <c r="C47" s="69" t="s">
+      <c r="B47" s="95"/>
+      <c r="C47" s="100" t="s">
         <v>1094</v>
       </c>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="70"/>
-      <c r="K47" s="70"/>
-      <c r="L47" s="71"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="101"/>
+      <c r="F47" s="101"/>
+      <c r="G47" s="101"/>
+      <c r="H47" s="101"/>
+      <c r="I47" s="101"/>
+      <c r="J47" s="101"/>
+      <c r="K47" s="101"/>
+      <c r="L47" s="102"/>
       <c r="M47" s="36"/>
       <c r="N47" s="36"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="65"/>
-      <c r="B48" s="66"/>
-      <c r="C48" s="72"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
-      <c r="K48" s="73"/>
-      <c r="L48" s="74"/>
+      <c r="A48" s="96"/>
+      <c r="B48" s="97"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="104"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="104"/>
+      <c r="K48" s="104"/>
+      <c r="L48" s="105"/>
       <c r="M48" s="36"/>
       <c r="N48" s="36"/>
       <c r="O48" s="39" t="s">
@@ -29942,28 +30908,28 @@
       <c r="R48" s="41"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="65"/>
-      <c r="B49" s="66"/>
-      <c r="C49" s="75" t="s">
+      <c r="A49" s="96"/>
+      <c r="B49" s="97"/>
+      <c r="C49" s="106" t="s">
         <v>1096</v>
       </c>
-      <c r="D49" s="76"/>
-      <c r="E49" s="75" t="s">
+      <c r="D49" s="107"/>
+      <c r="E49" s="106" t="s">
         <v>1097</v>
       </c>
-      <c r="F49" s="76"/>
-      <c r="G49" s="75" t="s">
+      <c r="F49" s="107"/>
+      <c r="G49" s="106" t="s">
         <v>1098</v>
       </c>
-      <c r="H49" s="76"/>
-      <c r="I49" s="79" t="s">
+      <c r="H49" s="107"/>
+      <c r="I49" s="110" t="s">
         <v>1099</v>
       </c>
-      <c r="J49" s="80"/>
-      <c r="K49" s="75" t="s">
+      <c r="J49" s="111"/>
+      <c r="K49" s="106" t="s">
         <v>1100</v>
       </c>
-      <c r="L49" s="76"/>
+      <c r="L49" s="107"/>
       <c r="M49" s="36"/>
       <c r="N49" s="36"/>
       <c r="O49" s="46" t="s">
@@ -29974,18 +30940,18 @@
       <c r="R49" s="41"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="67"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="77"/>
-      <c r="D50" s="78"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="78"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="82"/>
-      <c r="K50" s="77"/>
-      <c r="L50" s="78"/>
+      <c r="A50" s="98"/>
+      <c r="B50" s="99"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="109"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="109"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="109"/>
+      <c r="I50" s="112"/>
+      <c r="J50" s="113"/>
+      <c r="K50" s="108"/>
+      <c r="L50" s="109"/>
       <c r="M50" s="36"/>
       <c r="N50" s="36"/>
       <c r="O50" s="46" t="s">
@@ -29996,32 +30962,32 @@
       <c r="R50" s="41"/>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="83" t="s">
+      <c r="A51" s="89" t="s">
         <v>1103</v>
       </c>
-      <c r="B51" s="86" t="s">
+      <c r="B51" s="80" t="s">
         <v>1104</v>
       </c>
-      <c r="C51" s="89" t="s">
+      <c r="C51" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="90"/>
-      <c r="E51" s="95" t="s">
+      <c r="D51" s="75"/>
+      <c r="E51" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="96"/>
-      <c r="G51" s="101" t="s">
+      <c r="F51" s="63"/>
+      <c r="G51" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="102"/>
-      <c r="I51" s="101" t="s">
+      <c r="H51" s="69"/>
+      <c r="I51" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="102"/>
-      <c r="K51" s="101" t="s">
+      <c r="J51" s="69"/>
+      <c r="K51" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="102"/>
+      <c r="L51" s="69"/>
       <c r="M51" s="36"/>
       <c r="N51" s="36"/>
       <c r="O51" s="46" t="s">
@@ -30032,18 +30998,18 @@
       <c r="R51" s="41"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="84"/>
-      <c r="B52" s="87"/>
-      <c r="C52" s="91"/>
-      <c r="D52" s="92"/>
-      <c r="E52" s="97"/>
-      <c r="F52" s="98"/>
-      <c r="G52" s="103"/>
-      <c r="H52" s="104"/>
-      <c r="I52" s="103"/>
-      <c r="J52" s="104"/>
-      <c r="K52" s="103"/>
-      <c r="L52" s="104"/>
+      <c r="A52" s="90"/>
+      <c r="B52" s="81"/>
+      <c r="C52" s="76"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="65"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="70"/>
+      <c r="L52" s="71"/>
       <c r="M52" s="36"/>
       <c r="N52" s="36"/>
       <c r="O52" s="46" t="s">
@@ -30054,18 +31020,18 @@
       <c r="R52" s="41"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="84"/>
-      <c r="B53" s="87"/>
-      <c r="C53" s="91"/>
-      <c r="D53" s="92"/>
-      <c r="E53" s="97"/>
-      <c r="F53" s="98"/>
-      <c r="G53" s="103"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="103"/>
-      <c r="J53" s="104"/>
-      <c r="K53" s="103"/>
-      <c r="L53" s="104"/>
+      <c r="A53" s="90"/>
+      <c r="B53" s="81"/>
+      <c r="C53" s="76"/>
+      <c r="D53" s="77"/>
+      <c r="E53" s="64"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="70"/>
+      <c r="L53" s="71"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36"/>
       <c r="O53" s="43" t="s">
@@ -30076,34 +31042,34 @@
       <c r="R53" s="45"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="84"/>
-      <c r="B54" s="87"/>
-      <c r="C54" s="91"/>
-      <c r="D54" s="92"/>
-      <c r="E54" s="97"/>
-      <c r="F54" s="98"/>
-      <c r="G54" s="103"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="103"/>
-      <c r="J54" s="104"/>
-      <c r="K54" s="103"/>
-      <c r="L54" s="104"/>
+      <c r="A54" s="90"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="76"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="71"/>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="84"/>
-      <c r="B55" s="88"/>
-      <c r="C55" s="93"/>
-      <c r="D55" s="94"/>
-      <c r="E55" s="99"/>
-      <c r="F55" s="100"/>
-      <c r="G55" s="105"/>
-      <c r="H55" s="106"/>
-      <c r="I55" s="105"/>
-      <c r="J55" s="106"/>
-      <c r="K55" s="105"/>
-      <c r="L55" s="106"/>
+      <c r="A55" s="90"/>
+      <c r="B55" s="82"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="79"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="72"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="72"/>
+      <c r="J55" s="73"/>
+      <c r="K55" s="72"/>
+      <c r="L55" s="73"/>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
       <c r="O55" s="39" t="s">
@@ -30114,30 +31080,30 @@
       <c r="R55" s="41"/>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="84"/>
-      <c r="B56" s="86" t="s">
+      <c r="A56" s="90"/>
+      <c r="B56" s="80" t="s">
         <v>1109</v>
       </c>
-      <c r="C56" s="89" t="s">
+      <c r="C56" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="90"/>
-      <c r="E56" s="95" t="s">
+      <c r="D56" s="75"/>
+      <c r="E56" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="96"/>
-      <c r="G56" s="95" t="s">
+      <c r="F56" s="63"/>
+      <c r="G56" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="96"/>
-      <c r="I56" s="101" t="s">
+      <c r="H56" s="63"/>
+      <c r="I56" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="102"/>
-      <c r="K56" s="101" t="s">
+      <c r="J56" s="69"/>
+      <c r="K56" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="102"/>
+      <c r="L56" s="69"/>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
       <c r="O56" s="46" t="s">
@@ -30148,18 +31114,18 @@
       <c r="R56" s="41"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="84"/>
-      <c r="B57" s="87"/>
-      <c r="C57" s="91"/>
-      <c r="D57" s="92"/>
-      <c r="E57" s="97"/>
-      <c r="F57" s="98"/>
-      <c r="G57" s="97"/>
-      <c r="H57" s="98"/>
-      <c r="I57" s="103"/>
-      <c r="J57" s="104"/>
-      <c r="K57" s="103"/>
-      <c r="L57" s="104"/>
+      <c r="A57" s="90"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="76"/>
+      <c r="D57" s="77"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="64"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
+      <c r="K57" s="70"/>
+      <c r="L57" s="71"/>
       <c r="M57" s="36"/>
       <c r="N57" s="36"/>
       <c r="O57" s="46" t="s">
@@ -30170,18 +31136,18 @@
       <c r="R57" s="41"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="84"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="91"/>
-      <c r="D58" s="92"/>
-      <c r="E58" s="97"/>
-      <c r="F58" s="98"/>
-      <c r="G58" s="97"/>
-      <c r="H58" s="98"/>
-      <c r="I58" s="103"/>
-      <c r="J58" s="104"/>
-      <c r="K58" s="103"/>
-      <c r="L58" s="104"/>
+      <c r="A58" s="90"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="64"/>
+      <c r="H58" s="65"/>
+      <c r="I58" s="70"/>
+      <c r="J58" s="71"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="71"/>
       <c r="M58" s="36"/>
       <c r="N58" s="36"/>
       <c r="O58" s="46" t="s">
@@ -30192,18 +31158,18 @@
       <c r="R58" s="41"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="84"/>
-      <c r="B59" s="87"/>
-      <c r="C59" s="91"/>
-      <c r="D59" s="92"/>
-      <c r="E59" s="97"/>
-      <c r="F59" s="98"/>
-      <c r="G59" s="97"/>
-      <c r="H59" s="98"/>
-      <c r="I59" s="103"/>
-      <c r="J59" s="104"/>
-      <c r="K59" s="103"/>
-      <c r="L59" s="104"/>
+      <c r="A59" s="90"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="76"/>
+      <c r="D59" s="77"/>
+      <c r="E59" s="64"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="64"/>
+      <c r="H59" s="65"/>
+      <c r="I59" s="70"/>
+      <c r="J59" s="71"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="71"/>
       <c r="M59" s="36"/>
       <c r="N59" s="36"/>
       <c r="O59" s="43" t="s">
@@ -30214,18 +31180,18 @@
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="84"/>
-      <c r="B60" s="88"/>
-      <c r="C60" s="93"/>
-      <c r="D60" s="94"/>
-      <c r="E60" s="99"/>
-      <c r="F60" s="100"/>
-      <c r="G60" s="99"/>
-      <c r="H60" s="100"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="105"/>
-      <c r="L60" s="106"/>
+      <c r="A60" s="90"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="78"/>
+      <c r="D60" s="79"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="66"/>
+      <c r="H60" s="67"/>
+      <c r="I60" s="72"/>
+      <c r="J60" s="73"/>
+      <c r="K60" s="72"/>
+      <c r="L60" s="73"/>
       <c r="M60" s="36"/>
       <c r="N60" s="36"/>
       <c r="O60" s="36"/>
@@ -30234,30 +31200,30 @@
       <c r="R60" s="36"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="84"/>
-      <c r="B61" s="86" t="s">
+      <c r="A61" s="90"/>
+      <c r="B61" s="80" t="s">
         <v>1114</v>
       </c>
-      <c r="C61" s="107" t="s">
+      <c r="C61" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="108"/>
-      <c r="E61" s="89" t="s">
+      <c r="D61" s="84"/>
+      <c r="E61" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="90"/>
-      <c r="G61" s="95" t="s">
+      <c r="F61" s="75"/>
+      <c r="G61" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="96"/>
-      <c r="I61" s="95" t="s">
+      <c r="H61" s="63"/>
+      <c r="I61" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="96"/>
-      <c r="K61" s="101" t="s">
+      <c r="J61" s="63"/>
+      <c r="K61" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="102"/>
+      <c r="L61" s="69"/>
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
       <c r="O61" s="36"/>
@@ -30266,18 +31232,18 @@
       <c r="R61" s="36"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="84"/>
-      <c r="B62" s="87"/>
-      <c r="C62" s="109"/>
-      <c r="D62" s="110"/>
-      <c r="E62" s="91"/>
-      <c r="F62" s="92"/>
-      <c r="G62" s="97"/>
-      <c r="H62" s="98"/>
-      <c r="I62" s="97"/>
-      <c r="J62" s="98"/>
-      <c r="K62" s="103"/>
-      <c r="L62" s="104"/>
+      <c r="A62" s="90"/>
+      <c r="B62" s="81"/>
+      <c r="C62" s="85"/>
+      <c r="D62" s="86"/>
+      <c r="E62" s="76"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="65"/>
+      <c r="I62" s="64"/>
+      <c r="J62" s="65"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="71"/>
       <c r="M62" s="36"/>
       <c r="N62" s="36"/>
       <c r="O62" s="36"/>
@@ -30286,18 +31252,18 @@
       <c r="R62" s="36"/>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="84"/>
-      <c r="B63" s="87"/>
-      <c r="C63" s="109"/>
-      <c r="D63" s="110"/>
-      <c r="E63" s="91"/>
-      <c r="F63" s="92"/>
-      <c r="G63" s="97"/>
-      <c r="H63" s="98"/>
-      <c r="I63" s="97"/>
-      <c r="J63" s="98"/>
-      <c r="K63" s="103"/>
-      <c r="L63" s="104"/>
+      <c r="A63" s="90"/>
+      <c r="B63" s="81"/>
+      <c r="C63" s="85"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="76"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="64"/>
+      <c r="H63" s="65"/>
+      <c r="I63" s="64"/>
+      <c r="J63" s="65"/>
+      <c r="K63" s="70"/>
+      <c r="L63" s="71"/>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
       <c r="O63" s="36"/>
@@ -30306,18 +31272,18 @@
       <c r="R63" s="36"/>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="84"/>
-      <c r="B64" s="87"/>
-      <c r="C64" s="109"/>
-      <c r="D64" s="110"/>
-      <c r="E64" s="91"/>
-      <c r="F64" s="92"/>
-      <c r="G64" s="97"/>
-      <c r="H64" s="98"/>
-      <c r="I64" s="97"/>
-      <c r="J64" s="98"/>
-      <c r="K64" s="103"/>
-      <c r="L64" s="104"/>
+      <c r="A64" s="90"/>
+      <c r="B64" s="81"/>
+      <c r="C64" s="85"/>
+      <c r="D64" s="86"/>
+      <c r="E64" s="76"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="64"/>
+      <c r="H64" s="65"/>
+      <c r="I64" s="64"/>
+      <c r="J64" s="65"/>
+      <c r="K64" s="70"/>
+      <c r="L64" s="71"/>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
       <c r="O64" s="36"/>
@@ -30326,18 +31292,18 @@
       <c r="R64" s="36"/>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="84"/>
-      <c r="B65" s="88"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="112"/>
-      <c r="E65" s="93"/>
-      <c r="F65" s="94"/>
-      <c r="G65" s="99"/>
-      <c r="H65" s="100"/>
-      <c r="I65" s="99"/>
-      <c r="J65" s="100"/>
-      <c r="K65" s="105"/>
-      <c r="L65" s="106"/>
+      <c r="A65" s="90"/>
+      <c r="B65" s="82"/>
+      <c r="C65" s="87"/>
+      <c r="D65" s="88"/>
+      <c r="E65" s="78"/>
+      <c r="F65" s="79"/>
+      <c r="G65" s="66"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="66"/>
+      <c r="J65" s="67"/>
+      <c r="K65" s="72"/>
+      <c r="L65" s="73"/>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
       <c r="O65" s="36"/>
@@ -30346,30 +31312,30 @@
       <c r="R65" s="36"/>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="84"/>
-      <c r="B66" s="86" t="s">
+      <c r="A66" s="90"/>
+      <c r="B66" s="80" t="s">
         <v>1115</v>
       </c>
-      <c r="C66" s="107" t="s">
+      <c r="C66" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="108"/>
-      <c r="E66" s="107" t="s">
+      <c r="D66" s="84"/>
+      <c r="E66" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="108"/>
-      <c r="G66" s="89" t="s">
+      <c r="F66" s="84"/>
+      <c r="G66" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="90"/>
-      <c r="I66" s="89" t="s">
+      <c r="H66" s="75"/>
+      <c r="I66" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="90"/>
-      <c r="K66" s="95" t="s">
+      <c r="J66" s="75"/>
+      <c r="K66" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="96"/>
+      <c r="L66" s="63"/>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
       <c r="O66" s="36"/>
@@ -30378,18 +31344,18 @@
       <c r="R66" s="36"/>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="84"/>
-      <c r="B67" s="87"/>
-      <c r="C67" s="109"/>
-      <c r="D67" s="110"/>
-      <c r="E67" s="109"/>
-      <c r="F67" s="110"/>
-      <c r="G67" s="91"/>
-      <c r="H67" s="92"/>
-      <c r="I67" s="91"/>
-      <c r="J67" s="92"/>
-      <c r="K67" s="97"/>
-      <c r="L67" s="98"/>
+      <c r="A67" s="90"/>
+      <c r="B67" s="81"/>
+      <c r="C67" s="85"/>
+      <c r="D67" s="86"/>
+      <c r="E67" s="85"/>
+      <c r="F67" s="86"/>
+      <c r="G67" s="76"/>
+      <c r="H67" s="77"/>
+      <c r="I67" s="76"/>
+      <c r="J67" s="77"/>
+      <c r="K67" s="64"/>
+      <c r="L67" s="65"/>
       <c r="M67" s="36"/>
       <c r="N67" s="36"/>
       <c r="O67" s="36"/>
@@ -30398,18 +31364,18 @@
       <c r="R67" s="36"/>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="84"/>
-      <c r="B68" s="87"/>
-      <c r="C68" s="109"/>
-      <c r="D68" s="110"/>
-      <c r="E68" s="109"/>
-      <c r="F68" s="110"/>
-      <c r="G68" s="91"/>
-      <c r="H68" s="92"/>
-      <c r="I68" s="91"/>
-      <c r="J68" s="92"/>
-      <c r="K68" s="97"/>
-      <c r="L68" s="98"/>
+      <c r="A68" s="90"/>
+      <c r="B68" s="81"/>
+      <c r="C68" s="85"/>
+      <c r="D68" s="86"/>
+      <c r="E68" s="85"/>
+      <c r="F68" s="86"/>
+      <c r="G68" s="76"/>
+      <c r="H68" s="77"/>
+      <c r="I68" s="76"/>
+      <c r="J68" s="77"/>
+      <c r="K68" s="64"/>
+      <c r="L68" s="65"/>
       <c r="M68" s="36"/>
       <c r="N68" s="36"/>
       <c r="O68" s="36"/>
@@ -30418,18 +31384,18 @@
       <c r="R68" s="36"/>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="84"/>
-      <c r="B69" s="87"/>
-      <c r="C69" s="109"/>
-      <c r="D69" s="110"/>
-      <c r="E69" s="109"/>
-      <c r="F69" s="110"/>
-      <c r="G69" s="91"/>
-      <c r="H69" s="92"/>
-      <c r="I69" s="91"/>
-      <c r="J69" s="92"/>
-      <c r="K69" s="97"/>
-      <c r="L69" s="98"/>
+      <c r="A69" s="90"/>
+      <c r="B69" s="81"/>
+      <c r="C69" s="85"/>
+      <c r="D69" s="86"/>
+      <c r="E69" s="85"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="76"/>
+      <c r="H69" s="77"/>
+      <c r="I69" s="76"/>
+      <c r="J69" s="77"/>
+      <c r="K69" s="64"/>
+      <c r="L69" s="65"/>
       <c r="M69" s="36"/>
       <c r="N69" s="36"/>
       <c r="O69" s="36"/>
@@ -30438,18 +31404,18 @@
       <c r="R69" s="36"/>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="84"/>
-      <c r="B70" s="88"/>
-      <c r="C70" s="111"/>
-      <c r="D70" s="112"/>
-      <c r="E70" s="111"/>
-      <c r="F70" s="112"/>
-      <c r="G70" s="93"/>
-      <c r="H70" s="94"/>
-      <c r="I70" s="93"/>
-      <c r="J70" s="94"/>
-      <c r="K70" s="99"/>
-      <c r="L70" s="100"/>
+      <c r="A70" s="90"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="87"/>
+      <c r="D70" s="88"/>
+      <c r="E70" s="87"/>
+      <c r="F70" s="88"/>
+      <c r="G70" s="78"/>
+      <c r="H70" s="79"/>
+      <c r="I70" s="78"/>
+      <c r="J70" s="79"/>
+      <c r="K70" s="66"/>
+      <c r="L70" s="67"/>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="36"/>
@@ -30458,30 +31424,30 @@
       <c r="R70" s="36"/>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="84"/>
-      <c r="B71" s="86" t="s">
+      <c r="A71" s="90"/>
+      <c r="B71" s="80" t="s">
         <v>1116</v>
       </c>
-      <c r="C71" s="107" t="s">
+      <c r="C71" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="108"/>
-      <c r="E71" s="107" t="s">
+      <c r="D71" s="84"/>
+      <c r="E71" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="108"/>
-      <c r="G71" s="107" t="s">
+      <c r="F71" s="84"/>
+      <c r="G71" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="H71" s="108"/>
-      <c r="I71" s="107" t="s">
+      <c r="H71" s="84"/>
+      <c r="I71" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="108"/>
-      <c r="K71" s="89" t="s">
+      <c r="J71" s="84"/>
+      <c r="K71" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="90"/>
+      <c r="L71" s="75"/>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="36"/>
@@ -30490,18 +31456,18 @@
       <c r="R71" s="36"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="84"/>
-      <c r="B72" s="87"/>
-      <c r="C72" s="109"/>
-      <c r="D72" s="110"/>
-      <c r="E72" s="109"/>
-      <c r="F72" s="110"/>
-      <c r="G72" s="109"/>
-      <c r="H72" s="110"/>
-      <c r="I72" s="109"/>
-      <c r="J72" s="110"/>
-      <c r="K72" s="91"/>
-      <c r="L72" s="92"/>
+      <c r="A72" s="90"/>
+      <c r="B72" s="81"/>
+      <c r="C72" s="85"/>
+      <c r="D72" s="86"/>
+      <c r="E72" s="85"/>
+      <c r="F72" s="86"/>
+      <c r="G72" s="85"/>
+      <c r="H72" s="86"/>
+      <c r="I72" s="85"/>
+      <c r="J72" s="86"/>
+      <c r="K72" s="76"/>
+      <c r="L72" s="77"/>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="36"/>
@@ -30510,18 +31476,18 @@
       <c r="R72" s="36"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="84"/>
-      <c r="B73" s="87"/>
-      <c r="C73" s="109"/>
-      <c r="D73" s="110"/>
-      <c r="E73" s="109"/>
-      <c r="F73" s="110"/>
-      <c r="G73" s="109"/>
-      <c r="H73" s="110"/>
-      <c r="I73" s="109"/>
-      <c r="J73" s="110"/>
-      <c r="K73" s="91"/>
-      <c r="L73" s="92"/>
+      <c r="A73" s="90"/>
+      <c r="B73" s="81"/>
+      <c r="C73" s="85"/>
+      <c r="D73" s="86"/>
+      <c r="E73" s="85"/>
+      <c r="F73" s="86"/>
+      <c r="G73" s="85"/>
+      <c r="H73" s="86"/>
+      <c r="I73" s="85"/>
+      <c r="J73" s="86"/>
+      <c r="K73" s="76"/>
+      <c r="L73" s="77"/>
       <c r="M73" s="36"/>
       <c r="N73" s="36"/>
       <c r="O73" s="36"/>
@@ -30530,18 +31496,18 @@
       <c r="R73" s="36"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="84"/>
-      <c r="B74" s="87"/>
-      <c r="C74" s="109"/>
-      <c r="D74" s="110"/>
-      <c r="E74" s="109"/>
-      <c r="F74" s="110"/>
-      <c r="G74" s="109"/>
-      <c r="H74" s="110"/>
-      <c r="I74" s="109"/>
-      <c r="J74" s="110"/>
-      <c r="K74" s="91"/>
-      <c r="L74" s="92"/>
+      <c r="A74" s="90"/>
+      <c r="B74" s="81"/>
+      <c r="C74" s="85"/>
+      <c r="D74" s="86"/>
+      <c r="E74" s="85"/>
+      <c r="F74" s="86"/>
+      <c r="G74" s="85"/>
+      <c r="H74" s="86"/>
+      <c r="I74" s="85"/>
+      <c r="J74" s="86"/>
+      <c r="K74" s="76"/>
+      <c r="L74" s="77"/>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="36"/>
@@ -30550,18 +31516,18 @@
       <c r="R74" s="36"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="85"/>
-      <c r="B75" s="88"/>
-      <c r="C75" s="111"/>
-      <c r="D75" s="112"/>
-      <c r="E75" s="111"/>
-      <c r="F75" s="112"/>
-      <c r="G75" s="111"/>
-      <c r="H75" s="112"/>
-      <c r="I75" s="111"/>
-      <c r="J75" s="112"/>
-      <c r="K75" s="93"/>
-      <c r="L75" s="94"/>
+      <c r="A75" s="91"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="87"/>
+      <c r="D75" s="88"/>
+      <c r="E75" s="87"/>
+      <c r="F75" s="88"/>
+      <c r="G75" s="87"/>
+      <c r="H75" s="88"/>
+      <c r="I75" s="87"/>
+      <c r="J75" s="88"/>
+      <c r="K75" s="78"/>
+      <c r="L75" s="79"/>
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="36"/>
@@ -30591,6 +31557,34 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A47:B50"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A51:A75"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:D55"/>
+    <mergeCell ref="E51:F55"/>
+    <mergeCell ref="G51:H55"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:D65"/>
+    <mergeCell ref="E61:F65"/>
+    <mergeCell ref="G61:H65"/>
+    <mergeCell ref="I51:J55"/>
+    <mergeCell ref="K51:L55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:D60"/>
+    <mergeCell ref="E56:F60"/>
+    <mergeCell ref="G56:H60"/>
+    <mergeCell ref="I56:J60"/>
+    <mergeCell ref="K56:L60"/>
     <mergeCell ref="I61:J65"/>
     <mergeCell ref="K61:L65"/>
     <mergeCell ref="K71:L75"/>
@@ -30605,34 +31599,6 @@
     <mergeCell ref="E71:F75"/>
     <mergeCell ref="G71:H75"/>
     <mergeCell ref="I71:J75"/>
-    <mergeCell ref="I51:J55"/>
-    <mergeCell ref="K51:L55"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:D60"/>
-    <mergeCell ref="E56:F60"/>
-    <mergeCell ref="G56:H60"/>
-    <mergeCell ref="I56:J60"/>
-    <mergeCell ref="K56:L60"/>
-    <mergeCell ref="A51:A75"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:D55"/>
-    <mergeCell ref="E51:F55"/>
-    <mergeCell ref="G51:H55"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:D65"/>
-    <mergeCell ref="E61:F65"/>
-    <mergeCell ref="G61:H65"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A47:B50"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -41310,7 +42276,7 @@
         <v>679</v>
       </c>
       <c r="B4">
-        <f>'Cost Benefit Analysis'!B4</f>
+        <f>'Financial Evaluation'!B4</f>
         <v>14</v>
       </c>
       <c r="C4" t="s">
@@ -41329,7 +42295,7 @@
         <v>769</v>
       </c>
       <c r="H4">
-        <f>'Cost Benefit Analysis'!B14</f>
+        <f>'Financial Evaluation'!B14</f>
         <v>11</v>
       </c>
       <c r="I4" t="s">
@@ -41344,7 +42310,7 @@
         <v>22</v>
       </c>
       <c r="B5">
-        <f>'Cost Benefit Analysis'!B28</f>
+        <f>'Financial Evaluation'!B28</f>
         <v>4.9996855778092213</v>
       </c>
       <c r="C5" t="s">
@@ -41363,7 +42329,7 @@
         <v>737</v>
       </c>
       <c r="H5" s="16">
-        <f>'Cost Benefit Analysis'!B31</f>
+        <f>'Financial Evaluation'!B31</f>
         <v>0.11752053733020262</v>
       </c>
       <c r="I5" t="s">
@@ -41378,7 +42344,7 @@
         <v>76</v>
       </c>
       <c r="B6">
-        <f>'Cost Benefit Analysis'!B23</f>
+        <f>'Financial Evaluation'!B23</f>
         <v>23.487749999999998</v>
       </c>
       <c r="C6" t="s">
@@ -41397,7 +42363,7 @@
         <v>525</v>
       </c>
       <c r="H6">
-        <f>'Cost Benefit Analysis'!B16</f>
+        <f>'Financial Evaluation'!B16</f>
         <v>0.97499999999999998</v>
       </c>
       <c r="I6" t="s">
@@ -41412,7 +42378,7 @@
         <v>724</v>
       </c>
       <c r="B7">
-        <f>'Cost Benefit Analysis'!B24</f>
+        <f>'Financial Evaluation'!B24</f>
         <v>4.1103562499999997</v>
       </c>
       <c r="C7" t="s">
@@ -41431,7 +42397,7 @@
         <v>774</v>
       </c>
       <c r="H7">
-        <f>'Cost Benefit Analysis'!B26</f>
+        <f>'Financial Evaluation'!B26</f>
         <v>1.3101801625</v>
       </c>
       <c r="I7" t="s">
@@ -42008,30 +42974,30 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="21">
-      <c r="A33" s="113" t="s">
+      <c r="A33" s="114" t="s">
         <v>1047</v>
       </c>
-      <c r="B33" s="114"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="114"/>
-      <c r="E33" s="114"/>
-      <c r="F33" s="114"/>
-      <c r="G33" s="114"/>
-      <c r="H33" s="114"/>
-      <c r="I33" s="114"/>
+      <c r="B33" s="115"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="115"/>
+      <c r="F33" s="115"/>
+      <c r="G33" s="115"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="115"/>
     </row>
     <row r="35" spans="1:9" ht="15.75">
-      <c r="A35" s="115" t="s">
+      <c r="A35" s="116" t="s">
         <v>1048</v>
       </c>
-      <c r="B35" s="114"/>
-      <c r="C35" s="114"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="114"/>
-      <c r="H35" s="114"/>
-      <c r="I35" s="114"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="115"/>
+      <c r="D35" s="115"/>
+      <c r="E35" s="115"/>
+      <c r="F35" s="115"/>
+      <c r="G35" s="115"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="115"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="22" t="s">
@@ -42484,11 +43450,11 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75">
-      <c r="A52" s="115" t="s">
+      <c r="A52" s="116" t="s">
         <v>1071</v>
       </c>
-      <c r="B52" s="114"/>
-      <c r="C52" s="114"/>
+      <c r="B52" s="115"/>
+      <c r="C52" s="115"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="22" t="s">
@@ -42586,11 +43552,11 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.75">
-      <c r="A63" s="115" t="s">
+      <c r="A63" s="116" t="s">
         <v>1081</v>
       </c>
-      <c r="B63" s="114"/>
-      <c r="C63" s="114"/>
+      <c r="B63" s="115"/>
+      <c r="C63" s="115"/>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="22" t="s">

--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehrnia\Desktop\Job\AtlasCopco\Business Analysis Project and Stakeholder Management\Excel_PLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CC2D02-1BB8-42F2-911C-FE1289BF981D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF744198-B2BE-40AC-AF83-DE4095A7B300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4195,96 +4195,16 @@
     <xf numFmtId="0" fontId="37" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4351,6 +4271,96 @@
     <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4358,16 +4368,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -7963,14 +7963,14 @@
             <a:buAutoNum type="romanLcPeriod" startAt="3"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1">
+            <a:rPr lang="en-GB" sz="1400" b="1">
               <a:solidFill>
                 <a:schemeClr val="tx2"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Configuration, Change Management &amp; Design Validation</a:t>
           </a:r>
-          <a:endParaRPr lang="fa-IR" sz="1200" b="1">
+          <a:endParaRPr lang="fa-IR" sz="1400" b="1">
             <a:solidFill>
               <a:schemeClr val="tx2"/>
             </a:solidFill>
@@ -12829,12 +12829,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="45">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="62" t="s">
         <v>1124</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
       <c r="E1" s="52"/>
       <c r="F1" s="52"/>
       <c r="G1" s="52"/>
@@ -12845,69 +12845,69 @@
       <c r="L1" s="52"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
-      <c r="P1" s="119" t="s">
+      <c r="P1" s="64" t="s">
         <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="15.75">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="65" t="s">
         <v>1123</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="121"/>
-      <c r="M2" s="122" t="s">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="66"/>
+      <c r="M2" s="67" t="s">
         <v>1126</v>
       </c>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="122"/>
-      <c r="R2" s="122"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="118"/>
-      <c r="Y2" s="118"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="63"/>
+      <c r="Y2" s="63"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="M3" s="122" t="s">
+      <c r="M3" s="67" t="s">
         <v>1127</v>
       </c>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="122"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="122"/>
-      <c r="W3" s="122"/>
-      <c r="X3" s="118"/>
-      <c r="Y3" s="118"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="M4" s="122" t="s">
+      <c r="M4" s="67" t="s">
         <v>1128</v>
       </c>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="122"/>
-      <c r="U4" s="122"/>
-      <c r="V4" s="122"/>
-      <c r="W4" s="122"/>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="63"/>
+      <c r="Y4" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -30746,14 +30746,14 @@
       <c r="R40" s="36"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="92" t="s">
+      <c r="A41" s="68" t="s">
         <v>1117</v>
       </c>
-      <c r="B41" s="92"/>
-      <c r="C41" s="92" t="s">
+      <c r="B41" s="68"/>
+      <c r="C41" s="68" t="s">
         <v>1118</v>
       </c>
-      <c r="D41" s="92"/>
+      <c r="D41" s="68"/>
       <c r="E41" s="37" t="s">
         <v>9</v>
       </c>
@@ -30774,10 +30774,10 @@
       <c r="R41" s="41"/>
     </row>
     <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="93"/>
-      <c r="B42" s="93"/>
-      <c r="C42" s="93"/>
-      <c r="D42" s="93"/>
+      <c r="A42" s="69"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
       <c r="E42" s="42"/>
       <c r="F42" s="36"/>
       <c r="G42" s="36"/>
@@ -30866,38 +30866,38 @@
       <c r="R46" s="45"/>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="94" t="s">
+      <c r="A47" s="70" t="s">
         <v>1093</v>
       </c>
-      <c r="B47" s="95"/>
-      <c r="C47" s="100" t="s">
+      <c r="B47" s="71"/>
+      <c r="C47" s="76" t="s">
         <v>1094</v>
       </c>
-      <c r="D47" s="101"/>
-      <c r="E47" s="101"/>
-      <c r="F47" s="101"/>
-      <c r="G47" s="101"/>
-      <c r="H47" s="101"/>
-      <c r="I47" s="101"/>
-      <c r="J47" s="101"/>
-      <c r="K47" s="101"/>
-      <c r="L47" s="102"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
+      <c r="F47" s="77"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="77"/>
+      <c r="J47" s="77"/>
+      <c r="K47" s="77"/>
+      <c r="L47" s="78"/>
       <c r="M47" s="36"/>
       <c r="N47" s="36"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="96"/>
-      <c r="B48" s="97"/>
-      <c r="C48" s="103"/>
-      <c r="D48" s="104"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="104"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="104"/>
-      <c r="K48" s="104"/>
-      <c r="L48" s="105"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="80"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="80"/>
+      <c r="K48" s="80"/>
+      <c r="L48" s="81"/>
       <c r="M48" s="36"/>
       <c r="N48" s="36"/>
       <c r="O48" s="39" t="s">
@@ -30908,28 +30908,28 @@
       <c r="R48" s="41"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="96"/>
-      <c r="B49" s="97"/>
-      <c r="C49" s="106" t="s">
+      <c r="A49" s="72"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="82" t="s">
         <v>1096</v>
       </c>
-      <c r="D49" s="107"/>
-      <c r="E49" s="106" t="s">
+      <c r="D49" s="83"/>
+      <c r="E49" s="82" t="s">
         <v>1097</v>
       </c>
-      <c r="F49" s="107"/>
-      <c r="G49" s="106" t="s">
+      <c r="F49" s="83"/>
+      <c r="G49" s="82" t="s">
         <v>1098</v>
       </c>
-      <c r="H49" s="107"/>
-      <c r="I49" s="110" t="s">
+      <c r="H49" s="83"/>
+      <c r="I49" s="86" t="s">
         <v>1099</v>
       </c>
-      <c r="J49" s="111"/>
-      <c r="K49" s="106" t="s">
+      <c r="J49" s="87"/>
+      <c r="K49" s="82" t="s">
         <v>1100</v>
       </c>
-      <c r="L49" s="107"/>
+      <c r="L49" s="83"/>
       <c r="M49" s="36"/>
       <c r="N49" s="36"/>
       <c r="O49" s="46" t="s">
@@ -30940,18 +30940,18 @@
       <c r="R49" s="41"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="98"/>
-      <c r="B50" s="99"/>
-      <c r="C50" s="108"/>
-      <c r="D50" s="109"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="109"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="109"/>
-      <c r="I50" s="112"/>
-      <c r="J50" s="113"/>
-      <c r="K50" s="108"/>
-      <c r="L50" s="109"/>
+      <c r="A50" s="74"/>
+      <c r="B50" s="75"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="85"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="85"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="85"/>
+      <c r="I50" s="88"/>
+      <c r="J50" s="89"/>
+      <c r="K50" s="84"/>
+      <c r="L50" s="85"/>
       <c r="M50" s="36"/>
       <c r="N50" s="36"/>
       <c r="O50" s="46" t="s">
@@ -30962,32 +30962,32 @@
       <c r="R50" s="41"/>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="89" t="s">
+      <c r="A51" s="90" t="s">
         <v>1103</v>
       </c>
-      <c r="B51" s="80" t="s">
+      <c r="B51" s="93" t="s">
         <v>1104</v>
       </c>
-      <c r="C51" s="74" t="s">
+      <c r="C51" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="75"/>
-      <c r="E51" s="62" t="s">
+      <c r="D51" s="97"/>
+      <c r="E51" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="63"/>
-      <c r="G51" s="68" t="s">
+      <c r="F51" s="103"/>
+      <c r="G51" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="69"/>
-      <c r="I51" s="68" t="s">
+      <c r="H51" s="109"/>
+      <c r="I51" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="69"/>
-      <c r="K51" s="68" t="s">
+      <c r="J51" s="109"/>
+      <c r="K51" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="69"/>
+      <c r="L51" s="109"/>
       <c r="M51" s="36"/>
       <c r="N51" s="36"/>
       <c r="O51" s="46" t="s">
@@ -30998,18 +30998,18 @@
       <c r="R51" s="41"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="90"/>
-      <c r="B52" s="81"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="64"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="71"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="71"/>
-      <c r="K52" s="70"/>
-      <c r="L52" s="71"/>
+      <c r="A52" s="91"/>
+      <c r="B52" s="94"/>
+      <c r="C52" s="98"/>
+      <c r="D52" s="99"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="110"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="110"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="110"/>
+      <c r="L52" s="111"/>
       <c r="M52" s="36"/>
       <c r="N52" s="36"/>
       <c r="O52" s="46" t="s">
@@ -31020,18 +31020,18 @@
       <c r="R52" s="41"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="90"/>
-      <c r="B53" s="81"/>
-      <c r="C53" s="76"/>
-      <c r="D53" s="77"/>
-      <c r="E53" s="64"/>
-      <c r="F53" s="65"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="71"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="71"/>
-      <c r="K53" s="70"/>
-      <c r="L53" s="71"/>
+      <c r="A53" s="91"/>
+      <c r="B53" s="94"/>
+      <c r="C53" s="98"/>
+      <c r="D53" s="99"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="105"/>
+      <c r="G53" s="110"/>
+      <c r="H53" s="111"/>
+      <c r="I53" s="110"/>
+      <c r="J53" s="111"/>
+      <c r="K53" s="110"/>
+      <c r="L53" s="111"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36"/>
       <c r="O53" s="43" t="s">
@@ -31042,34 +31042,34 @@
       <c r="R53" s="45"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="90"/>
-      <c r="B54" s="81"/>
-      <c r="C54" s="76"/>
-      <c r="D54" s="77"/>
-      <c r="E54" s="64"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="71"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="71"/>
-      <c r="K54" s="70"/>
-      <c r="L54" s="71"/>
+      <c r="A54" s="91"/>
+      <c r="B54" s="94"/>
+      <c r="C54" s="98"/>
+      <c r="D54" s="99"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="105"/>
+      <c r="G54" s="110"/>
+      <c r="H54" s="111"/>
+      <c r="I54" s="110"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="110"/>
+      <c r="L54" s="111"/>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="90"/>
-      <c r="B55" s="82"/>
-      <c r="C55" s="78"/>
-      <c r="D55" s="79"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="72"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="72"/>
-      <c r="J55" s="73"/>
-      <c r="K55" s="72"/>
-      <c r="L55" s="73"/>
+      <c r="A55" s="91"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="100"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="106"/>
+      <c r="F55" s="107"/>
+      <c r="G55" s="112"/>
+      <c r="H55" s="113"/>
+      <c r="I55" s="112"/>
+      <c r="J55" s="113"/>
+      <c r="K55" s="112"/>
+      <c r="L55" s="113"/>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
       <c r="O55" s="39" t="s">
@@ -31080,30 +31080,30 @@
       <c r="R55" s="41"/>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="90"/>
-      <c r="B56" s="80" t="s">
+      <c r="A56" s="91"/>
+      <c r="B56" s="93" t="s">
         <v>1109</v>
       </c>
-      <c r="C56" s="74" t="s">
+      <c r="C56" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="75"/>
-      <c r="E56" s="62" t="s">
+      <c r="D56" s="97"/>
+      <c r="E56" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="63"/>
-      <c r="G56" s="62" t="s">
+      <c r="F56" s="103"/>
+      <c r="G56" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="63"/>
-      <c r="I56" s="68" t="s">
+      <c r="H56" s="103"/>
+      <c r="I56" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="69"/>
-      <c r="K56" s="68" t="s">
+      <c r="J56" s="109"/>
+      <c r="K56" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="69"/>
+      <c r="L56" s="109"/>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
       <c r="O56" s="46" t="s">
@@ -31114,18 +31114,18 @@
       <c r="R56" s="41"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="90"/>
-      <c r="B57" s="81"/>
-      <c r="C57" s="76"/>
-      <c r="D57" s="77"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="65"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="65"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="71"/>
-      <c r="K57" s="70"/>
-      <c r="L57" s="71"/>
+      <c r="A57" s="91"/>
+      <c r="B57" s="94"/>
+      <c r="C57" s="98"/>
+      <c r="D57" s="99"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="105"/>
+      <c r="G57" s="104"/>
+      <c r="H57" s="105"/>
+      <c r="I57" s="110"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="110"/>
+      <c r="L57" s="111"/>
       <c r="M57" s="36"/>
       <c r="N57" s="36"/>
       <c r="O57" s="46" t="s">
@@ -31136,18 +31136,18 @@
       <c r="R57" s="41"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="90"/>
-      <c r="B58" s="81"/>
-      <c r="C58" s="76"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="65"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="65"/>
-      <c r="I58" s="70"/>
-      <c r="J58" s="71"/>
-      <c r="K58" s="70"/>
-      <c r="L58" s="71"/>
+      <c r="A58" s="91"/>
+      <c r="B58" s="94"/>
+      <c r="C58" s="98"/>
+      <c r="D58" s="99"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="105"/>
+      <c r="G58" s="104"/>
+      <c r="H58" s="105"/>
+      <c r="I58" s="110"/>
+      <c r="J58" s="111"/>
+      <c r="K58" s="110"/>
+      <c r="L58" s="111"/>
       <c r="M58" s="36"/>
       <c r="N58" s="36"/>
       <c r="O58" s="46" t="s">
@@ -31158,18 +31158,18 @@
       <c r="R58" s="41"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="90"/>
-      <c r="B59" s="81"/>
-      <c r="C59" s="76"/>
-      <c r="D59" s="77"/>
-      <c r="E59" s="64"/>
-      <c r="F59" s="65"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="65"/>
-      <c r="I59" s="70"/>
-      <c r="J59" s="71"/>
-      <c r="K59" s="70"/>
-      <c r="L59" s="71"/>
+      <c r="A59" s="91"/>
+      <c r="B59" s="94"/>
+      <c r="C59" s="98"/>
+      <c r="D59" s="99"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="105"/>
+      <c r="G59" s="104"/>
+      <c r="H59" s="105"/>
+      <c r="I59" s="110"/>
+      <c r="J59" s="111"/>
+      <c r="K59" s="110"/>
+      <c r="L59" s="111"/>
       <c r="M59" s="36"/>
       <c r="N59" s="36"/>
       <c r="O59" s="43" t="s">
@@ -31180,18 +31180,18 @@
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="90"/>
-      <c r="B60" s="82"/>
-      <c r="C60" s="78"/>
-      <c r="D60" s="79"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="72"/>
-      <c r="J60" s="73"/>
-      <c r="K60" s="72"/>
-      <c r="L60" s="73"/>
+      <c r="A60" s="91"/>
+      <c r="B60" s="95"/>
+      <c r="C60" s="100"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="112"/>
+      <c r="L60" s="113"/>
       <c r="M60" s="36"/>
       <c r="N60" s="36"/>
       <c r="O60" s="36"/>
@@ -31200,30 +31200,30 @@
       <c r="R60" s="36"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="90"/>
-      <c r="B61" s="80" t="s">
+      <c r="A61" s="91"/>
+      <c r="B61" s="93" t="s">
         <v>1114</v>
       </c>
-      <c r="C61" s="83" t="s">
+      <c r="C61" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="84"/>
-      <c r="E61" s="74" t="s">
+      <c r="D61" s="115"/>
+      <c r="E61" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="75"/>
-      <c r="G61" s="62" t="s">
+      <c r="F61" s="97"/>
+      <c r="G61" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="63"/>
-      <c r="I61" s="62" t="s">
+      <c r="H61" s="103"/>
+      <c r="I61" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="63"/>
-      <c r="K61" s="68" t="s">
+      <c r="J61" s="103"/>
+      <c r="K61" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="69"/>
+      <c r="L61" s="109"/>
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
       <c r="O61" s="36"/>
@@ -31232,18 +31232,18 @@
       <c r="R61" s="36"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="90"/>
-      <c r="B62" s="81"/>
-      <c r="C62" s="85"/>
-      <c r="D62" s="86"/>
-      <c r="E62" s="76"/>
-      <c r="F62" s="77"/>
-      <c r="G62" s="64"/>
-      <c r="H62" s="65"/>
-      <c r="I62" s="64"/>
-      <c r="J62" s="65"/>
-      <c r="K62" s="70"/>
-      <c r="L62" s="71"/>
+      <c r="A62" s="91"/>
+      <c r="B62" s="94"/>
+      <c r="C62" s="116"/>
+      <c r="D62" s="117"/>
+      <c r="E62" s="98"/>
+      <c r="F62" s="99"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="105"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="105"/>
+      <c r="K62" s="110"/>
+      <c r="L62" s="111"/>
       <c r="M62" s="36"/>
       <c r="N62" s="36"/>
       <c r="O62" s="36"/>
@@ -31252,18 +31252,18 @@
       <c r="R62" s="36"/>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="90"/>
-      <c r="B63" s="81"/>
-      <c r="C63" s="85"/>
-      <c r="D63" s="86"/>
-      <c r="E63" s="76"/>
-      <c r="F63" s="77"/>
-      <c r="G63" s="64"/>
-      <c r="H63" s="65"/>
-      <c r="I63" s="64"/>
-      <c r="J63" s="65"/>
-      <c r="K63" s="70"/>
-      <c r="L63" s="71"/>
+      <c r="A63" s="91"/>
+      <c r="B63" s="94"/>
+      <c r="C63" s="116"/>
+      <c r="D63" s="117"/>
+      <c r="E63" s="98"/>
+      <c r="F63" s="99"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="105"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="105"/>
+      <c r="K63" s="110"/>
+      <c r="L63" s="111"/>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
       <c r="O63" s="36"/>
@@ -31272,18 +31272,18 @@
       <c r="R63" s="36"/>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="90"/>
-      <c r="B64" s="81"/>
-      <c r="C64" s="85"/>
-      <c r="D64" s="86"/>
-      <c r="E64" s="76"/>
-      <c r="F64" s="77"/>
-      <c r="G64" s="64"/>
-      <c r="H64" s="65"/>
-      <c r="I64" s="64"/>
-      <c r="J64" s="65"/>
-      <c r="K64" s="70"/>
-      <c r="L64" s="71"/>
+      <c r="A64" s="91"/>
+      <c r="B64" s="94"/>
+      <c r="C64" s="116"/>
+      <c r="D64" s="117"/>
+      <c r="E64" s="98"/>
+      <c r="F64" s="99"/>
+      <c r="G64" s="104"/>
+      <c r="H64" s="105"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="105"/>
+      <c r="K64" s="110"/>
+      <c r="L64" s="111"/>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
       <c r="O64" s="36"/>
@@ -31292,18 +31292,18 @@
       <c r="R64" s="36"/>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="90"/>
-      <c r="B65" s="82"/>
-      <c r="C65" s="87"/>
-      <c r="D65" s="88"/>
-      <c r="E65" s="78"/>
-      <c r="F65" s="79"/>
-      <c r="G65" s="66"/>
-      <c r="H65" s="67"/>
-      <c r="I65" s="66"/>
-      <c r="J65" s="67"/>
-      <c r="K65" s="72"/>
-      <c r="L65" s="73"/>
+      <c r="A65" s="91"/>
+      <c r="B65" s="95"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="100"/>
+      <c r="F65" s="101"/>
+      <c r="G65" s="106"/>
+      <c r="H65" s="107"/>
+      <c r="I65" s="106"/>
+      <c r="J65" s="107"/>
+      <c r="K65" s="112"/>
+      <c r="L65" s="113"/>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
       <c r="O65" s="36"/>
@@ -31312,30 +31312,30 @@
       <c r="R65" s="36"/>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="90"/>
-      <c r="B66" s="80" t="s">
+      <c r="A66" s="91"/>
+      <c r="B66" s="93" t="s">
         <v>1115</v>
       </c>
-      <c r="C66" s="83" t="s">
+      <c r="C66" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="84"/>
-      <c r="E66" s="83" t="s">
+      <c r="D66" s="115"/>
+      <c r="E66" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="84"/>
-      <c r="G66" s="74" t="s">
+      <c r="F66" s="115"/>
+      <c r="G66" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="75"/>
-      <c r="I66" s="74" t="s">
+      <c r="H66" s="97"/>
+      <c r="I66" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="75"/>
-      <c r="K66" s="62" t="s">
+      <c r="J66" s="97"/>
+      <c r="K66" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="63"/>
+      <c r="L66" s="103"/>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
       <c r="O66" s="36"/>
@@ -31344,18 +31344,18 @@
       <c r="R66" s="36"/>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="90"/>
-      <c r="B67" s="81"/>
-      <c r="C67" s="85"/>
-      <c r="D67" s="86"/>
-      <c r="E67" s="85"/>
-      <c r="F67" s="86"/>
-      <c r="G67" s="76"/>
-      <c r="H67" s="77"/>
-      <c r="I67" s="76"/>
-      <c r="J67" s="77"/>
-      <c r="K67" s="64"/>
-      <c r="L67" s="65"/>
+      <c r="A67" s="91"/>
+      <c r="B67" s="94"/>
+      <c r="C67" s="116"/>
+      <c r="D67" s="117"/>
+      <c r="E67" s="116"/>
+      <c r="F67" s="117"/>
+      <c r="G67" s="98"/>
+      <c r="H67" s="99"/>
+      <c r="I67" s="98"/>
+      <c r="J67" s="99"/>
+      <c r="K67" s="104"/>
+      <c r="L67" s="105"/>
       <c r="M67" s="36"/>
       <c r="N67" s="36"/>
       <c r="O67" s="36"/>
@@ -31364,18 +31364,18 @@
       <c r="R67" s="36"/>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="90"/>
-      <c r="B68" s="81"/>
-      <c r="C68" s="85"/>
-      <c r="D68" s="86"/>
-      <c r="E68" s="85"/>
-      <c r="F68" s="86"/>
-      <c r="G68" s="76"/>
-      <c r="H68" s="77"/>
-      <c r="I68" s="76"/>
-      <c r="J68" s="77"/>
-      <c r="K68" s="64"/>
-      <c r="L68" s="65"/>
+      <c r="A68" s="91"/>
+      <c r="B68" s="94"/>
+      <c r="C68" s="116"/>
+      <c r="D68" s="117"/>
+      <c r="E68" s="116"/>
+      <c r="F68" s="117"/>
+      <c r="G68" s="98"/>
+      <c r="H68" s="99"/>
+      <c r="I68" s="98"/>
+      <c r="J68" s="99"/>
+      <c r="K68" s="104"/>
+      <c r="L68" s="105"/>
       <c r="M68" s="36"/>
       <c r="N68" s="36"/>
       <c r="O68" s="36"/>
@@ -31384,18 +31384,18 @@
       <c r="R68" s="36"/>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="90"/>
-      <c r="B69" s="81"/>
-      <c r="C69" s="85"/>
-      <c r="D69" s="86"/>
-      <c r="E69" s="85"/>
-      <c r="F69" s="86"/>
-      <c r="G69" s="76"/>
-      <c r="H69" s="77"/>
-      <c r="I69" s="76"/>
-      <c r="J69" s="77"/>
-      <c r="K69" s="64"/>
-      <c r="L69" s="65"/>
+      <c r="A69" s="91"/>
+      <c r="B69" s="94"/>
+      <c r="C69" s="116"/>
+      <c r="D69" s="117"/>
+      <c r="E69" s="116"/>
+      <c r="F69" s="117"/>
+      <c r="G69" s="98"/>
+      <c r="H69" s="99"/>
+      <c r="I69" s="98"/>
+      <c r="J69" s="99"/>
+      <c r="K69" s="104"/>
+      <c r="L69" s="105"/>
       <c r="M69" s="36"/>
       <c r="N69" s="36"/>
       <c r="O69" s="36"/>
@@ -31404,18 +31404,18 @@
       <c r="R69" s="36"/>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="90"/>
-      <c r="B70" s="82"/>
-      <c r="C70" s="87"/>
-      <c r="D70" s="88"/>
-      <c r="E70" s="87"/>
-      <c r="F70" s="88"/>
-      <c r="G70" s="78"/>
-      <c r="H70" s="79"/>
-      <c r="I70" s="78"/>
-      <c r="J70" s="79"/>
-      <c r="K70" s="66"/>
-      <c r="L70" s="67"/>
+      <c r="A70" s="91"/>
+      <c r="B70" s="95"/>
+      <c r="C70" s="118"/>
+      <c r="D70" s="119"/>
+      <c r="E70" s="118"/>
+      <c r="F70" s="119"/>
+      <c r="G70" s="100"/>
+      <c r="H70" s="101"/>
+      <c r="I70" s="100"/>
+      <c r="J70" s="101"/>
+      <c r="K70" s="106"/>
+      <c r="L70" s="107"/>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="36"/>
@@ -31424,30 +31424,30 @@
       <c r="R70" s="36"/>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="90"/>
-      <c r="B71" s="80" t="s">
+      <c r="A71" s="91"/>
+      <c r="B71" s="93" t="s">
         <v>1116</v>
       </c>
-      <c r="C71" s="83" t="s">
+      <c r="C71" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="84"/>
-      <c r="E71" s="83" t="s">
+      <c r="D71" s="115"/>
+      <c r="E71" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="84"/>
-      <c r="G71" s="83" t="s">
+      <c r="F71" s="115"/>
+      <c r="G71" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="H71" s="84"/>
-      <c r="I71" s="83" t="s">
+      <c r="H71" s="115"/>
+      <c r="I71" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="84"/>
-      <c r="K71" s="74" t="s">
+      <c r="J71" s="115"/>
+      <c r="K71" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="75"/>
+      <c r="L71" s="97"/>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="36"/>
@@ -31456,18 +31456,18 @@
       <c r="R71" s="36"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="90"/>
-      <c r="B72" s="81"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="86"/>
-      <c r="E72" s="85"/>
-      <c r="F72" s="86"/>
-      <c r="G72" s="85"/>
-      <c r="H72" s="86"/>
-      <c r="I72" s="85"/>
-      <c r="J72" s="86"/>
-      <c r="K72" s="76"/>
-      <c r="L72" s="77"/>
+      <c r="A72" s="91"/>
+      <c r="B72" s="94"/>
+      <c r="C72" s="116"/>
+      <c r="D72" s="117"/>
+      <c r="E72" s="116"/>
+      <c r="F72" s="117"/>
+      <c r="G72" s="116"/>
+      <c r="H72" s="117"/>
+      <c r="I72" s="116"/>
+      <c r="J72" s="117"/>
+      <c r="K72" s="98"/>
+      <c r="L72" s="99"/>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="36"/>
@@ -31476,18 +31476,18 @@
       <c r="R72" s="36"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="90"/>
-      <c r="B73" s="81"/>
-      <c r="C73" s="85"/>
-      <c r="D73" s="86"/>
-      <c r="E73" s="85"/>
-      <c r="F73" s="86"/>
-      <c r="G73" s="85"/>
-      <c r="H73" s="86"/>
-      <c r="I73" s="85"/>
-      <c r="J73" s="86"/>
-      <c r="K73" s="76"/>
-      <c r="L73" s="77"/>
+      <c r="A73" s="91"/>
+      <c r="B73" s="94"/>
+      <c r="C73" s="116"/>
+      <c r="D73" s="117"/>
+      <c r="E73" s="116"/>
+      <c r="F73" s="117"/>
+      <c r="G73" s="116"/>
+      <c r="H73" s="117"/>
+      <c r="I73" s="116"/>
+      <c r="J73" s="117"/>
+      <c r="K73" s="98"/>
+      <c r="L73" s="99"/>
       <c r="M73" s="36"/>
       <c r="N73" s="36"/>
       <c r="O73" s="36"/>
@@ -31496,18 +31496,18 @@
       <c r="R73" s="36"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="90"/>
-      <c r="B74" s="81"/>
-      <c r="C74" s="85"/>
-      <c r="D74" s="86"/>
-      <c r="E74" s="85"/>
-      <c r="F74" s="86"/>
-      <c r="G74" s="85"/>
-      <c r="H74" s="86"/>
-      <c r="I74" s="85"/>
-      <c r="J74" s="86"/>
-      <c r="K74" s="76"/>
-      <c r="L74" s="77"/>
+      <c r="A74" s="91"/>
+      <c r="B74" s="94"/>
+      <c r="C74" s="116"/>
+      <c r="D74" s="117"/>
+      <c r="E74" s="116"/>
+      <c r="F74" s="117"/>
+      <c r="G74" s="116"/>
+      <c r="H74" s="117"/>
+      <c r="I74" s="116"/>
+      <c r="J74" s="117"/>
+      <c r="K74" s="98"/>
+      <c r="L74" s="99"/>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="36"/>
@@ -31516,18 +31516,18 @@
       <c r="R74" s="36"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="91"/>
-      <c r="B75" s="82"/>
-      <c r="C75" s="87"/>
-      <c r="D75" s="88"/>
-      <c r="E75" s="87"/>
-      <c r="F75" s="88"/>
-      <c r="G75" s="87"/>
-      <c r="H75" s="88"/>
-      <c r="I75" s="87"/>
-      <c r="J75" s="88"/>
-      <c r="K75" s="78"/>
-      <c r="L75" s="79"/>
+      <c r="A75" s="92"/>
+      <c r="B75" s="95"/>
+      <c r="C75" s="118"/>
+      <c r="D75" s="119"/>
+      <c r="E75" s="118"/>
+      <c r="F75" s="119"/>
+      <c r="G75" s="118"/>
+      <c r="H75" s="119"/>
+      <c r="I75" s="118"/>
+      <c r="J75" s="119"/>
+      <c r="K75" s="100"/>
+      <c r="L75" s="101"/>
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="36"/>
@@ -31557,34 +31557,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A47:B50"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
-    <mergeCell ref="A51:A75"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:D55"/>
-    <mergeCell ref="E51:F55"/>
-    <mergeCell ref="G51:H55"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:D65"/>
-    <mergeCell ref="E61:F65"/>
-    <mergeCell ref="G61:H65"/>
-    <mergeCell ref="I51:J55"/>
-    <mergeCell ref="K51:L55"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:D60"/>
-    <mergeCell ref="E56:F60"/>
-    <mergeCell ref="G56:H60"/>
-    <mergeCell ref="I56:J60"/>
-    <mergeCell ref="K56:L60"/>
     <mergeCell ref="I61:J65"/>
     <mergeCell ref="K61:L65"/>
     <mergeCell ref="K71:L75"/>
@@ -31599,6 +31571,34 @@
     <mergeCell ref="E71:F75"/>
     <mergeCell ref="G71:H75"/>
     <mergeCell ref="I71:J75"/>
+    <mergeCell ref="I51:J55"/>
+    <mergeCell ref="K51:L55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:D60"/>
+    <mergeCell ref="E56:F60"/>
+    <mergeCell ref="G56:H60"/>
+    <mergeCell ref="I56:J60"/>
+    <mergeCell ref="K56:L60"/>
+    <mergeCell ref="A51:A75"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:D55"/>
+    <mergeCell ref="E51:F55"/>
+    <mergeCell ref="G51:H55"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:D65"/>
+    <mergeCell ref="E61:F65"/>
+    <mergeCell ref="G61:H65"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A47:B50"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -42974,30 +42974,30 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="21">
-      <c r="A33" s="114" t="s">
+      <c r="A33" s="120" t="s">
         <v>1047</v>
       </c>
-      <c r="B33" s="115"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="115"/>
-      <c r="F33" s="115"/>
-      <c r="G33" s="115"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
+      <c r="B33" s="121"/>
+      <c r="C33" s="121"/>
+      <c r="D33" s="121"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="121"/>
+      <c r="H33" s="121"/>
+      <c r="I33" s="121"/>
     </row>
     <row r="35" spans="1:9" ht="15.75">
-      <c r="A35" s="116" t="s">
+      <c r="A35" s="122" t="s">
         <v>1048</v>
       </c>
-      <c r="B35" s="115"/>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="115"/>
-      <c r="G35" s="115"/>
-      <c r="H35" s="115"/>
-      <c r="I35" s="115"/>
+      <c r="B35" s="121"/>
+      <c r="C35" s="121"/>
+      <c r="D35" s="121"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="121"/>
+      <c r="H35" s="121"/>
+      <c r="I35" s="121"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="22" t="s">
@@ -43450,11 +43450,11 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75">
-      <c r="A52" s="116" t="s">
+      <c r="A52" s="122" t="s">
         <v>1071</v>
       </c>
-      <c r="B52" s="115"/>
-      <c r="C52" s="115"/>
+      <c r="B52" s="121"/>
+      <c r="C52" s="121"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="22" t="s">
@@ -43552,11 +43552,11 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.75">
-      <c r="A63" s="116" t="s">
+      <c r="A63" s="122" t="s">
         <v>1081</v>
       </c>
-      <c r="B63" s="115"/>
-      <c r="C63" s="115"/>
+      <c r="B63" s="121"/>
+      <c r="C63" s="121"/>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="22" t="s">

--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -4205,6 +4205,96 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4269,96 +4359,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -30746,14 +30746,14 @@
       <c r="R40" s="36"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="98" t="s">
         <v>1117</v>
       </c>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68" t="s">
+      <c r="B41" s="98"/>
+      <c r="C41" s="98" t="s">
         <v>1118</v>
       </c>
-      <c r="D41" s="68"/>
+      <c r="D41" s="98"/>
       <c r="E41" s="37" t="s">
         <v>9</v>
       </c>
@@ -30774,10 +30774,10 @@
       <c r="R41" s="41"/>
     </row>
     <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="69"/>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
+      <c r="A42" s="99"/>
+      <c r="B42" s="99"/>
+      <c r="C42" s="99"/>
+      <c r="D42" s="99"/>
       <c r="E42" s="42"/>
       <c r="F42" s="36"/>
       <c r="G42" s="36"/>
@@ -30866,38 +30866,38 @@
       <c r="R46" s="45"/>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="70" t="s">
+      <c r="A47" s="100" t="s">
         <v>1093</v>
       </c>
-      <c r="B47" s="71"/>
-      <c r="C47" s="76" t="s">
+      <c r="B47" s="101"/>
+      <c r="C47" s="106" t="s">
         <v>1094</v>
       </c>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
-      <c r="F47" s="77"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="77"/>
-      <c r="J47" s="77"/>
-      <c r="K47" s="77"/>
-      <c r="L47" s="78"/>
+      <c r="D47" s="107"/>
+      <c r="E47" s="107"/>
+      <c r="F47" s="107"/>
+      <c r="G47" s="107"/>
+      <c r="H47" s="107"/>
+      <c r="I47" s="107"/>
+      <c r="J47" s="107"/>
+      <c r="K47" s="107"/>
+      <c r="L47" s="108"/>
       <c r="M47" s="36"/>
       <c r="N47" s="36"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="72"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="79"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="80"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="80"/>
-      <c r="J48" s="80"/>
-      <c r="K48" s="80"/>
-      <c r="L48" s="81"/>
+      <c r="A48" s="102"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="109"/>
+      <c r="D48" s="110"/>
+      <c r="E48" s="110"/>
+      <c r="F48" s="110"/>
+      <c r="G48" s="110"/>
+      <c r="H48" s="110"/>
+      <c r="I48" s="110"/>
+      <c r="J48" s="110"/>
+      <c r="K48" s="110"/>
+      <c r="L48" s="111"/>
       <c r="M48" s="36"/>
       <c r="N48" s="36"/>
       <c r="O48" s="39" t="s">
@@ -30908,28 +30908,28 @@
       <c r="R48" s="41"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="72"/>
-      <c r="B49" s="73"/>
-      <c r="C49" s="82" t="s">
+      <c r="A49" s="102"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="112" t="s">
         <v>1096</v>
       </c>
-      <c r="D49" s="83"/>
-      <c r="E49" s="82" t="s">
+      <c r="D49" s="113"/>
+      <c r="E49" s="112" t="s">
         <v>1097</v>
       </c>
-      <c r="F49" s="83"/>
-      <c r="G49" s="82" t="s">
+      <c r="F49" s="113"/>
+      <c r="G49" s="112" t="s">
         <v>1098</v>
       </c>
-      <c r="H49" s="83"/>
-      <c r="I49" s="86" t="s">
+      <c r="H49" s="113"/>
+      <c r="I49" s="116" t="s">
         <v>1099</v>
       </c>
-      <c r="J49" s="87"/>
-      <c r="K49" s="82" t="s">
+      <c r="J49" s="117"/>
+      <c r="K49" s="112" t="s">
         <v>1100</v>
       </c>
-      <c r="L49" s="83"/>
+      <c r="L49" s="113"/>
       <c r="M49" s="36"/>
       <c r="N49" s="36"/>
       <c r="O49" s="46" t="s">
@@ -30940,18 +30940,18 @@
       <c r="R49" s="41"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="74"/>
-      <c r="B50" s="75"/>
-      <c r="C50" s="84"/>
-      <c r="D50" s="85"/>
-      <c r="E50" s="84"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="85"/>
-      <c r="I50" s="88"/>
-      <c r="J50" s="89"/>
-      <c r="K50" s="84"/>
-      <c r="L50" s="85"/>
+      <c r="A50" s="104"/>
+      <c r="B50" s="105"/>
+      <c r="C50" s="114"/>
+      <c r="D50" s="115"/>
+      <c r="E50" s="114"/>
+      <c r="F50" s="115"/>
+      <c r="G50" s="114"/>
+      <c r="H50" s="115"/>
+      <c r="I50" s="118"/>
+      <c r="J50" s="119"/>
+      <c r="K50" s="114"/>
+      <c r="L50" s="115"/>
       <c r="M50" s="36"/>
       <c r="N50" s="36"/>
       <c r="O50" s="46" t="s">
@@ -30962,32 +30962,32 @@
       <c r="R50" s="41"/>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="90" t="s">
+      <c r="A51" s="95" t="s">
         <v>1103</v>
       </c>
-      <c r="B51" s="93" t="s">
+      <c r="B51" s="86" t="s">
         <v>1104</v>
       </c>
-      <c r="C51" s="96" t="s">
+      <c r="C51" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="97"/>
-      <c r="E51" s="102" t="s">
+      <c r="D51" s="81"/>
+      <c r="E51" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="103"/>
-      <c r="G51" s="108" t="s">
+      <c r="F51" s="69"/>
+      <c r="G51" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="109"/>
-      <c r="I51" s="108" t="s">
+      <c r="H51" s="75"/>
+      <c r="I51" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="109"/>
-      <c r="K51" s="108" t="s">
+      <c r="J51" s="75"/>
+      <c r="K51" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="109"/>
+      <c r="L51" s="75"/>
       <c r="M51" s="36"/>
       <c r="N51" s="36"/>
       <c r="O51" s="46" t="s">
@@ -30998,18 +30998,18 @@
       <c r="R51" s="41"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="91"/>
-      <c r="B52" s="94"/>
-      <c r="C52" s="98"/>
-      <c r="D52" s="99"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="110"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="110"/>
-      <c r="J52" s="111"/>
-      <c r="K52" s="110"/>
-      <c r="L52" s="111"/>
+      <c r="A52" s="96"/>
+      <c r="B52" s="87"/>
+      <c r="C52" s="82"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="76"/>
+      <c r="H52" s="77"/>
+      <c r="I52" s="76"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="76"/>
+      <c r="L52" s="77"/>
       <c r="M52" s="36"/>
       <c r="N52" s="36"/>
       <c r="O52" s="46" t="s">
@@ -31020,18 +31020,18 @@
       <c r="R52" s="41"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="91"/>
-      <c r="B53" s="94"/>
-      <c r="C53" s="98"/>
-      <c r="D53" s="99"/>
-      <c r="E53" s="104"/>
-      <c r="F53" s="105"/>
-      <c r="G53" s="110"/>
-      <c r="H53" s="111"/>
-      <c r="I53" s="110"/>
-      <c r="J53" s="111"/>
-      <c r="K53" s="110"/>
-      <c r="L53" s="111"/>
+      <c r="A53" s="96"/>
+      <c r="B53" s="87"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="77"/>
+      <c r="I53" s="76"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="76"/>
+      <c r="L53" s="77"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36"/>
       <c r="O53" s="43" t="s">
@@ -31042,34 +31042,34 @@
       <c r="R53" s="45"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="91"/>
-      <c r="B54" s="94"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="99"/>
-      <c r="E54" s="104"/>
-      <c r="F54" s="105"/>
-      <c r="G54" s="110"/>
-      <c r="H54" s="111"/>
-      <c r="I54" s="110"/>
-      <c r="J54" s="111"/>
-      <c r="K54" s="110"/>
-      <c r="L54" s="111"/>
+      <c r="A54" s="96"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="77"/>
+      <c r="I54" s="76"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="76"/>
+      <c r="L54" s="77"/>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="91"/>
-      <c r="B55" s="95"/>
-      <c r="C55" s="100"/>
-      <c r="D55" s="101"/>
-      <c r="E55" s="106"/>
-      <c r="F55" s="107"/>
-      <c r="G55" s="112"/>
-      <c r="H55" s="113"/>
-      <c r="I55" s="112"/>
-      <c r="J55" s="113"/>
-      <c r="K55" s="112"/>
-      <c r="L55" s="113"/>
+      <c r="A55" s="96"/>
+      <c r="B55" s="88"/>
+      <c r="C55" s="84"/>
+      <c r="D55" s="85"/>
+      <c r="E55" s="72"/>
+      <c r="F55" s="73"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="79"/>
+      <c r="I55" s="78"/>
+      <c r="J55" s="79"/>
+      <c r="K55" s="78"/>
+      <c r="L55" s="79"/>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
       <c r="O55" s="39" t="s">
@@ -31080,30 +31080,30 @@
       <c r="R55" s="41"/>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="91"/>
-      <c r="B56" s="93" t="s">
+      <c r="A56" s="96"/>
+      <c r="B56" s="86" t="s">
         <v>1109</v>
       </c>
-      <c r="C56" s="96" t="s">
+      <c r="C56" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="97"/>
-      <c r="E56" s="102" t="s">
+      <c r="D56" s="81"/>
+      <c r="E56" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="103"/>
-      <c r="G56" s="102" t="s">
+      <c r="F56" s="69"/>
+      <c r="G56" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="103"/>
-      <c r="I56" s="108" t="s">
+      <c r="H56" s="69"/>
+      <c r="I56" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="109"/>
-      <c r="K56" s="108" t="s">
+      <c r="J56" s="75"/>
+      <c r="K56" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="109"/>
+      <c r="L56" s="75"/>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
       <c r="O56" s="46" t="s">
@@ -31114,18 +31114,18 @@
       <c r="R56" s="41"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="91"/>
-      <c r="B57" s="94"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="99"/>
-      <c r="E57" s="104"/>
-      <c r="F57" s="105"/>
-      <c r="G57" s="104"/>
-      <c r="H57" s="105"/>
-      <c r="I57" s="110"/>
-      <c r="J57" s="111"/>
-      <c r="K57" s="110"/>
-      <c r="L57" s="111"/>
+      <c r="A57" s="96"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="82"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="76"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="76"/>
+      <c r="L57" s="77"/>
       <c r="M57" s="36"/>
       <c r="N57" s="36"/>
       <c r="O57" s="46" t="s">
@@ -31136,18 +31136,18 @@
       <c r="R57" s="41"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="91"/>
-      <c r="B58" s="94"/>
-      <c r="C58" s="98"/>
-      <c r="D58" s="99"/>
-      <c r="E58" s="104"/>
-      <c r="F58" s="105"/>
-      <c r="G58" s="104"/>
-      <c r="H58" s="105"/>
-      <c r="I58" s="110"/>
-      <c r="J58" s="111"/>
-      <c r="K58" s="110"/>
-      <c r="L58" s="111"/>
+      <c r="A58" s="96"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="70"/>
+      <c r="F58" s="71"/>
+      <c r="G58" s="70"/>
+      <c r="H58" s="71"/>
+      <c r="I58" s="76"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="76"/>
+      <c r="L58" s="77"/>
       <c r="M58" s="36"/>
       <c r="N58" s="36"/>
       <c r="O58" s="46" t="s">
@@ -31158,18 +31158,18 @@
       <c r="R58" s="41"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="91"/>
-      <c r="B59" s="94"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="99"/>
-      <c r="E59" s="104"/>
-      <c r="F59" s="105"/>
-      <c r="G59" s="104"/>
-      <c r="H59" s="105"/>
-      <c r="I59" s="110"/>
-      <c r="J59" s="111"/>
-      <c r="K59" s="110"/>
-      <c r="L59" s="111"/>
+      <c r="A59" s="96"/>
+      <c r="B59" s="87"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="71"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="76"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="76"/>
+      <c r="L59" s="77"/>
       <c r="M59" s="36"/>
       <c r="N59" s="36"/>
       <c r="O59" s="43" t="s">
@@ -31180,18 +31180,18 @@
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="91"/>
-      <c r="B60" s="95"/>
-      <c r="C60" s="100"/>
-      <c r="D60" s="101"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="107"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="107"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="112"/>
-      <c r="L60" s="113"/>
+      <c r="A60" s="96"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="84"/>
+      <c r="D60" s="85"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="73"/>
+      <c r="G60" s="72"/>
+      <c r="H60" s="73"/>
+      <c r="I60" s="78"/>
+      <c r="J60" s="79"/>
+      <c r="K60" s="78"/>
+      <c r="L60" s="79"/>
       <c r="M60" s="36"/>
       <c r="N60" s="36"/>
       <c r="O60" s="36"/>
@@ -31200,30 +31200,30 @@
       <c r="R60" s="36"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="91"/>
-      <c r="B61" s="93" t="s">
+      <c r="A61" s="96"/>
+      <c r="B61" s="86" t="s">
         <v>1114</v>
       </c>
-      <c r="C61" s="114" t="s">
+      <c r="C61" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="115"/>
-      <c r="E61" s="96" t="s">
+      <c r="D61" s="90"/>
+      <c r="E61" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="97"/>
-      <c r="G61" s="102" t="s">
+      <c r="F61" s="81"/>
+      <c r="G61" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="103"/>
-      <c r="I61" s="102" t="s">
+      <c r="H61" s="69"/>
+      <c r="I61" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="103"/>
-      <c r="K61" s="108" t="s">
+      <c r="J61" s="69"/>
+      <c r="K61" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="109"/>
+      <c r="L61" s="75"/>
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
       <c r="O61" s="36"/>
@@ -31232,18 +31232,18 @@
       <c r="R61" s="36"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="91"/>
-      <c r="B62" s="94"/>
-      <c r="C62" s="116"/>
-      <c r="D62" s="117"/>
-      <c r="E62" s="98"/>
-      <c r="F62" s="99"/>
-      <c r="G62" s="104"/>
-      <c r="H62" s="105"/>
-      <c r="I62" s="104"/>
-      <c r="J62" s="105"/>
-      <c r="K62" s="110"/>
-      <c r="L62" s="111"/>
+      <c r="A62" s="96"/>
+      <c r="B62" s="87"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="82"/>
+      <c r="F62" s="83"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="71"/>
+      <c r="I62" s="70"/>
+      <c r="J62" s="71"/>
+      <c r="K62" s="76"/>
+      <c r="L62" s="77"/>
       <c r="M62" s="36"/>
       <c r="N62" s="36"/>
       <c r="O62" s="36"/>
@@ -31252,18 +31252,18 @@
       <c r="R62" s="36"/>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="91"/>
-      <c r="B63" s="94"/>
-      <c r="C63" s="116"/>
-      <c r="D63" s="117"/>
-      <c r="E63" s="98"/>
-      <c r="F63" s="99"/>
-      <c r="G63" s="104"/>
-      <c r="H63" s="105"/>
-      <c r="I63" s="104"/>
-      <c r="J63" s="105"/>
-      <c r="K63" s="110"/>
-      <c r="L63" s="111"/>
+      <c r="A63" s="96"/>
+      <c r="B63" s="87"/>
+      <c r="C63" s="91"/>
+      <c r="D63" s="92"/>
+      <c r="E63" s="82"/>
+      <c r="F63" s="83"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="71"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="71"/>
+      <c r="K63" s="76"/>
+      <c r="L63" s="77"/>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
       <c r="O63" s="36"/>
@@ -31272,18 +31272,18 @@
       <c r="R63" s="36"/>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="91"/>
-      <c r="B64" s="94"/>
-      <c r="C64" s="116"/>
-      <c r="D64" s="117"/>
-      <c r="E64" s="98"/>
-      <c r="F64" s="99"/>
-      <c r="G64" s="104"/>
-      <c r="H64" s="105"/>
-      <c r="I64" s="104"/>
-      <c r="J64" s="105"/>
-      <c r="K64" s="110"/>
-      <c r="L64" s="111"/>
+      <c r="A64" s="96"/>
+      <c r="B64" s="87"/>
+      <c r="C64" s="91"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="82"/>
+      <c r="F64" s="83"/>
+      <c r="G64" s="70"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="70"/>
+      <c r="J64" s="71"/>
+      <c r="K64" s="76"/>
+      <c r="L64" s="77"/>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
       <c r="O64" s="36"/>
@@ -31292,18 +31292,18 @@
       <c r="R64" s="36"/>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="91"/>
-      <c r="B65" s="95"/>
-      <c r="C65" s="118"/>
-      <c r="D65" s="119"/>
-      <c r="E65" s="100"/>
-      <c r="F65" s="101"/>
-      <c r="G65" s="106"/>
-      <c r="H65" s="107"/>
-      <c r="I65" s="106"/>
-      <c r="J65" s="107"/>
-      <c r="K65" s="112"/>
-      <c r="L65" s="113"/>
+      <c r="A65" s="96"/>
+      <c r="B65" s="88"/>
+      <c r="C65" s="93"/>
+      <c r="D65" s="94"/>
+      <c r="E65" s="84"/>
+      <c r="F65" s="85"/>
+      <c r="G65" s="72"/>
+      <c r="H65" s="73"/>
+      <c r="I65" s="72"/>
+      <c r="J65" s="73"/>
+      <c r="K65" s="78"/>
+      <c r="L65" s="79"/>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
       <c r="O65" s="36"/>
@@ -31312,30 +31312,30 @@
       <c r="R65" s="36"/>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="91"/>
-      <c r="B66" s="93" t="s">
+      <c r="A66" s="96"/>
+      <c r="B66" s="86" t="s">
         <v>1115</v>
       </c>
-      <c r="C66" s="114" t="s">
+      <c r="C66" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="115"/>
-      <c r="E66" s="114" t="s">
+      <c r="D66" s="90"/>
+      <c r="E66" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="115"/>
-      <c r="G66" s="96" t="s">
+      <c r="F66" s="90"/>
+      <c r="G66" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="97"/>
-      <c r="I66" s="96" t="s">
+      <c r="H66" s="81"/>
+      <c r="I66" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="97"/>
-      <c r="K66" s="102" t="s">
+      <c r="J66" s="81"/>
+      <c r="K66" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="103"/>
+      <c r="L66" s="69"/>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
       <c r="O66" s="36"/>
@@ -31344,18 +31344,18 @@
       <c r="R66" s="36"/>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="91"/>
-      <c r="B67" s="94"/>
-      <c r="C67" s="116"/>
-      <c r="D67" s="117"/>
-      <c r="E67" s="116"/>
-      <c r="F67" s="117"/>
-      <c r="G67" s="98"/>
-      <c r="H67" s="99"/>
-      <c r="I67" s="98"/>
-      <c r="J67" s="99"/>
-      <c r="K67" s="104"/>
-      <c r="L67" s="105"/>
+      <c r="A67" s="96"/>
+      <c r="B67" s="87"/>
+      <c r="C67" s="91"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="91"/>
+      <c r="F67" s="92"/>
+      <c r="G67" s="82"/>
+      <c r="H67" s="83"/>
+      <c r="I67" s="82"/>
+      <c r="J67" s="83"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="71"/>
       <c r="M67" s="36"/>
       <c r="N67" s="36"/>
       <c r="O67" s="36"/>
@@ -31364,18 +31364,18 @@
       <c r="R67" s="36"/>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="91"/>
-      <c r="B68" s="94"/>
-      <c r="C68" s="116"/>
-      <c r="D68" s="117"/>
-      <c r="E68" s="116"/>
-      <c r="F68" s="117"/>
-      <c r="G68" s="98"/>
-      <c r="H68" s="99"/>
-      <c r="I68" s="98"/>
-      <c r="J68" s="99"/>
-      <c r="K68" s="104"/>
-      <c r="L68" s="105"/>
+      <c r="A68" s="96"/>
+      <c r="B68" s="87"/>
+      <c r="C68" s="91"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="91"/>
+      <c r="F68" s="92"/>
+      <c r="G68" s="82"/>
+      <c r="H68" s="83"/>
+      <c r="I68" s="82"/>
+      <c r="J68" s="83"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="71"/>
       <c r="M68" s="36"/>
       <c r="N68" s="36"/>
       <c r="O68" s="36"/>
@@ -31384,18 +31384,18 @@
       <c r="R68" s="36"/>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="91"/>
-      <c r="B69" s="94"/>
-      <c r="C69" s="116"/>
-      <c r="D69" s="117"/>
-      <c r="E69" s="116"/>
-      <c r="F69" s="117"/>
-      <c r="G69" s="98"/>
-      <c r="H69" s="99"/>
-      <c r="I69" s="98"/>
-      <c r="J69" s="99"/>
-      <c r="K69" s="104"/>
-      <c r="L69" s="105"/>
+      <c r="A69" s="96"/>
+      <c r="B69" s="87"/>
+      <c r="C69" s="91"/>
+      <c r="D69" s="92"/>
+      <c r="E69" s="91"/>
+      <c r="F69" s="92"/>
+      <c r="G69" s="82"/>
+      <c r="H69" s="83"/>
+      <c r="I69" s="82"/>
+      <c r="J69" s="83"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="71"/>
       <c r="M69" s="36"/>
       <c r="N69" s="36"/>
       <c r="O69" s="36"/>
@@ -31404,18 +31404,18 @@
       <c r="R69" s="36"/>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="91"/>
-      <c r="B70" s="95"/>
-      <c r="C70" s="118"/>
-      <c r="D70" s="119"/>
-      <c r="E70" s="118"/>
-      <c r="F70" s="119"/>
-      <c r="G70" s="100"/>
-      <c r="H70" s="101"/>
-      <c r="I70" s="100"/>
-      <c r="J70" s="101"/>
-      <c r="K70" s="106"/>
-      <c r="L70" s="107"/>
+      <c r="A70" s="96"/>
+      <c r="B70" s="88"/>
+      <c r="C70" s="93"/>
+      <c r="D70" s="94"/>
+      <c r="E70" s="93"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="84"/>
+      <c r="H70" s="85"/>
+      <c r="I70" s="84"/>
+      <c r="J70" s="85"/>
+      <c r="K70" s="72"/>
+      <c r="L70" s="73"/>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="36"/>
@@ -31424,30 +31424,30 @@
       <c r="R70" s="36"/>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="91"/>
-      <c r="B71" s="93" t="s">
+      <c r="A71" s="96"/>
+      <c r="B71" s="86" t="s">
         <v>1116</v>
       </c>
-      <c r="C71" s="114" t="s">
+      <c r="C71" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="115"/>
-      <c r="E71" s="114" t="s">
+      <c r="D71" s="90"/>
+      <c r="E71" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="115"/>
-      <c r="G71" s="114" t="s">
+      <c r="F71" s="90"/>
+      <c r="G71" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="H71" s="115"/>
-      <c r="I71" s="114" t="s">
+      <c r="H71" s="90"/>
+      <c r="I71" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="115"/>
-      <c r="K71" s="96" t="s">
+      <c r="J71" s="90"/>
+      <c r="K71" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="97"/>
+      <c r="L71" s="81"/>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="36"/>
@@ -31456,18 +31456,18 @@
       <c r="R71" s="36"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="91"/>
-      <c r="B72" s="94"/>
-      <c r="C72" s="116"/>
-      <c r="D72" s="117"/>
-      <c r="E72" s="116"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="116"/>
-      <c r="H72" s="117"/>
-      <c r="I72" s="116"/>
-      <c r="J72" s="117"/>
-      <c r="K72" s="98"/>
-      <c r="L72" s="99"/>
+      <c r="A72" s="96"/>
+      <c r="B72" s="87"/>
+      <c r="C72" s="91"/>
+      <c r="D72" s="92"/>
+      <c r="E72" s="91"/>
+      <c r="F72" s="92"/>
+      <c r="G72" s="91"/>
+      <c r="H72" s="92"/>
+      <c r="I72" s="91"/>
+      <c r="J72" s="92"/>
+      <c r="K72" s="82"/>
+      <c r="L72" s="83"/>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="36"/>
@@ -31476,18 +31476,18 @@
       <c r="R72" s="36"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="91"/>
-      <c r="B73" s="94"/>
-      <c r="C73" s="116"/>
-      <c r="D73" s="117"/>
-      <c r="E73" s="116"/>
-      <c r="F73" s="117"/>
-      <c r="G73" s="116"/>
-      <c r="H73" s="117"/>
-      <c r="I73" s="116"/>
-      <c r="J73" s="117"/>
-      <c r="K73" s="98"/>
-      <c r="L73" s="99"/>
+      <c r="A73" s="96"/>
+      <c r="B73" s="87"/>
+      <c r="C73" s="91"/>
+      <c r="D73" s="92"/>
+      <c r="E73" s="91"/>
+      <c r="F73" s="92"/>
+      <c r="G73" s="91"/>
+      <c r="H73" s="92"/>
+      <c r="I73" s="91"/>
+      <c r="J73" s="92"/>
+      <c r="K73" s="82"/>
+      <c r="L73" s="83"/>
       <c r="M73" s="36"/>
       <c r="N73" s="36"/>
       <c r="O73" s="36"/>
@@ -31496,18 +31496,18 @@
       <c r="R73" s="36"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="91"/>
-      <c r="B74" s="94"/>
-      <c r="C74" s="116"/>
-      <c r="D74" s="117"/>
-      <c r="E74" s="116"/>
-      <c r="F74" s="117"/>
-      <c r="G74" s="116"/>
-      <c r="H74" s="117"/>
-      <c r="I74" s="116"/>
-      <c r="J74" s="117"/>
-      <c r="K74" s="98"/>
-      <c r="L74" s="99"/>
+      <c r="A74" s="96"/>
+      <c r="B74" s="87"/>
+      <c r="C74" s="91"/>
+      <c r="D74" s="92"/>
+      <c r="E74" s="91"/>
+      <c r="F74" s="92"/>
+      <c r="G74" s="91"/>
+      <c r="H74" s="92"/>
+      <c r="I74" s="91"/>
+      <c r="J74" s="92"/>
+      <c r="K74" s="82"/>
+      <c r="L74" s="83"/>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="36"/>
@@ -31516,18 +31516,18 @@
       <c r="R74" s="36"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="92"/>
-      <c r="B75" s="95"/>
-      <c r="C75" s="118"/>
-      <c r="D75" s="119"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="119"/>
-      <c r="G75" s="118"/>
-      <c r="H75" s="119"/>
-      <c r="I75" s="118"/>
-      <c r="J75" s="119"/>
-      <c r="K75" s="100"/>
-      <c r="L75" s="101"/>
+      <c r="A75" s="97"/>
+      <c r="B75" s="88"/>
+      <c r="C75" s="93"/>
+      <c r="D75" s="94"/>
+      <c r="E75" s="93"/>
+      <c r="F75" s="94"/>
+      <c r="G75" s="93"/>
+      <c r="H75" s="94"/>
+      <c r="I75" s="93"/>
+      <c r="J75" s="94"/>
+      <c r="K75" s="84"/>
+      <c r="L75" s="85"/>
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="36"/>
@@ -31557,6 +31557,34 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A47:B50"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A51:A75"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:D55"/>
+    <mergeCell ref="E51:F55"/>
+    <mergeCell ref="G51:H55"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:D65"/>
+    <mergeCell ref="E61:F65"/>
+    <mergeCell ref="G61:H65"/>
+    <mergeCell ref="I51:J55"/>
+    <mergeCell ref="K51:L55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:D60"/>
+    <mergeCell ref="E56:F60"/>
+    <mergeCell ref="G56:H60"/>
+    <mergeCell ref="I56:J60"/>
+    <mergeCell ref="K56:L60"/>
     <mergeCell ref="I61:J65"/>
     <mergeCell ref="K61:L65"/>
     <mergeCell ref="K71:L75"/>
@@ -31571,34 +31599,6 @@
     <mergeCell ref="E71:F75"/>
     <mergeCell ref="G71:H75"/>
     <mergeCell ref="I71:J75"/>
-    <mergeCell ref="I51:J55"/>
-    <mergeCell ref="K51:L55"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:D60"/>
-    <mergeCell ref="E56:F60"/>
-    <mergeCell ref="G56:H60"/>
-    <mergeCell ref="I56:J60"/>
-    <mergeCell ref="K56:L60"/>
-    <mergeCell ref="A51:A75"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:D55"/>
-    <mergeCell ref="E51:F55"/>
-    <mergeCell ref="G51:H55"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:D65"/>
-    <mergeCell ref="E61:F65"/>
-    <mergeCell ref="G61:H65"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A47:B50"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehrnia\Desktop\Job\AtlasCopco\Business Analysis Project and Stakeholder Management\Excel_PLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92812D2F-DF46-43C4-993C-89D7BAC8C2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB58BE1-30A5-4FC5-BAF8-247823352BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="1130">
   <si>
     <t>Description</t>
   </si>
@@ -3463,6 +3463,9 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-Site Pressure Reducing &amp; Power Generation </t>
+  </si>
+  <si>
+    <t>PROJECT Manager: Majid Mehrnia</t>
   </si>
 </sst>
 </file>
@@ -3756,7 +3759,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3864,6 +3867,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4068,7 +4077,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -4213,96 +4222,6 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4369,6 +4288,96 @@
     <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4376,6 +4385,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -12892,6 +12902,12 @@
       <c r="Y2" s="63"/>
     </row>
     <row r="3" spans="1:25">
+      <c r="D3" s="125" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
       <c r="M3" s="69" t="s">
         <v>1124</v>
       </c>
@@ -12932,7 +12948,8 @@
     <mergeCell ref="M4:W4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -30762,14 +30779,14 @@
       <c r="R40" s="36"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="100" t="s">
+      <c r="A41" s="70" t="s">
         <v>1115</v>
       </c>
-      <c r="B41" s="100"/>
-      <c r="C41" s="100" t="s">
+      <c r="B41" s="70"/>
+      <c r="C41" s="70" t="s">
         <v>1116</v>
       </c>
-      <c r="D41" s="100"/>
+      <c r="D41" s="70"/>
       <c r="E41" s="37" t="s">
         <v>9</v>
       </c>
@@ -30790,10 +30807,10 @@
       <c r="R41" s="41"/>
     </row>
     <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="101"/>
-      <c r="B42" s="101"/>
-      <c r="C42" s="101"/>
-      <c r="D42" s="101"/>
+      <c r="A42" s="71"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
       <c r="E42" s="42"/>
       <c r="F42" s="36"/>
       <c r="G42" s="36"/>
@@ -30882,38 +30899,38 @@
       <c r="R46" s="45"/>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="102" t="s">
+      <c r="A47" s="72" t="s">
         <v>1091</v>
       </c>
-      <c r="B47" s="103"/>
-      <c r="C47" s="108" t="s">
+      <c r="B47" s="73"/>
+      <c r="C47" s="78" t="s">
         <v>1092</v>
       </c>
-      <c r="D47" s="109"/>
-      <c r="E47" s="109"/>
-      <c r="F47" s="109"/>
-      <c r="G47" s="109"/>
-      <c r="H47" s="109"/>
-      <c r="I47" s="109"/>
-      <c r="J47" s="109"/>
-      <c r="K47" s="109"/>
-      <c r="L47" s="110"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="79"/>
+      <c r="J47" s="79"/>
+      <c r="K47" s="79"/>
+      <c r="L47" s="80"/>
       <c r="M47" s="36"/>
       <c r="N47" s="36"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="104"/>
-      <c r="B48" s="105"/>
-      <c r="C48" s="111"/>
-      <c r="D48" s="112"/>
-      <c r="E48" s="112"/>
-      <c r="F48" s="112"/>
-      <c r="G48" s="112"/>
-      <c r="H48" s="112"/>
-      <c r="I48" s="112"/>
-      <c r="J48" s="112"/>
-      <c r="K48" s="112"/>
-      <c r="L48" s="113"/>
+      <c r="A48" s="74"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="82"/>
+      <c r="E48" s="82"/>
+      <c r="F48" s="82"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="82"/>
+      <c r="I48" s="82"/>
+      <c r="J48" s="82"/>
+      <c r="K48" s="82"/>
+      <c r="L48" s="83"/>
       <c r="M48" s="36"/>
       <c r="N48" s="36"/>
       <c r="O48" s="39" t="s">
@@ -30924,28 +30941,28 @@
       <c r="R48" s="41"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="104"/>
-      <c r="B49" s="105"/>
-      <c r="C49" s="114" t="s">
+      <c r="A49" s="74"/>
+      <c r="B49" s="75"/>
+      <c r="C49" s="84" t="s">
         <v>1094</v>
       </c>
-      <c r="D49" s="115"/>
-      <c r="E49" s="114" t="s">
+      <c r="D49" s="85"/>
+      <c r="E49" s="84" t="s">
         <v>1095</v>
       </c>
-      <c r="F49" s="115"/>
-      <c r="G49" s="114" t="s">
+      <c r="F49" s="85"/>
+      <c r="G49" s="84" t="s">
         <v>1096</v>
       </c>
-      <c r="H49" s="115"/>
-      <c r="I49" s="118" t="s">
+      <c r="H49" s="85"/>
+      <c r="I49" s="88" t="s">
         <v>1097</v>
       </c>
-      <c r="J49" s="119"/>
-      <c r="K49" s="114" t="s">
+      <c r="J49" s="89"/>
+      <c r="K49" s="84" t="s">
         <v>1098</v>
       </c>
-      <c r="L49" s="115"/>
+      <c r="L49" s="85"/>
       <c r="M49" s="36"/>
       <c r="N49" s="36"/>
       <c r="O49" s="46" t="s">
@@ -30956,18 +30973,18 @@
       <c r="R49" s="41"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="106"/>
-      <c r="B50" s="107"/>
-      <c r="C50" s="116"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="116"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="116"/>
-      <c r="H50" s="117"/>
-      <c r="I50" s="120"/>
-      <c r="J50" s="121"/>
-      <c r="K50" s="116"/>
-      <c r="L50" s="117"/>
+      <c r="A50" s="76"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="86"/>
+      <c r="F50" s="87"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="87"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="91"/>
+      <c r="K50" s="86"/>
+      <c r="L50" s="87"/>
       <c r="M50" s="36"/>
       <c r="N50" s="36"/>
       <c r="O50" s="46" t="s">
@@ -30978,32 +30995,32 @@
       <c r="R50" s="41"/>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="97" t="s">
+      <c r="A51" s="92" t="s">
         <v>1101</v>
       </c>
-      <c r="B51" s="88" t="s">
+      <c r="B51" s="95" t="s">
         <v>1102</v>
       </c>
-      <c r="C51" s="82" t="s">
+      <c r="C51" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="70" t="s">
+      <c r="D51" s="99"/>
+      <c r="E51" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="71"/>
-      <c r="G51" s="76" t="s">
+      <c r="F51" s="105"/>
+      <c r="G51" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="77"/>
-      <c r="I51" s="76" t="s">
+      <c r="H51" s="111"/>
+      <c r="I51" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="77"/>
-      <c r="K51" s="76" t="s">
+      <c r="J51" s="111"/>
+      <c r="K51" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="77"/>
+      <c r="L51" s="111"/>
       <c r="M51" s="36"/>
       <c r="N51" s="36"/>
       <c r="O51" s="46" t="s">
@@ -31014,18 +31031,18 @@
       <c r="R51" s="41"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="98"/>
-      <c r="B52" s="89"/>
-      <c r="C52" s="84"/>
-      <c r="D52" s="85"/>
-      <c r="E52" s="72"/>
-      <c r="F52" s="73"/>
-      <c r="G52" s="78"/>
-      <c r="H52" s="79"/>
-      <c r="I52" s="78"/>
-      <c r="J52" s="79"/>
-      <c r="K52" s="78"/>
-      <c r="L52" s="79"/>
+      <c r="A52" s="93"/>
+      <c r="B52" s="96"/>
+      <c r="C52" s="100"/>
+      <c r="D52" s="101"/>
+      <c r="E52" s="106"/>
+      <c r="F52" s="107"/>
+      <c r="G52" s="112"/>
+      <c r="H52" s="113"/>
+      <c r="I52" s="112"/>
+      <c r="J52" s="113"/>
+      <c r="K52" s="112"/>
+      <c r="L52" s="113"/>
       <c r="M52" s="36"/>
       <c r="N52" s="36"/>
       <c r="O52" s="46" t="s">
@@ -31036,18 +31053,18 @@
       <c r="R52" s="41"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="98"/>
-      <c r="B53" s="89"/>
-      <c r="C53" s="84"/>
-      <c r="D53" s="85"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="73"/>
-      <c r="G53" s="78"/>
-      <c r="H53" s="79"/>
-      <c r="I53" s="78"/>
-      <c r="J53" s="79"/>
-      <c r="K53" s="78"/>
-      <c r="L53" s="79"/>
+      <c r="A53" s="93"/>
+      <c r="B53" s="96"/>
+      <c r="C53" s="100"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="106"/>
+      <c r="F53" s="107"/>
+      <c r="G53" s="112"/>
+      <c r="H53" s="113"/>
+      <c r="I53" s="112"/>
+      <c r="J53" s="113"/>
+      <c r="K53" s="112"/>
+      <c r="L53" s="113"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36"/>
       <c r="O53" s="43" t="s">
@@ -31058,34 +31075,34 @@
       <c r="R53" s="45"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="98"/>
-      <c r="B54" s="89"/>
-      <c r="C54" s="84"/>
-      <c r="D54" s="85"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="78"/>
-      <c r="H54" s="79"/>
-      <c r="I54" s="78"/>
-      <c r="J54" s="79"/>
-      <c r="K54" s="78"/>
-      <c r="L54" s="79"/>
+      <c r="A54" s="93"/>
+      <c r="B54" s="96"/>
+      <c r="C54" s="100"/>
+      <c r="D54" s="101"/>
+      <c r="E54" s="106"/>
+      <c r="F54" s="107"/>
+      <c r="G54" s="112"/>
+      <c r="H54" s="113"/>
+      <c r="I54" s="112"/>
+      <c r="J54" s="113"/>
+      <c r="K54" s="112"/>
+      <c r="L54" s="113"/>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="98"/>
-      <c r="B55" s="90"/>
-      <c r="C55" s="86"/>
-      <c r="D55" s="87"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="75"/>
-      <c r="G55" s="80"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="80"/>
-      <c r="J55" s="81"/>
-      <c r="K55" s="80"/>
-      <c r="L55" s="81"/>
+      <c r="A55" s="93"/>
+      <c r="B55" s="97"/>
+      <c r="C55" s="102"/>
+      <c r="D55" s="103"/>
+      <c r="E55" s="108"/>
+      <c r="F55" s="109"/>
+      <c r="G55" s="114"/>
+      <c r="H55" s="115"/>
+      <c r="I55" s="114"/>
+      <c r="J55" s="115"/>
+      <c r="K55" s="114"/>
+      <c r="L55" s="115"/>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
       <c r="O55" s="39" t="s">
@@ -31096,30 +31113,30 @@
       <c r="R55" s="41"/>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="98"/>
-      <c r="B56" s="88" t="s">
+      <c r="A56" s="93"/>
+      <c r="B56" s="95" t="s">
         <v>1107</v>
       </c>
-      <c r="C56" s="82" t="s">
+      <c r="C56" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="83"/>
-      <c r="E56" s="70" t="s">
+      <c r="D56" s="99"/>
+      <c r="E56" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="71"/>
-      <c r="G56" s="70" t="s">
+      <c r="F56" s="105"/>
+      <c r="G56" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="71"/>
-      <c r="I56" s="76" t="s">
+      <c r="H56" s="105"/>
+      <c r="I56" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="77"/>
-      <c r="K56" s="76" t="s">
+      <c r="J56" s="111"/>
+      <c r="K56" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="77"/>
+      <c r="L56" s="111"/>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
       <c r="O56" s="46" t="s">
@@ -31130,18 +31147,18 @@
       <c r="R56" s="41"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="98"/>
-      <c r="B57" s="89"/>
-      <c r="C57" s="84"/>
-      <c r="D57" s="85"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="73"/>
-      <c r="G57" s="72"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="78"/>
-      <c r="J57" s="79"/>
-      <c r="K57" s="78"/>
-      <c r="L57" s="79"/>
+      <c r="A57" s="93"/>
+      <c r="B57" s="96"/>
+      <c r="C57" s="100"/>
+      <c r="D57" s="101"/>
+      <c r="E57" s="106"/>
+      <c r="F57" s="107"/>
+      <c r="G57" s="106"/>
+      <c r="H57" s="107"/>
+      <c r="I57" s="112"/>
+      <c r="J57" s="113"/>
+      <c r="K57" s="112"/>
+      <c r="L57" s="113"/>
       <c r="M57" s="36"/>
       <c r="N57" s="36"/>
       <c r="O57" s="46" t="s">
@@ -31152,18 +31169,18 @@
       <c r="R57" s="41"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="98"/>
-      <c r="B58" s="89"/>
-      <c r="C58" s="84"/>
-      <c r="D58" s="85"/>
-      <c r="E58" s="72"/>
-      <c r="F58" s="73"/>
-      <c r="G58" s="72"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="78"/>
-      <c r="J58" s="79"/>
-      <c r="K58" s="78"/>
-      <c r="L58" s="79"/>
+      <c r="A58" s="93"/>
+      <c r="B58" s="96"/>
+      <c r="C58" s="100"/>
+      <c r="D58" s="101"/>
+      <c r="E58" s="106"/>
+      <c r="F58" s="107"/>
+      <c r="G58" s="106"/>
+      <c r="H58" s="107"/>
+      <c r="I58" s="112"/>
+      <c r="J58" s="113"/>
+      <c r="K58" s="112"/>
+      <c r="L58" s="113"/>
       <c r="M58" s="36"/>
       <c r="N58" s="36"/>
       <c r="O58" s="46" t="s">
@@ -31174,18 +31191,18 @@
       <c r="R58" s="41"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="98"/>
-      <c r="B59" s="89"/>
-      <c r="C59" s="84"/>
-      <c r="D59" s="85"/>
-      <c r="E59" s="72"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="72"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="78"/>
-      <c r="J59" s="79"/>
-      <c r="K59" s="78"/>
-      <c r="L59" s="79"/>
+      <c r="A59" s="93"/>
+      <c r="B59" s="96"/>
+      <c r="C59" s="100"/>
+      <c r="D59" s="101"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="107"/>
+      <c r="G59" s="106"/>
+      <c r="H59" s="107"/>
+      <c r="I59" s="112"/>
+      <c r="J59" s="113"/>
+      <c r="K59" s="112"/>
+      <c r="L59" s="113"/>
       <c r="M59" s="36"/>
       <c r="N59" s="36"/>
       <c r="O59" s="43" t="s">
@@ -31196,18 +31213,18 @@
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="98"/>
-      <c r="B60" s="90"/>
-      <c r="C60" s="86"/>
-      <c r="D60" s="87"/>
-      <c r="E60" s="74"/>
-      <c r="F60" s="75"/>
-      <c r="G60" s="74"/>
-      <c r="H60" s="75"/>
-      <c r="I60" s="80"/>
-      <c r="J60" s="81"/>
-      <c r="K60" s="80"/>
-      <c r="L60" s="81"/>
+      <c r="A60" s="93"/>
+      <c r="B60" s="97"/>
+      <c r="C60" s="102"/>
+      <c r="D60" s="103"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="115"/>
+      <c r="K60" s="114"/>
+      <c r="L60" s="115"/>
       <c r="M60" s="36"/>
       <c r="N60" s="36"/>
       <c r="O60" s="36"/>
@@ -31216,30 +31233,30 @@
       <c r="R60" s="36"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="98"/>
-      <c r="B61" s="88" t="s">
+      <c r="A61" s="93"/>
+      <c r="B61" s="95" t="s">
         <v>1112</v>
       </c>
-      <c r="C61" s="91" t="s">
+      <c r="C61" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="92"/>
-      <c r="E61" s="82" t="s">
+      <c r="D61" s="117"/>
+      <c r="E61" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="83"/>
-      <c r="G61" s="70" t="s">
+      <c r="F61" s="99"/>
+      <c r="G61" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="71"/>
-      <c r="I61" s="70" t="s">
+      <c r="H61" s="105"/>
+      <c r="I61" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="71"/>
-      <c r="K61" s="76" t="s">
+      <c r="J61" s="105"/>
+      <c r="K61" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="77"/>
+      <c r="L61" s="111"/>
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
       <c r="O61" s="36"/>
@@ -31248,18 +31265,18 @@
       <c r="R61" s="36"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="98"/>
-      <c r="B62" s="89"/>
-      <c r="C62" s="93"/>
-      <c r="D62" s="94"/>
-      <c r="E62" s="84"/>
-      <c r="F62" s="85"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="73"/>
-      <c r="I62" s="72"/>
-      <c r="J62" s="73"/>
-      <c r="K62" s="78"/>
-      <c r="L62" s="79"/>
+      <c r="A62" s="93"/>
+      <c r="B62" s="96"/>
+      <c r="C62" s="118"/>
+      <c r="D62" s="119"/>
+      <c r="E62" s="100"/>
+      <c r="F62" s="101"/>
+      <c r="G62" s="106"/>
+      <c r="H62" s="107"/>
+      <c r="I62" s="106"/>
+      <c r="J62" s="107"/>
+      <c r="K62" s="112"/>
+      <c r="L62" s="113"/>
       <c r="M62" s="36"/>
       <c r="N62" s="36"/>
       <c r="O62" s="36"/>
@@ -31268,18 +31285,18 @@
       <c r="R62" s="36"/>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="98"/>
-      <c r="B63" s="89"/>
-      <c r="C63" s="93"/>
-      <c r="D63" s="94"/>
-      <c r="E63" s="84"/>
-      <c r="F63" s="85"/>
-      <c r="G63" s="72"/>
-      <c r="H63" s="73"/>
-      <c r="I63" s="72"/>
-      <c r="J63" s="73"/>
-      <c r="K63" s="78"/>
-      <c r="L63" s="79"/>
+      <c r="A63" s="93"/>
+      <c r="B63" s="96"/>
+      <c r="C63" s="118"/>
+      <c r="D63" s="119"/>
+      <c r="E63" s="100"/>
+      <c r="F63" s="101"/>
+      <c r="G63" s="106"/>
+      <c r="H63" s="107"/>
+      <c r="I63" s="106"/>
+      <c r="J63" s="107"/>
+      <c r="K63" s="112"/>
+      <c r="L63" s="113"/>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
       <c r="O63" s="36"/>
@@ -31288,18 +31305,18 @@
       <c r="R63" s="36"/>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="98"/>
-      <c r="B64" s="89"/>
-      <c r="C64" s="93"/>
-      <c r="D64" s="94"/>
-      <c r="E64" s="84"/>
-      <c r="F64" s="85"/>
-      <c r="G64" s="72"/>
-      <c r="H64" s="73"/>
-      <c r="I64" s="72"/>
-      <c r="J64" s="73"/>
-      <c r="K64" s="78"/>
-      <c r="L64" s="79"/>
+      <c r="A64" s="93"/>
+      <c r="B64" s="96"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="100"/>
+      <c r="F64" s="101"/>
+      <c r="G64" s="106"/>
+      <c r="H64" s="107"/>
+      <c r="I64" s="106"/>
+      <c r="J64" s="107"/>
+      <c r="K64" s="112"/>
+      <c r="L64" s="113"/>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
       <c r="O64" s="36"/>
@@ -31308,18 +31325,18 @@
       <c r="R64" s="36"/>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="98"/>
-      <c r="B65" s="90"/>
-      <c r="C65" s="95"/>
-      <c r="D65" s="96"/>
-      <c r="E65" s="86"/>
-      <c r="F65" s="87"/>
-      <c r="G65" s="74"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="74"/>
-      <c r="J65" s="75"/>
-      <c r="K65" s="80"/>
-      <c r="L65" s="81"/>
+      <c r="A65" s="93"/>
+      <c r="B65" s="97"/>
+      <c r="C65" s="120"/>
+      <c r="D65" s="121"/>
+      <c r="E65" s="102"/>
+      <c r="F65" s="103"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="109"/>
+      <c r="I65" s="108"/>
+      <c r="J65" s="109"/>
+      <c r="K65" s="114"/>
+      <c r="L65" s="115"/>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
       <c r="O65" s="36"/>
@@ -31328,30 +31345,30 @@
       <c r="R65" s="36"/>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="98"/>
-      <c r="B66" s="88" t="s">
+      <c r="A66" s="93"/>
+      <c r="B66" s="95" t="s">
         <v>1113</v>
       </c>
-      <c r="C66" s="91" t="s">
+      <c r="C66" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="92"/>
-      <c r="E66" s="91" t="s">
+      <c r="D66" s="117"/>
+      <c r="E66" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="92"/>
-      <c r="G66" s="82" t="s">
+      <c r="F66" s="117"/>
+      <c r="G66" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="83"/>
-      <c r="I66" s="82" t="s">
+      <c r="H66" s="99"/>
+      <c r="I66" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="83"/>
-      <c r="K66" s="70" t="s">
+      <c r="J66" s="99"/>
+      <c r="K66" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="71"/>
+      <c r="L66" s="105"/>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
       <c r="O66" s="36"/>
@@ -31360,18 +31377,18 @@
       <c r="R66" s="36"/>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="98"/>
-      <c r="B67" s="89"/>
-      <c r="C67" s="93"/>
-      <c r="D67" s="94"/>
-      <c r="E67" s="93"/>
-      <c r="F67" s="94"/>
-      <c r="G67" s="84"/>
-      <c r="H67" s="85"/>
-      <c r="I67" s="84"/>
-      <c r="J67" s="85"/>
-      <c r="K67" s="72"/>
-      <c r="L67" s="73"/>
+      <c r="A67" s="93"/>
+      <c r="B67" s="96"/>
+      <c r="C67" s="118"/>
+      <c r="D67" s="119"/>
+      <c r="E67" s="118"/>
+      <c r="F67" s="119"/>
+      <c r="G67" s="100"/>
+      <c r="H67" s="101"/>
+      <c r="I67" s="100"/>
+      <c r="J67" s="101"/>
+      <c r="K67" s="106"/>
+      <c r="L67" s="107"/>
       <c r="M67" s="36"/>
       <c r="N67" s="36"/>
       <c r="O67" s="36"/>
@@ -31380,18 +31397,18 @@
       <c r="R67" s="36"/>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="98"/>
-      <c r="B68" s="89"/>
-      <c r="C68" s="93"/>
-      <c r="D68" s="94"/>
-      <c r="E68" s="93"/>
-      <c r="F68" s="94"/>
-      <c r="G68" s="84"/>
-      <c r="H68" s="85"/>
-      <c r="I68" s="84"/>
-      <c r="J68" s="85"/>
-      <c r="K68" s="72"/>
-      <c r="L68" s="73"/>
+      <c r="A68" s="93"/>
+      <c r="B68" s="96"/>
+      <c r="C68" s="118"/>
+      <c r="D68" s="119"/>
+      <c r="E68" s="118"/>
+      <c r="F68" s="119"/>
+      <c r="G68" s="100"/>
+      <c r="H68" s="101"/>
+      <c r="I68" s="100"/>
+      <c r="J68" s="101"/>
+      <c r="K68" s="106"/>
+      <c r="L68" s="107"/>
       <c r="M68" s="36"/>
       <c r="N68" s="36"/>
       <c r="O68" s="36"/>
@@ -31400,18 +31417,18 @@
       <c r="R68" s="36"/>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="98"/>
-      <c r="B69" s="89"/>
-      <c r="C69" s="93"/>
-      <c r="D69" s="94"/>
-      <c r="E69" s="93"/>
-      <c r="F69" s="94"/>
-      <c r="G69" s="84"/>
-      <c r="H69" s="85"/>
-      <c r="I69" s="84"/>
-      <c r="J69" s="85"/>
-      <c r="K69" s="72"/>
-      <c r="L69" s="73"/>
+      <c r="A69" s="93"/>
+      <c r="B69" s="96"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="119"/>
+      <c r="E69" s="118"/>
+      <c r="F69" s="119"/>
+      <c r="G69" s="100"/>
+      <c r="H69" s="101"/>
+      <c r="I69" s="100"/>
+      <c r="J69" s="101"/>
+      <c r="K69" s="106"/>
+      <c r="L69" s="107"/>
       <c r="M69" s="36"/>
       <c r="N69" s="36"/>
       <c r="O69" s="36"/>
@@ -31420,18 +31437,18 @@
       <c r="R69" s="36"/>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="98"/>
-      <c r="B70" s="90"/>
-      <c r="C70" s="95"/>
-      <c r="D70" s="96"/>
-      <c r="E70" s="95"/>
-      <c r="F70" s="96"/>
-      <c r="G70" s="86"/>
-      <c r="H70" s="87"/>
-      <c r="I70" s="86"/>
-      <c r="J70" s="87"/>
-      <c r="K70" s="74"/>
-      <c r="L70" s="75"/>
+      <c r="A70" s="93"/>
+      <c r="B70" s="97"/>
+      <c r="C70" s="120"/>
+      <c r="D70" s="121"/>
+      <c r="E70" s="120"/>
+      <c r="F70" s="121"/>
+      <c r="G70" s="102"/>
+      <c r="H70" s="103"/>
+      <c r="I70" s="102"/>
+      <c r="J70" s="103"/>
+      <c r="K70" s="108"/>
+      <c r="L70" s="109"/>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="36"/>
@@ -31440,30 +31457,30 @@
       <c r="R70" s="36"/>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="98"/>
-      <c r="B71" s="88" t="s">
+      <c r="A71" s="93"/>
+      <c r="B71" s="95" t="s">
         <v>1114</v>
       </c>
-      <c r="C71" s="91" t="s">
+      <c r="C71" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="92"/>
-      <c r="E71" s="91" t="s">
+      <c r="D71" s="117"/>
+      <c r="E71" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="92"/>
-      <c r="G71" s="91" t="s">
+      <c r="F71" s="117"/>
+      <c r="G71" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="H71" s="92"/>
-      <c r="I71" s="91" t="s">
+      <c r="H71" s="117"/>
+      <c r="I71" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="92"/>
-      <c r="K71" s="82" t="s">
+      <c r="J71" s="117"/>
+      <c r="K71" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="83"/>
+      <c r="L71" s="99"/>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="36"/>
@@ -31472,18 +31489,18 @@
       <c r="R71" s="36"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="98"/>
-      <c r="B72" s="89"/>
-      <c r="C72" s="93"/>
-      <c r="D72" s="94"/>
-      <c r="E72" s="93"/>
-      <c r="F72" s="94"/>
-      <c r="G72" s="93"/>
-      <c r="H72" s="94"/>
-      <c r="I72" s="93"/>
-      <c r="J72" s="94"/>
-      <c r="K72" s="84"/>
-      <c r="L72" s="85"/>
+      <c r="A72" s="93"/>
+      <c r="B72" s="96"/>
+      <c r="C72" s="118"/>
+      <c r="D72" s="119"/>
+      <c r="E72" s="118"/>
+      <c r="F72" s="119"/>
+      <c r="G72" s="118"/>
+      <c r="H72" s="119"/>
+      <c r="I72" s="118"/>
+      <c r="J72" s="119"/>
+      <c r="K72" s="100"/>
+      <c r="L72" s="101"/>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="36"/>
@@ -31492,18 +31509,18 @@
       <c r="R72" s="36"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="98"/>
-      <c r="B73" s="89"/>
-      <c r="C73" s="93"/>
-      <c r="D73" s="94"/>
-      <c r="E73" s="93"/>
-      <c r="F73" s="94"/>
-      <c r="G73" s="93"/>
-      <c r="H73" s="94"/>
-      <c r="I73" s="93"/>
-      <c r="J73" s="94"/>
-      <c r="K73" s="84"/>
-      <c r="L73" s="85"/>
+      <c r="A73" s="93"/>
+      <c r="B73" s="96"/>
+      <c r="C73" s="118"/>
+      <c r="D73" s="119"/>
+      <c r="E73" s="118"/>
+      <c r="F73" s="119"/>
+      <c r="G73" s="118"/>
+      <c r="H73" s="119"/>
+      <c r="I73" s="118"/>
+      <c r="J73" s="119"/>
+      <c r="K73" s="100"/>
+      <c r="L73" s="101"/>
       <c r="M73" s="36"/>
       <c r="N73" s="36"/>
       <c r="O73" s="36"/>
@@ -31512,18 +31529,18 @@
       <c r="R73" s="36"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="98"/>
-      <c r="B74" s="89"/>
-      <c r="C74" s="93"/>
-      <c r="D74" s="94"/>
-      <c r="E74" s="93"/>
-      <c r="F74" s="94"/>
-      <c r="G74" s="93"/>
-      <c r="H74" s="94"/>
-      <c r="I74" s="93"/>
-      <c r="J74" s="94"/>
-      <c r="K74" s="84"/>
-      <c r="L74" s="85"/>
+      <c r="A74" s="93"/>
+      <c r="B74" s="96"/>
+      <c r="C74" s="118"/>
+      <c r="D74" s="119"/>
+      <c r="E74" s="118"/>
+      <c r="F74" s="119"/>
+      <c r="G74" s="118"/>
+      <c r="H74" s="119"/>
+      <c r="I74" s="118"/>
+      <c r="J74" s="119"/>
+      <c r="K74" s="100"/>
+      <c r="L74" s="101"/>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="36"/>
@@ -31532,18 +31549,18 @@
       <c r="R74" s="36"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="99"/>
-      <c r="B75" s="90"/>
-      <c r="C75" s="95"/>
-      <c r="D75" s="96"/>
-      <c r="E75" s="95"/>
-      <c r="F75" s="96"/>
-      <c r="G75" s="95"/>
-      <c r="H75" s="96"/>
-      <c r="I75" s="95"/>
-      <c r="J75" s="96"/>
-      <c r="K75" s="86"/>
-      <c r="L75" s="87"/>
+      <c r="A75" s="94"/>
+      <c r="B75" s="97"/>
+      <c r="C75" s="120"/>
+      <c r="D75" s="121"/>
+      <c r="E75" s="120"/>
+      <c r="F75" s="121"/>
+      <c r="G75" s="120"/>
+      <c r="H75" s="121"/>
+      <c r="I75" s="120"/>
+      <c r="J75" s="121"/>
+      <c r="K75" s="102"/>
+      <c r="L75" s="103"/>
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="36"/>
@@ -31573,34 +31590,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A47:B50"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
-    <mergeCell ref="A51:A75"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:D55"/>
-    <mergeCell ref="E51:F55"/>
-    <mergeCell ref="G51:H55"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:D65"/>
-    <mergeCell ref="E61:F65"/>
-    <mergeCell ref="G61:H65"/>
-    <mergeCell ref="I51:J55"/>
-    <mergeCell ref="K51:L55"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:D60"/>
-    <mergeCell ref="E56:F60"/>
-    <mergeCell ref="G56:H60"/>
-    <mergeCell ref="I56:J60"/>
-    <mergeCell ref="K56:L60"/>
     <mergeCell ref="I61:J65"/>
     <mergeCell ref="K61:L65"/>
     <mergeCell ref="K71:L75"/>
@@ -31615,6 +31604,34 @@
     <mergeCell ref="E71:F75"/>
     <mergeCell ref="G71:H75"/>
     <mergeCell ref="I71:J75"/>
+    <mergeCell ref="I51:J55"/>
+    <mergeCell ref="K51:L55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:D60"/>
+    <mergeCell ref="E56:F60"/>
+    <mergeCell ref="G56:H60"/>
+    <mergeCell ref="I56:J60"/>
+    <mergeCell ref="K56:L60"/>
+    <mergeCell ref="A51:A75"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:D55"/>
+    <mergeCell ref="E51:F55"/>
+    <mergeCell ref="G51:H55"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:D65"/>
+    <mergeCell ref="E61:F65"/>
+    <mergeCell ref="G61:H65"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A47:B50"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehrnia\Desktop\Job\AtlasCopco\Business Analysis Project and Stakeholder Management\Excel_PLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB58BE1-30A5-4FC5-BAF8-247823352BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EEE314-578B-4A4A-A9B1-C4F97FB6ED8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="1131">
   <si>
     <t>Description</t>
   </si>
@@ -3465,7 +3465,10 @@
     <t xml:space="preserve">Multi-Site Pressure Reducing &amp; Power Generation </t>
   </si>
   <si>
-    <t>PROJECT Manager: Majid Mehrnia</t>
+    <t>Project Manager: Majid Mehrnia</t>
+  </si>
+  <si>
+    <t>Project Title: Multi-Site Pressure Reducing &amp; Power Generation</t>
   </si>
 </sst>
 </file>
@@ -4222,6 +4225,96 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4288,96 +4381,6 @@
     <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4385,7 +4388,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -12877,7 +12882,7 @@
     </row>
     <row r="2" spans="1:25" ht="15.75">
       <c r="A2" s="64" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
       <c r="B2" s="64"/>
       <c r="C2" s="64"/>
@@ -30779,14 +30784,14 @@
       <c r="R40" s="36"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="100" t="s">
         <v>1115</v>
       </c>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70" t="s">
+      <c r="B41" s="100"/>
+      <c r="C41" s="100" t="s">
         <v>1116</v>
       </c>
-      <c r="D41" s="70"/>
+      <c r="D41" s="100"/>
       <c r="E41" s="37" t="s">
         <v>9</v>
       </c>
@@ -30807,10 +30812,10 @@
       <c r="R41" s="41"/>
     </row>
     <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="71"/>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
+      <c r="A42" s="101"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="101"/>
+      <c r="D42" s="101"/>
       <c r="E42" s="42"/>
       <c r="F42" s="36"/>
       <c r="G42" s="36"/>
@@ -30899,38 +30904,38 @@
       <c r="R46" s="45"/>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="72" t="s">
+      <c r="A47" s="102" t="s">
         <v>1091</v>
       </c>
-      <c r="B47" s="73"/>
-      <c r="C47" s="78" t="s">
+      <c r="B47" s="103"/>
+      <c r="C47" s="108" t="s">
         <v>1092</v>
       </c>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="79"/>
-      <c r="J47" s="79"/>
-      <c r="K47" s="79"/>
-      <c r="L47" s="80"/>
+      <c r="D47" s="109"/>
+      <c r="E47" s="109"/>
+      <c r="F47" s="109"/>
+      <c r="G47" s="109"/>
+      <c r="H47" s="109"/>
+      <c r="I47" s="109"/>
+      <c r="J47" s="109"/>
+      <c r="K47" s="109"/>
+      <c r="L47" s="110"/>
       <c r="M47" s="36"/>
       <c r="N47" s="36"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="74"/>
-      <c r="B48" s="75"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="82"/>
-      <c r="F48" s="82"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="82"/>
-      <c r="I48" s="82"/>
-      <c r="J48" s="82"/>
-      <c r="K48" s="82"/>
-      <c r="L48" s="83"/>
+      <c r="A48" s="104"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="111"/>
+      <c r="D48" s="112"/>
+      <c r="E48" s="112"/>
+      <c r="F48" s="112"/>
+      <c r="G48" s="112"/>
+      <c r="H48" s="112"/>
+      <c r="I48" s="112"/>
+      <c r="J48" s="112"/>
+      <c r="K48" s="112"/>
+      <c r="L48" s="113"/>
       <c r="M48" s="36"/>
       <c r="N48" s="36"/>
       <c r="O48" s="39" t="s">
@@ -30941,28 +30946,28 @@
       <c r="R48" s="41"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="74"/>
-      <c r="B49" s="75"/>
-      <c r="C49" s="84" t="s">
+      <c r="A49" s="104"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="114" t="s">
         <v>1094</v>
       </c>
-      <c r="D49" s="85"/>
-      <c r="E49" s="84" t="s">
+      <c r="D49" s="115"/>
+      <c r="E49" s="114" t="s">
         <v>1095</v>
       </c>
-      <c r="F49" s="85"/>
-      <c r="G49" s="84" t="s">
+      <c r="F49" s="115"/>
+      <c r="G49" s="114" t="s">
         <v>1096</v>
       </c>
-      <c r="H49" s="85"/>
-      <c r="I49" s="88" t="s">
+      <c r="H49" s="115"/>
+      <c r="I49" s="118" t="s">
         <v>1097</v>
       </c>
-      <c r="J49" s="89"/>
-      <c r="K49" s="84" t="s">
+      <c r="J49" s="119"/>
+      <c r="K49" s="114" t="s">
         <v>1098</v>
       </c>
-      <c r="L49" s="85"/>
+      <c r="L49" s="115"/>
       <c r="M49" s="36"/>
       <c r="N49" s="36"/>
       <c r="O49" s="46" t="s">
@@ -30973,18 +30978,18 @@
       <c r="R49" s="41"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="76"/>
-      <c r="B50" s="77"/>
-      <c r="C50" s="86"/>
-      <c r="D50" s="87"/>
-      <c r="E50" s="86"/>
-      <c r="F50" s="87"/>
-      <c r="G50" s="86"/>
-      <c r="H50" s="87"/>
-      <c r="I50" s="90"/>
-      <c r="J50" s="91"/>
-      <c r="K50" s="86"/>
-      <c r="L50" s="87"/>
+      <c r="A50" s="106"/>
+      <c r="B50" s="107"/>
+      <c r="C50" s="116"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="116"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="116"/>
+      <c r="H50" s="117"/>
+      <c r="I50" s="120"/>
+      <c r="J50" s="121"/>
+      <c r="K50" s="116"/>
+      <c r="L50" s="117"/>
       <c r="M50" s="36"/>
       <c r="N50" s="36"/>
       <c r="O50" s="46" t="s">
@@ -30995,32 +31000,32 @@
       <c r="R50" s="41"/>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="92" t="s">
+      <c r="A51" s="97" t="s">
         <v>1101</v>
       </c>
-      <c r="B51" s="95" t="s">
+      <c r="B51" s="88" t="s">
         <v>1102</v>
       </c>
-      <c r="C51" s="98" t="s">
+      <c r="C51" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="99"/>
-      <c r="E51" s="104" t="s">
+      <c r="D51" s="83"/>
+      <c r="E51" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="105"/>
-      <c r="G51" s="110" t="s">
+      <c r="F51" s="71"/>
+      <c r="G51" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="111"/>
-      <c r="I51" s="110" t="s">
+      <c r="H51" s="77"/>
+      <c r="I51" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="111"/>
-      <c r="K51" s="110" t="s">
+      <c r="J51" s="77"/>
+      <c r="K51" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="111"/>
+      <c r="L51" s="77"/>
       <c r="M51" s="36"/>
       <c r="N51" s="36"/>
       <c r="O51" s="46" t="s">
@@ -31031,18 +31036,18 @@
       <c r="R51" s="41"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="93"/>
-      <c r="B52" s="96"/>
-      <c r="C52" s="100"/>
-      <c r="D52" s="101"/>
-      <c r="E52" s="106"/>
-      <c r="F52" s="107"/>
-      <c r="G52" s="112"/>
-      <c r="H52" s="113"/>
-      <c r="I52" s="112"/>
-      <c r="J52" s="113"/>
-      <c r="K52" s="112"/>
-      <c r="L52" s="113"/>
+      <c r="A52" s="98"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="84"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="78"/>
+      <c r="H52" s="79"/>
+      <c r="I52" s="78"/>
+      <c r="J52" s="79"/>
+      <c r="K52" s="78"/>
+      <c r="L52" s="79"/>
       <c r="M52" s="36"/>
       <c r="N52" s="36"/>
       <c r="O52" s="46" t="s">
@@ -31053,18 +31058,18 @@
       <c r="R52" s="41"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="93"/>
-      <c r="B53" s="96"/>
-      <c r="C53" s="100"/>
-      <c r="D53" s="101"/>
-      <c r="E53" s="106"/>
-      <c r="F53" s="107"/>
-      <c r="G53" s="112"/>
-      <c r="H53" s="113"/>
-      <c r="I53" s="112"/>
-      <c r="J53" s="113"/>
-      <c r="K53" s="112"/>
-      <c r="L53" s="113"/>
+      <c r="A53" s="98"/>
+      <c r="B53" s="89"/>
+      <c r="C53" s="84"/>
+      <c r="D53" s="85"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="73"/>
+      <c r="G53" s="78"/>
+      <c r="H53" s="79"/>
+      <c r="I53" s="78"/>
+      <c r="J53" s="79"/>
+      <c r="K53" s="78"/>
+      <c r="L53" s="79"/>
       <c r="M53" s="36"/>
       <c r="N53" s="36"/>
       <c r="O53" s="43" t="s">
@@ -31075,34 +31080,34 @@
       <c r="R53" s="45"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="93"/>
-      <c r="B54" s="96"/>
-      <c r="C54" s="100"/>
-      <c r="D54" s="101"/>
-      <c r="E54" s="106"/>
-      <c r="F54" s="107"/>
-      <c r="G54" s="112"/>
-      <c r="H54" s="113"/>
-      <c r="I54" s="112"/>
-      <c r="J54" s="113"/>
-      <c r="K54" s="112"/>
-      <c r="L54" s="113"/>
+      <c r="A54" s="98"/>
+      <c r="B54" s="89"/>
+      <c r="C54" s="84"/>
+      <c r="D54" s="85"/>
+      <c r="E54" s="72"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="78"/>
+      <c r="H54" s="79"/>
+      <c r="I54" s="78"/>
+      <c r="J54" s="79"/>
+      <c r="K54" s="78"/>
+      <c r="L54" s="79"/>
       <c r="M54" s="36"/>
       <c r="N54" s="36"/>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="93"/>
-      <c r="B55" s="97"/>
-      <c r="C55" s="102"/>
-      <c r="D55" s="103"/>
-      <c r="E55" s="108"/>
-      <c r="F55" s="109"/>
-      <c r="G55" s="114"/>
-      <c r="H55" s="115"/>
-      <c r="I55" s="114"/>
-      <c r="J55" s="115"/>
-      <c r="K55" s="114"/>
-      <c r="L55" s="115"/>
+      <c r="A55" s="98"/>
+      <c r="B55" s="90"/>
+      <c r="C55" s="86"/>
+      <c r="D55" s="87"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="80"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="80"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="80"/>
+      <c r="L55" s="81"/>
       <c r="M55" s="36"/>
       <c r="N55" s="36"/>
       <c r="O55" s="39" t="s">
@@ -31113,30 +31118,30 @@
       <c r="R55" s="41"/>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="93"/>
-      <c r="B56" s="95" t="s">
+      <c r="A56" s="98"/>
+      <c r="B56" s="88" t="s">
         <v>1107</v>
       </c>
-      <c r="C56" s="98" t="s">
+      <c r="C56" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="99"/>
-      <c r="E56" s="104" t="s">
+      <c r="D56" s="83"/>
+      <c r="E56" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="105"/>
-      <c r="G56" s="104" t="s">
+      <c r="F56" s="71"/>
+      <c r="G56" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="105"/>
-      <c r="I56" s="110" t="s">
+      <c r="H56" s="71"/>
+      <c r="I56" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="111"/>
-      <c r="K56" s="110" t="s">
+      <c r="J56" s="77"/>
+      <c r="K56" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="111"/>
+      <c r="L56" s="77"/>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
       <c r="O56" s="46" t="s">
@@ -31147,18 +31152,18 @@
       <c r="R56" s="41"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="93"/>
-      <c r="B57" s="96"/>
-      <c r="C57" s="100"/>
-      <c r="D57" s="101"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="107"/>
-      <c r="G57" s="106"/>
-      <c r="H57" s="107"/>
-      <c r="I57" s="112"/>
-      <c r="J57" s="113"/>
-      <c r="K57" s="112"/>
-      <c r="L57" s="113"/>
+      <c r="A57" s="98"/>
+      <c r="B57" s="89"/>
+      <c r="C57" s="84"/>
+      <c r="D57" s="85"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="72"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="78"/>
+      <c r="J57" s="79"/>
+      <c r="K57" s="78"/>
+      <c r="L57" s="79"/>
       <c r="M57" s="36"/>
       <c r="N57" s="36"/>
       <c r="O57" s="46" t="s">
@@ -31169,18 +31174,18 @@
       <c r="R57" s="41"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="93"/>
-      <c r="B58" s="96"/>
-      <c r="C58" s="100"/>
-      <c r="D58" s="101"/>
-      <c r="E58" s="106"/>
-      <c r="F58" s="107"/>
-      <c r="G58" s="106"/>
-      <c r="H58" s="107"/>
-      <c r="I58" s="112"/>
-      <c r="J58" s="113"/>
-      <c r="K58" s="112"/>
-      <c r="L58" s="113"/>
+      <c r="A58" s="98"/>
+      <c r="B58" s="89"/>
+      <c r="C58" s="84"/>
+      <c r="D58" s="85"/>
+      <c r="E58" s="72"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="72"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="78"/>
+      <c r="J58" s="79"/>
+      <c r="K58" s="78"/>
+      <c r="L58" s="79"/>
       <c r="M58" s="36"/>
       <c r="N58" s="36"/>
       <c r="O58" s="46" t="s">
@@ -31191,18 +31196,18 @@
       <c r="R58" s="41"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="93"/>
-      <c r="B59" s="96"/>
-      <c r="C59" s="100"/>
-      <c r="D59" s="101"/>
-      <c r="E59" s="106"/>
-      <c r="F59" s="107"/>
-      <c r="G59" s="106"/>
-      <c r="H59" s="107"/>
-      <c r="I59" s="112"/>
-      <c r="J59" s="113"/>
-      <c r="K59" s="112"/>
-      <c r="L59" s="113"/>
+      <c r="A59" s="98"/>
+      <c r="B59" s="89"/>
+      <c r="C59" s="84"/>
+      <c r="D59" s="85"/>
+      <c r="E59" s="72"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="72"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="78"/>
+      <c r="J59" s="79"/>
+      <c r="K59" s="78"/>
+      <c r="L59" s="79"/>
       <c r="M59" s="36"/>
       <c r="N59" s="36"/>
       <c r="O59" s="43" t="s">
@@ -31213,18 +31218,18 @@
       <c r="R59" s="45"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="93"/>
-      <c r="B60" s="97"/>
-      <c r="C60" s="102"/>
-      <c r="D60" s="103"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="114"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="114"/>
-      <c r="L60" s="115"/>
+      <c r="A60" s="98"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="86"/>
+      <c r="D60" s="87"/>
+      <c r="E60" s="74"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="80"/>
+      <c r="J60" s="81"/>
+      <c r="K60" s="80"/>
+      <c r="L60" s="81"/>
       <c r="M60" s="36"/>
       <c r="N60" s="36"/>
       <c r="O60" s="36"/>
@@ -31233,30 +31238,30 @@
       <c r="R60" s="36"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="93"/>
-      <c r="B61" s="95" t="s">
+      <c r="A61" s="98"/>
+      <c r="B61" s="88" t="s">
         <v>1112</v>
       </c>
-      <c r="C61" s="116" t="s">
+      <c r="C61" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="117"/>
-      <c r="E61" s="98" t="s">
+      <c r="D61" s="92"/>
+      <c r="E61" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="99"/>
-      <c r="G61" s="104" t="s">
+      <c r="F61" s="83"/>
+      <c r="G61" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="105"/>
-      <c r="I61" s="104" t="s">
+      <c r="H61" s="71"/>
+      <c r="I61" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="105"/>
-      <c r="K61" s="110" t="s">
+      <c r="J61" s="71"/>
+      <c r="K61" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="111"/>
+      <c r="L61" s="77"/>
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
       <c r="O61" s="36"/>
@@ -31265,18 +31270,18 @@
       <c r="R61" s="36"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="93"/>
-      <c r="B62" s="96"/>
-      <c r="C62" s="118"/>
-      <c r="D62" s="119"/>
-      <c r="E62" s="100"/>
-      <c r="F62" s="101"/>
-      <c r="G62" s="106"/>
-      <c r="H62" s="107"/>
-      <c r="I62" s="106"/>
-      <c r="J62" s="107"/>
-      <c r="K62" s="112"/>
-      <c r="L62" s="113"/>
+      <c r="A62" s="98"/>
+      <c r="B62" s="89"/>
+      <c r="C62" s="93"/>
+      <c r="D62" s="94"/>
+      <c r="E62" s="84"/>
+      <c r="F62" s="85"/>
+      <c r="G62" s="72"/>
+      <c r="H62" s="73"/>
+      <c r="I62" s="72"/>
+      <c r="J62" s="73"/>
+      <c r="K62" s="78"/>
+      <c r="L62" s="79"/>
       <c r="M62" s="36"/>
       <c r="N62" s="36"/>
       <c r="O62" s="36"/>
@@ -31285,18 +31290,18 @@
       <c r="R62" s="36"/>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="93"/>
-      <c r="B63" s="96"/>
-      <c r="C63" s="118"/>
-      <c r="D63" s="119"/>
-      <c r="E63" s="100"/>
-      <c r="F63" s="101"/>
-      <c r="G63" s="106"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="106"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="112"/>
-      <c r="L63" s="113"/>
+      <c r="A63" s="98"/>
+      <c r="B63" s="89"/>
+      <c r="C63" s="93"/>
+      <c r="D63" s="94"/>
+      <c r="E63" s="84"/>
+      <c r="F63" s="85"/>
+      <c r="G63" s="72"/>
+      <c r="H63" s="73"/>
+      <c r="I63" s="72"/>
+      <c r="J63" s="73"/>
+      <c r="K63" s="78"/>
+      <c r="L63" s="79"/>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
       <c r="O63" s="36"/>
@@ -31305,18 +31310,18 @@
       <c r="R63" s="36"/>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="93"/>
-      <c r="B64" s="96"/>
-      <c r="C64" s="118"/>
-      <c r="D64" s="119"/>
-      <c r="E64" s="100"/>
-      <c r="F64" s="101"/>
-      <c r="G64" s="106"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="106"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="112"/>
-      <c r="L64" s="113"/>
+      <c r="A64" s="98"/>
+      <c r="B64" s="89"/>
+      <c r="C64" s="93"/>
+      <c r="D64" s="94"/>
+      <c r="E64" s="84"/>
+      <c r="F64" s="85"/>
+      <c r="G64" s="72"/>
+      <c r="H64" s="73"/>
+      <c r="I64" s="72"/>
+      <c r="J64" s="73"/>
+      <c r="K64" s="78"/>
+      <c r="L64" s="79"/>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
       <c r="O64" s="36"/>
@@ -31325,18 +31330,18 @@
       <c r="R64" s="36"/>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="93"/>
-      <c r="B65" s="97"/>
-      <c r="C65" s="120"/>
-      <c r="D65" s="121"/>
-      <c r="E65" s="102"/>
-      <c r="F65" s="103"/>
-      <c r="G65" s="108"/>
-      <c r="H65" s="109"/>
-      <c r="I65" s="108"/>
-      <c r="J65" s="109"/>
-      <c r="K65" s="114"/>
-      <c r="L65" s="115"/>
+      <c r="A65" s="98"/>
+      <c r="B65" s="90"/>
+      <c r="C65" s="95"/>
+      <c r="D65" s="96"/>
+      <c r="E65" s="86"/>
+      <c r="F65" s="87"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="74"/>
+      <c r="J65" s="75"/>
+      <c r="K65" s="80"/>
+      <c r="L65" s="81"/>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
       <c r="O65" s="36"/>
@@ -31345,30 +31350,30 @@
       <c r="R65" s="36"/>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="93"/>
-      <c r="B66" s="95" t="s">
+      <c r="A66" s="98"/>
+      <c r="B66" s="88" t="s">
         <v>1113</v>
       </c>
-      <c r="C66" s="116" t="s">
+      <c r="C66" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="117"/>
-      <c r="E66" s="116" t="s">
+      <c r="D66" s="92"/>
+      <c r="E66" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="117"/>
-      <c r="G66" s="98" t="s">
+      <c r="F66" s="92"/>
+      <c r="G66" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="99"/>
-      <c r="I66" s="98" t="s">
+      <c r="H66" s="83"/>
+      <c r="I66" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="99"/>
-      <c r="K66" s="104" t="s">
+      <c r="J66" s="83"/>
+      <c r="K66" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="105"/>
+      <c r="L66" s="71"/>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
       <c r="O66" s="36"/>
@@ -31377,18 +31382,18 @@
       <c r="R66" s="36"/>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="93"/>
-      <c r="B67" s="96"/>
-      <c r="C67" s="118"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="118"/>
-      <c r="F67" s="119"/>
-      <c r="G67" s="100"/>
-      <c r="H67" s="101"/>
-      <c r="I67" s="100"/>
-      <c r="J67" s="101"/>
-      <c r="K67" s="106"/>
-      <c r="L67" s="107"/>
+      <c r="A67" s="98"/>
+      <c r="B67" s="89"/>
+      <c r="C67" s="93"/>
+      <c r="D67" s="94"/>
+      <c r="E67" s="93"/>
+      <c r="F67" s="94"/>
+      <c r="G67" s="84"/>
+      <c r="H67" s="85"/>
+      <c r="I67" s="84"/>
+      <c r="J67" s="85"/>
+      <c r="K67" s="72"/>
+      <c r="L67" s="73"/>
       <c r="M67" s="36"/>
       <c r="N67" s="36"/>
       <c r="O67" s="36"/>
@@ -31397,18 +31402,18 @@
       <c r="R67" s="36"/>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="93"/>
-      <c r="B68" s="96"/>
-      <c r="C68" s="118"/>
-      <c r="D68" s="119"/>
-      <c r="E68" s="118"/>
-      <c r="F68" s="119"/>
-      <c r="G68" s="100"/>
-      <c r="H68" s="101"/>
-      <c r="I68" s="100"/>
-      <c r="J68" s="101"/>
-      <c r="K68" s="106"/>
-      <c r="L68" s="107"/>
+      <c r="A68" s="98"/>
+      <c r="B68" s="89"/>
+      <c r="C68" s="93"/>
+      <c r="D68" s="94"/>
+      <c r="E68" s="93"/>
+      <c r="F68" s="94"/>
+      <c r="G68" s="84"/>
+      <c r="H68" s="85"/>
+      <c r="I68" s="84"/>
+      <c r="J68" s="85"/>
+      <c r="K68" s="72"/>
+      <c r="L68" s="73"/>
       <c r="M68" s="36"/>
       <c r="N68" s="36"/>
       <c r="O68" s="36"/>
@@ -31417,18 +31422,18 @@
       <c r="R68" s="36"/>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="93"/>
-      <c r="B69" s="96"/>
-      <c r="C69" s="118"/>
-      <c r="D69" s="119"/>
-      <c r="E69" s="118"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="100"/>
-      <c r="H69" s="101"/>
-      <c r="I69" s="100"/>
-      <c r="J69" s="101"/>
-      <c r="K69" s="106"/>
-      <c r="L69" s="107"/>
+      <c r="A69" s="98"/>
+      <c r="B69" s="89"/>
+      <c r="C69" s="93"/>
+      <c r="D69" s="94"/>
+      <c r="E69" s="93"/>
+      <c r="F69" s="94"/>
+      <c r="G69" s="84"/>
+      <c r="H69" s="85"/>
+      <c r="I69" s="84"/>
+      <c r="J69" s="85"/>
+      <c r="K69" s="72"/>
+      <c r="L69" s="73"/>
       <c r="M69" s="36"/>
       <c r="N69" s="36"/>
       <c r="O69" s="36"/>
@@ -31437,18 +31442,18 @@
       <c r="R69" s="36"/>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="93"/>
-      <c r="B70" s="97"/>
-      <c r="C70" s="120"/>
-      <c r="D70" s="121"/>
-      <c r="E70" s="120"/>
-      <c r="F70" s="121"/>
-      <c r="G70" s="102"/>
-      <c r="H70" s="103"/>
-      <c r="I70" s="102"/>
-      <c r="J70" s="103"/>
-      <c r="K70" s="108"/>
-      <c r="L70" s="109"/>
+      <c r="A70" s="98"/>
+      <c r="B70" s="90"/>
+      <c r="C70" s="95"/>
+      <c r="D70" s="96"/>
+      <c r="E70" s="95"/>
+      <c r="F70" s="96"/>
+      <c r="G70" s="86"/>
+      <c r="H70" s="87"/>
+      <c r="I70" s="86"/>
+      <c r="J70" s="87"/>
+      <c r="K70" s="74"/>
+      <c r="L70" s="75"/>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="36"/>
@@ -31457,30 +31462,30 @@
       <c r="R70" s="36"/>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="93"/>
-      <c r="B71" s="95" t="s">
+      <c r="A71" s="98"/>
+      <c r="B71" s="88" t="s">
         <v>1114</v>
       </c>
-      <c r="C71" s="116" t="s">
+      <c r="C71" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="117"/>
-      <c r="E71" s="116" t="s">
+      <c r="D71" s="92"/>
+      <c r="E71" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="117"/>
-      <c r="G71" s="116" t="s">
+      <c r="F71" s="92"/>
+      <c r="G71" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="H71" s="117"/>
-      <c r="I71" s="116" t="s">
+      <c r="H71" s="92"/>
+      <c r="I71" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="117"/>
-      <c r="K71" s="98" t="s">
+      <c r="J71" s="92"/>
+      <c r="K71" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="99"/>
+      <c r="L71" s="83"/>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="36"/>
@@ -31489,18 +31494,18 @@
       <c r="R71" s="36"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="93"/>
-      <c r="B72" s="96"/>
-      <c r="C72" s="118"/>
-      <c r="D72" s="119"/>
-      <c r="E72" s="118"/>
-      <c r="F72" s="119"/>
-      <c r="G72" s="118"/>
-      <c r="H72" s="119"/>
-      <c r="I72" s="118"/>
-      <c r="J72" s="119"/>
-      <c r="K72" s="100"/>
-      <c r="L72" s="101"/>
+      <c r="A72" s="98"/>
+      <c r="B72" s="89"/>
+      <c r="C72" s="93"/>
+      <c r="D72" s="94"/>
+      <c r="E72" s="93"/>
+      <c r="F72" s="94"/>
+      <c r="G72" s="93"/>
+      <c r="H72" s="94"/>
+      <c r="I72" s="93"/>
+      <c r="J72" s="94"/>
+      <c r="K72" s="84"/>
+      <c r="L72" s="85"/>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="36"/>
@@ -31509,18 +31514,18 @@
       <c r="R72" s="36"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="93"/>
-      <c r="B73" s="96"/>
-      <c r="C73" s="118"/>
-      <c r="D73" s="119"/>
-      <c r="E73" s="118"/>
-      <c r="F73" s="119"/>
-      <c r="G73" s="118"/>
-      <c r="H73" s="119"/>
-      <c r="I73" s="118"/>
-      <c r="J73" s="119"/>
-      <c r="K73" s="100"/>
-      <c r="L73" s="101"/>
+      <c r="A73" s="98"/>
+      <c r="B73" s="89"/>
+      <c r="C73" s="93"/>
+      <c r="D73" s="94"/>
+      <c r="E73" s="93"/>
+      <c r="F73" s="94"/>
+      <c r="G73" s="93"/>
+      <c r="H73" s="94"/>
+      <c r="I73" s="93"/>
+      <c r="J73" s="94"/>
+      <c r="K73" s="84"/>
+      <c r="L73" s="85"/>
       <c r="M73" s="36"/>
       <c r="N73" s="36"/>
       <c r="O73" s="36"/>
@@ -31529,18 +31534,18 @@
       <c r="R73" s="36"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="93"/>
-      <c r="B74" s="96"/>
-      <c r="C74" s="118"/>
-      <c r="D74" s="119"/>
-      <c r="E74" s="118"/>
-      <c r="F74" s="119"/>
-      <c r="G74" s="118"/>
-      <c r="H74" s="119"/>
-      <c r="I74" s="118"/>
-      <c r="J74" s="119"/>
-      <c r="K74" s="100"/>
-      <c r="L74" s="101"/>
+      <c r="A74" s="98"/>
+      <c r="B74" s="89"/>
+      <c r="C74" s="93"/>
+      <c r="D74" s="94"/>
+      <c r="E74" s="93"/>
+      <c r="F74" s="94"/>
+      <c r="G74" s="93"/>
+      <c r="H74" s="94"/>
+      <c r="I74" s="93"/>
+      <c r="J74" s="94"/>
+      <c r="K74" s="84"/>
+      <c r="L74" s="85"/>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="36"/>
@@ -31549,18 +31554,18 @@
       <c r="R74" s="36"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="94"/>
-      <c r="B75" s="97"/>
-      <c r="C75" s="120"/>
-      <c r="D75" s="121"/>
-      <c r="E75" s="120"/>
-      <c r="F75" s="121"/>
-      <c r="G75" s="120"/>
-      <c r="H75" s="121"/>
-      <c r="I75" s="120"/>
-      <c r="J75" s="121"/>
-      <c r="K75" s="102"/>
-      <c r="L75" s="103"/>
+      <c r="A75" s="99"/>
+      <c r="B75" s="90"/>
+      <c r="C75" s="95"/>
+      <c r="D75" s="96"/>
+      <c r="E75" s="95"/>
+      <c r="F75" s="96"/>
+      <c r="G75" s="95"/>
+      <c r="H75" s="96"/>
+      <c r="I75" s="95"/>
+      <c r="J75" s="96"/>
+      <c r="K75" s="86"/>
+      <c r="L75" s="87"/>
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="36"/>
@@ -31590,6 +31595,34 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A47:B50"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A51:A75"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:D55"/>
+    <mergeCell ref="E51:F55"/>
+    <mergeCell ref="G51:H55"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:D65"/>
+    <mergeCell ref="E61:F65"/>
+    <mergeCell ref="G61:H65"/>
+    <mergeCell ref="I51:J55"/>
+    <mergeCell ref="K51:L55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:D60"/>
+    <mergeCell ref="E56:F60"/>
+    <mergeCell ref="G56:H60"/>
+    <mergeCell ref="I56:J60"/>
+    <mergeCell ref="K56:L60"/>
     <mergeCell ref="I61:J65"/>
     <mergeCell ref="K61:L65"/>
     <mergeCell ref="K71:L75"/>
@@ -31604,34 +31637,6 @@
     <mergeCell ref="E71:F75"/>
     <mergeCell ref="G71:H75"/>
     <mergeCell ref="I71:J75"/>
-    <mergeCell ref="I51:J55"/>
-    <mergeCell ref="K51:L55"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:D60"/>
-    <mergeCell ref="E56:F60"/>
-    <mergeCell ref="G56:H60"/>
-    <mergeCell ref="I56:J60"/>
-    <mergeCell ref="K56:L60"/>
-    <mergeCell ref="A51:A75"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:D55"/>
-    <mergeCell ref="E51:F55"/>
-    <mergeCell ref="G51:H55"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:D65"/>
-    <mergeCell ref="E61:F65"/>
-    <mergeCell ref="G61:H65"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A47:B50"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PLM-Performance-Dashboard.xlsx
+++ b/PLM-Performance-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mehrnia\Desktop\Job\AtlasCopco\Business Analysis Project and Stakeholder Management\Excel_PLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB46D7AD-B0FC-4114-A22D-154F95F3E2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64EA143-710E-4DAA-89F7-76437B5C746C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="894" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5999,7 +5999,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -6263,6 +6263,96 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6329,96 +6419,6 @@
     <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -6426,6 +6426,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -39925,14 +39926,14 @@
       <c r="R40" s="35"/>
     </row>
     <row r="41" spans="1:18" ht="18.75">
-      <c r="A41" s="153" t="s">
+      <c r="A41" s="183" t="s">
         <v>1054</v>
       </c>
-      <c r="B41" s="153"/>
-      <c r="C41" s="153" t="s">
+      <c r="B41" s="183"/>
+      <c r="C41" s="183" t="s">
         <v>1055</v>
       </c>
-      <c r="D41" s="153"/>
+      <c r="D41" s="183"/>
       <c r="E41" s="36" t="s">
         <v>9</v>
       </c>
@@ -39953,10 +39954,10 @@
       <c r="R41" s="40"/>
     </row>
     <row r="42" spans="1:18" ht="18.75">
-      <c r="A42" s="154"/>
-      <c r="B42" s="154"/>
-      <c r="C42" s="154"/>
-      <c r="D42" s="154"/>
+      <c r="A42" s="184"/>
+      <c r="B42" s="184"/>
+      <c r="C42" s="184"/>
+      <c r="D42" s="184"/>
       <c r="E42" s="41"/>
       <c r="F42" s="35"/>
       <c r="G42" s="35"/>
@@ -40045,38 +40046,38 @@
       <c r="R46" s="44"/>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="155" t="s">
+      <c r="A47" s="185" t="s">
         <v>1030</v>
       </c>
-      <c r="B47" s="156"/>
-      <c r="C47" s="161" t="s">
+      <c r="B47" s="186"/>
+      <c r="C47" s="191" t="s">
         <v>1031</v>
       </c>
-      <c r="D47" s="162"/>
-      <c r="E47" s="162"/>
-      <c r="F47" s="162"/>
-      <c r="G47" s="162"/>
-      <c r="H47" s="162"/>
-      <c r="I47" s="162"/>
-      <c r="J47" s="162"/>
-      <c r="K47" s="162"/>
-      <c r="L47" s="163"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="192"/>
+      <c r="F47" s="192"/>
+      <c r="G47" s="192"/>
+      <c r="H47" s="192"/>
+      <c r="I47" s="192"/>
+      <c r="J47" s="192"/>
+      <c r="K47" s="192"/>
+      <c r="L47" s="193"/>
       <c r="M47" s="35"/>
       <c r="N47" s="35"/>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="157"/>
-      <c r="B48" s="158"/>
-      <c r="C48" s="164"/>
-      <c r="D48" s="165"/>
-      <c r="E48" s="165"/>
-      <c r="F48" s="165"/>
-      <c r="G48" s="165"/>
-      <c r="H48" s="165"/>
-      <c r="I48" s="165"/>
-      <c r="J48" s="165"/>
-      <c r="K48" s="165"/>
-      <c r="L48" s="166"/>
+      <c r="A48" s="187"/>
+      <c r="B48" s="188"/>
+      <c r="C48" s="194"/>
+      <c r="D48" s="195"/>
+      <c r="E48" s="195"/>
+      <c r="F48" s="195"/>
+      <c r="G48" s="195"/>
+      <c r="H48" s="195"/>
+      <c r="I48" s="195"/>
+      <c r="J48" s="195"/>
+      <c r="K48" s="195"/>
+      <c r="L48" s="196"/>
       <c r="M48" s="35"/>
       <c r="N48" s="35"/>
       <c r="O48" s="38" t="s">
@@ -40087,28 +40088,28 @@
       <c r="R48" s="40"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="157"/>
-      <c r="B49" s="158"/>
-      <c r="C49" s="167" t="s">
+      <c r="A49" s="187"/>
+      <c r="B49" s="188"/>
+      <c r="C49" s="197" t="s">
         <v>1033</v>
       </c>
-      <c r="D49" s="168"/>
-      <c r="E49" s="167" t="s">
+      <c r="D49" s="198"/>
+      <c r="E49" s="197" t="s">
         <v>1034</v>
       </c>
-      <c r="F49" s="168"/>
-      <c r="G49" s="167" t="s">
+      <c r="F49" s="198"/>
+      <c r="G49" s="197" t="s">
         <v>1035</v>
       </c>
-      <c r="H49" s="168"/>
-      <c r="I49" s="171" t="s">
+      <c r="H49" s="198"/>
+      <c r="I49" s="201" t="s">
         <v>1036</v>
       </c>
-      <c r="J49" s="172"/>
-      <c r="K49" s="167" t="s">
+      <c r="J49" s="202"/>
+      <c r="K49" s="197" t="s">
         <v>1037</v>
       </c>
-      <c r="L49" s="168"/>
+      <c r="L49" s="198"/>
       <c r="M49" s="35"/>
       <c r="N49" s="35"/>
       <c r="O49" s="45" t="s">
@@ -40119,18 +40120,18 @@
       <c r="R49" s="40"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="159"/>
-      <c r="B50" s="160"/>
-      <c r="C50" s="169"/>
-      <c r="D50" s="170"/>
-      <c r="E50" s="169"/>
-      <c r="F50" s="170"/>
-      <c r="G50" s="169"/>
-      <c r="H50" s="170"/>
-      <c r="I50" s="173"/>
-      <c r="J50" s="174"/>
-      <c r="K50" s="169"/>
-      <c r="L50" s="170"/>
+      <c r="A50" s="189"/>
+      <c r="B50" s="190"/>
+      <c r="C50" s="199"/>
+      <c r="D50" s="200"/>
+      <c r="E50" s="199"/>
+      <c r="F50" s="200"/>
+      <c r="G50" s="199"/>
+      <c r="H50" s="200"/>
+      <c r="I50" s="203"/>
+      <c r="J50" s="204"/>
+      <c r="K50" s="199"/>
+      <c r="L50" s="200"/>
       <c r="M50" s="35"/>
       <c r="N50" s="35"/>
       <c r="O50" s="45" t="s">
@@ -40141,32 +40142,32 @@
       <c r="R50" s="40"/>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="175" t="s">
+      <c r="A51" s="180" t="s">
         <v>1040</v>
       </c>
-      <c r="B51" s="178" t="s">
+      <c r="B51" s="171" t="s">
         <v>1041</v>
       </c>
-      <c r="C51" s="181" t="s">
+      <c r="C51" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="182"/>
-      <c r="E51" s="187" t="s">
+      <c r="D51" s="166"/>
+      <c r="E51" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="188"/>
-      <c r="G51" s="193" t="s">
+      <c r="F51" s="154"/>
+      <c r="G51" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="194"/>
-      <c r="I51" s="193" t="s">
+      <c r="H51" s="160"/>
+      <c r="I51" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="194"/>
-      <c r="K51" s="193" t="s">
+      <c r="J51" s="160"/>
+      <c r="K51" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="194"/>
+      <c r="L51" s="160"/>
       <c r="M51" s="35"/>
       <c r="N51" s="35"/>
       <c r="O51" s="45" t="s">
@@ -40177,18 +40178,18 @@
       <c r="R51" s="40"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="176"/>
-      <c r="B52" s="179"/>
-      <c r="C52" s="183"/>
-      <c r="D52" s="184"/>
-      <c r="E52" s="189"/>
-      <c r="F52" s="190"/>
-      <c r="G52" s="195"/>
-      <c r="H52" s="196"/>
-      <c r="I52" s="195"/>
-      <c r="J52" s="196"/>
-      <c r="K52" s="195"/>
-      <c r="L52" s="196"/>
+      <c r="A52" s="181"/>
+      <c r="B52" s="172"/>
+      <c r="C52" s="167"/>
+      <c r="D52" s="168"/>
+      <c r="E52" s="155"/>
+      <c r="F52" s="156"/>
+      <c r="G52" s="161"/>
+      <c r="H52" s="162"/>
+      <c r="I52" s="161"/>
+      <c r="J52" s="162"/>
+      <c r="K52" s="161"/>
+      <c r="L52" s="162"/>
       <c r="M52" s="35"/>
       <c r="N52" s="35"/>
       <c r="O52" s="45" t="s">
@@ -40199,18 +40200,18 @@
       <c r="R52" s="40"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="176"/>
-      <c r="B53" s="179"/>
-      <c r="C53" s="183"/>
-      <c r="D53" s="184"/>
-      <c r="E53" s="189"/>
-      <c r="F53" s="190"/>
-      <c r="G53" s="195"/>
-      <c r="H53" s="196"/>
-      <c r="I53" s="195"/>
-      <c r="J53" s="196"/>
-      <c r="K53" s="195"/>
-      <c r="L53" s="196"/>
+      <c r="A53" s="181"/>
+      <c r="B53" s="172"/>
+      <c r="C53" s="167"/>
+      <c r="D53" s="168"/>
+      <c r="E53" s="155"/>
+      <c r="F53" s="156"/>
+      <c r="G53" s="161"/>
+      <c r="H53" s="162"/>
+      <c r="I53" s="161"/>
+      <c r="J53" s="162"/>
+      <c r="K53" s="161"/>
+      <c r="L53" s="162"/>
       <c r="M53" s="35"/>
       <c r="N53" s="35"/>
       <c r="O53" s="42" t="s">
@@ -40221,34 +40222,34 @@
       <c r="R53" s="44"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="176"/>
-      <c r="B54" s="179"/>
-      <c r="C54" s="183"/>
-      <c r="D54" s="184"/>
-      <c r="E54" s="189"/>
-      <c r="F54" s="190"/>
-      <c r="G54" s="195"/>
-      <c r="H54" s="196"/>
-      <c r="I54" s="195"/>
-      <c r="J54" s="196"/>
-      <c r="K54" s="195"/>
-      <c r="L54" s="196"/>
+      <c r="A54" s="181"/>
+      <c r="B54" s="172"/>
+      <c r="C54" s="167"/>
+      <c r="D54" s="168"/>
+      <c r="E54" s="155"/>
+      <c r="F54" s="156"/>
+      <c r="G54" s="161"/>
+      <c r="H54" s="162"/>
+      <c r="I54" s="161"/>
+      <c r="J54" s="162"/>
+      <c r="K54" s="161"/>
+      <c r="L54" s="162"/>
       <c r="M54" s="35"/>
       <c r="N54" s="35"/>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="176"/>
-      <c r="B55" s="180"/>
-      <c r="C55" s="185"/>
-      <c r="D55" s="186"/>
-      <c r="E55" s="191"/>
-      <c r="F55" s="192"/>
-      <c r="G55" s="197"/>
-      <c r="H55" s="198"/>
-      <c r="I55" s="197"/>
-      <c r="J55" s="198"/>
-      <c r="K55" s="197"/>
-      <c r="L55" s="198"/>
+      <c r="A55" s="181"/>
+      <c r="B55" s="173"/>
+      <c r="C55" s="169"/>
+      <c r="D55" s="170"/>
+      <c r="E55" s="157"/>
+      <c r="F55" s="158"/>
+      <c r="G55" s="163"/>
+      <c r="H55" s="164"/>
+      <c r="I55" s="163"/>
+      <c r="J55" s="164"/>
+      <c r="K55" s="163"/>
+      <c r="L55" s="164"/>
       <c r="M55" s="35"/>
       <c r="N55" s="35"/>
       <c r="O55" s="38" t="s">
@@ -40259,30 +40260,30 @@
       <c r="R55" s="40"/>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="176"/>
-      <c r="B56" s="178" t="s">
+      <c r="A56" s="181"/>
+      <c r="B56" s="171" t="s">
         <v>1046</v>
       </c>
-      <c r="C56" s="181" t="s">
+      <c r="C56" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="182"/>
-      <c r="E56" s="187" t="s">
+      <c r="D56" s="166"/>
+      <c r="E56" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="188"/>
-      <c r="G56" s="187" t="s">
+      <c r="F56" s="154"/>
+      <c r="G56" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="188"/>
-      <c r="I56" s="193" t="s">
+      <c r="H56" s="154"/>
+      <c r="I56" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="J56" s="194"/>
-      <c r="K56" s="193" t="s">
+      <c r="J56" s="160"/>
+      <c r="K56" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="194"/>
+      <c r="L56" s="160"/>
       <c r="M56" s="35"/>
       <c r="N56" s="35"/>
       <c r="O56" s="45" t="s">
@@ -40293,18 +40294,18 @@
       <c r="R56" s="40"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="176"/>
-      <c r="B57" s="179"/>
-      <c r="C57" s="183"/>
-      <c r="D57" s="184"/>
-      <c r="E57" s="189"/>
-      <c r="F57" s="190"/>
-      <c r="G57" s="189"/>
-      <c r="H57" s="190"/>
-      <c r="I57" s="195"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="195"/>
-      <c r="L57" s="196"/>
+      <c r="A57" s="181"/>
+      <c r="B57" s="172"/>
+      <c r="C57" s="167"/>
+      <c r="D57" s="168"/>
+      <c r="E57" s="155"/>
+      <c r="F57" s="156"/>
+      <c r="G57" s="155"/>
+      <c r="H57" s="156"/>
+      <c r="I57" s="161"/>
+      <c r="J57" s="162"/>
+      <c r="K57" s="161"/>
+      <c r="L57" s="162"/>
       <c r="M57" s="35"/>
       <c r="N57" s="35"/>
       <c r="O57" s="45" t="s">
@@ -40315,18 +40316,18 @@
       <c r="R57" s="40"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="176"/>
-      <c r="B58" s="179"/>
-      <c r="C58" s="183"/>
-      <c r="D58" s="184"/>
-      <c r="E58" s="189"/>
-      <c r="F58" s="190"/>
-      <c r="G58" s="189"/>
-      <c r="H58" s="190"/>
-      <c r="I58" s="195"/>
-      <c r="J58" s="196"/>
-      <c r="K58" s="195"/>
-      <c r="L58" s="196"/>
+      <c r="A58" s="181"/>
+      <c r="B58" s="172"/>
+      <c r="C58" s="167"/>
+      <c r="D58" s="168"/>
+      <c r="E58" s="155"/>
+      <c r="F58" s="156"/>
+      <c r="G58" s="155"/>
+      <c r="H58" s="156"/>
+      <c r="I58" s="161"/>
+      <c r="J58" s="162"/>
+      <c r="K58" s="161"/>
+      <c r="L58" s="162"/>
       <c r="M58" s="35"/>
       <c r="N58" s="35"/>
       <c r="O58" s="45" t="s">
@@ -40337,18 +40338,18 @@
       <c r="R58" s="40"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="176"/>
-      <c r="B59" s="179"/>
-      <c r="C59" s="183"/>
-      <c r="D59" s="184"/>
-      <c r="E59" s="189"/>
-      <c r="F59" s="190"/>
-      <c r="G59" s="189"/>
-      <c r="H59" s="190"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="196"/>
-      <c r="K59" s="195"/>
-      <c r="L59" s="196"/>
+      <c r="A59" s="181"/>
+      <c r="B59" s="172"/>
+      <c r="C59" s="167"/>
+      <c r="D59" s="168"/>
+      <c r="E59" s="155"/>
+      <c r="F59" s="156"/>
+      <c r="G59" s="155"/>
+      <c r="H59" s="156"/>
+      <c r="I59" s="161"/>
+      <c r="J59" s="162"/>
+      <c r="K59" s="161"/>
+      <c r="L59" s="162"/>
       <c r="M59" s="35"/>
       <c r="N59" s="35"/>
       <c r="O59" s="42" t="s">
@@ -40359,18 +40360,18 @@
       <c r="R59" s="44"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="176"/>
-      <c r="B60" s="180"/>
-      <c r="C60" s="185"/>
-      <c r="D60" s="186"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="197"/>
-      <c r="J60" s="198"/>
-      <c r="K60" s="197"/>
-      <c r="L60" s="198"/>
+      <c r="A60" s="181"/>
+      <c r="B60" s="173"/>
+      <c r="C60" s="169"/>
+      <c r="D60" s="170"/>
+      <c r="E60" s="157"/>
+      <c r="F60" s="158"/>
+      <c r="G60" s="157"/>
+      <c r="H60" s="158"/>
+      <c r="I60" s="163"/>
+      <c r="J60" s="164"/>
+      <c r="K60" s="163"/>
+      <c r="L60" s="164"/>
       <c r="M60" s="35"/>
       <c r="N60" s="35"/>
       <c r="O60" s="35"/>
@@ -40379,30 +40380,30 @@
       <c r="R60" s="35"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="176"/>
-      <c r="B61" s="178" t="s">
+      <c r="A61" s="181"/>
+      <c r="B61" s="171" t="s">
         <v>1051</v>
       </c>
-      <c r="C61" s="199" t="s">
+      <c r="C61" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="200"/>
-      <c r="E61" s="181" t="s">
+      <c r="D61" s="175"/>
+      <c r="E61" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="182"/>
-      <c r="G61" s="187" t="s">
+      <c r="F61" s="166"/>
+      <c r="G61" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="188"/>
-      <c r="I61" s="187" t="s">
+      <c r="H61" s="154"/>
+      <c r="I61" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="188"/>
-      <c r="K61" s="193" t="s">
+      <c r="J61" s="154"/>
+      <c r="K61" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="L61" s="194"/>
+      <c r="L61" s="160"/>
       <c r="M61" s="35"/>
       <c r="N61" s="35"/>
       <c r="O61" s="35"/>
@@ -40411,18 +40412,18 @@
       <c r="R61" s="35"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="176"/>
-      <c r="B62" s="179"/>
-      <c r="C62" s="201"/>
-      <c r="D62" s="202"/>
-      <c r="E62" s="183"/>
-      <c r="F62" s="184"/>
-      <c r="G62" s="189"/>
-      <c r="H62" s="190"/>
-      <c r="I62" s="189"/>
-      <c r="J62" s="190"/>
-      <c r="K62" s="195"/>
-      <c r="L62" s="196"/>
+      <c r="A62" s="181"/>
+      <c r="B62" s="172"/>
+      <c r="C62" s="176"/>
+      <c r="D62" s="177"/>
+      <c r="E62" s="167"/>
+      <c r="F62" s="168"/>
+      <c r="G62" s="155"/>
+      <c r="H62" s="156"/>
+      <c r="I62" s="155"/>
+      <c r="J62" s="156"/>
+      <c r="K62" s="161"/>
+      <c r="L62" s="162"/>
       <c r="M62" s="35"/>
       <c r="N62" s="35"/>
       <c r="O62" s="35"/>
@@ -40431,18 +40432,18 @@
       <c r="R62" s="35"/>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="176"/>
-      <c r="B63" s="179"/>
-      <c r="C63" s="201"/>
-      <c r="D63" s="202"/>
-      <c r="E63" s="183"/>
-      <c r="F63" s="184"/>
-      <c r="G63" s="189"/>
-      <c r="H63" s="190"/>
-      <c r="I63" s="189"/>
-      <c r="J63" s="190"/>
-      <c r="K63" s="195"/>
-      <c r="L63" s="196"/>
+      <c r="A63" s="181"/>
+      <c r="B63" s="172"/>
+      <c r="C63" s="176"/>
+      <c r="D63" s="177"/>
+      <c r="E63" s="167"/>
+      <c r="F63" s="168"/>
+      <c r="G63" s="155"/>
+      <c r="H63" s="156"/>
+      <c r="I63" s="155"/>
+      <c r="J63" s="156"/>
+      <c r="K63" s="161"/>
+      <c r="L63" s="162"/>
       <c r="M63" s="35"/>
       <c r="N63" s="35"/>
       <c r="O63" s="35"/>
@@ -40451,18 +40452,18 @@
       <c r="R63" s="35"/>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="176"/>
-      <c r="B64" s="179"/>
-      <c r="C64" s="201"/>
-      <c r="D64" s="202"/>
-      <c r="E64" s="183"/>
-      <c r="F64" s="184"/>
-      <c r="G64" s="189"/>
-      <c r="H64" s="190"/>
-      <c r="I64" s="189"/>
-      <c r="J64" s="190"/>
-      <c r="K64" s="195"/>
-      <c r="L64" s="196"/>
+      <c r="A64" s="181"/>
+      <c r="B64" s="172"/>
+      <c r="C64" s="176"/>
+      <c r="D64" s="177"/>
+      <c r="E64" s="167"/>
+      <c r="F64" s="168"/>
+      <c r="G64" s="155"/>
+      <c r="H64" s="156"/>
+      <c r="I64" s="155"/>
+      <c r="J64" s="156"/>
+      <c r="K64" s="161"/>
+      <c r="L64" s="162"/>
       <c r="M64" s="35"/>
       <c r="N64" s="35"/>
       <c r="O64" s="35"/>
@@ -40471,18 +40472,18 @@
       <c r="R64" s="35"/>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="176"/>
-      <c r="B65" s="180"/>
-      <c r="C65" s="203"/>
-      <c r="D65" s="204"/>
-      <c r="E65" s="185"/>
-      <c r="F65" s="186"/>
-      <c r="G65" s="191"/>
-      <c r="H65" s="192"/>
-      <c r="I65" s="191"/>
-      <c r="J65" s="192"/>
-      <c r="K65" s="197"/>
-      <c r="L65" s="198"/>
+      <c r="A65" s="181"/>
+      <c r="B65" s="173"/>
+      <c r="C65" s="178"/>
+      <c r="D65" s="179"/>
+      <c r="E65" s="169"/>
+      <c r="F65" s="170"/>
+      <c r="G65" s="157"/>
+      <c r="H65" s="158"/>
+      <c r="I65" s="157"/>
+      <c r="J65" s="158"/>
+      <c r="K65" s="163"/>
+      <c r="L65" s="164"/>
       <c r="M65" s="35"/>
       <c r="N65" s="35"/>
       <c r="O65" s="35"/>
@@ -40491,30 +40492,30 @@
       <c r="R65" s="35"/>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="176"/>
-      <c r="B66" s="178" t="s">
+      <c r="A66" s="181"/>
+      <c r="B66" s="171" t="s">
         <v>1052</v>
       </c>
-      <c r="C66" s="199" t="s">
+      <c r="C66" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="200"/>
-      <c r="E66" s="199" t="s">
+      <c r="D66" s="175"/>
+      <c r="E66" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="200"/>
-      <c r="G66" s="181" t="s">
+      <c r="F66" s="175"/>
+      <c r="G66" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="182"/>
-      <c r="I66" s="181" t="s">
+      <c r="H66" s="166"/>
+      <c r="I66" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="182"/>
-      <c r="K66" s="187" t="s">
+      <c r="J66" s="166"/>
+      <c r="K66" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="188"/>
+      <c r="L66" s="154"/>
       <c r="M66" s="35"/>
       <c r="N66" s="35"/>
       <c r="O66" s="35"/>
@@ -40523,18 +40524,18 @@
       <c r="R66" s="35"/>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="176"/>
-      <c r="B67" s="179"/>
-      <c r="C67" s="201"/>
-      <c r="D67" s="202"/>
-      <c r="E67" s="201"/>
-      <c r="F67" s="202"/>
-      <c r="G67" s="183"/>
-      <c r="H67" s="184"/>
-      <c r="I67" s="183"/>
-      <c r="J67" s="184"/>
-      <c r="K67" s="189"/>
-      <c r="L67" s="190"/>
+      <c r="A67" s="181"/>
+      <c r="B67" s="172"/>
+      <c r="C67" s="176"/>
+      <c r="D67" s="177"/>
+      <c r="E67" s="176"/>
+      <c r="F67" s="177"/>
+      <c r="G67" s="167"/>
+      <c r="H67" s="168"/>
+      <c r="I67" s="167"/>
+      <c r="J67" s="168"/>
+      <c r="K67" s="155"/>
+      <c r="L67" s="156"/>
       <c r="M67" s="35"/>
       <c r="N67" s="35"/>
       <c r="O67" s="35"/>
@@ -40543,18 +40544,18 @@
       <c r="R67" s="35"/>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="176"/>
-      <c r="B68" s="179"/>
-      <c r="C68" s="201"/>
-      <c r="D68" s="202"/>
-      <c r="E68" s="201"/>
-      <c r="F68" s="202"/>
-      <c r="G68" s="183"/>
-      <c r="H68" s="184"/>
-      <c r="I68" s="183"/>
-      <c r="J68" s="184"/>
-      <c r="K68" s="189"/>
-      <c r="L68" s="190"/>
+      <c r="A68" s="181"/>
+      <c r="B68" s="172"/>
+      <c r="C68" s="176"/>
+      <c r="D68" s="177"/>
+      <c r="E68" s="176"/>
+      <c r="F68" s="177"/>
+      <c r="G68" s="167"/>
+      <c r="H68" s="168"/>
+      <c r="I68" s="167"/>
+      <c r="J68" s="168"/>
+      <c r="K68" s="155"/>
+      <c r="L68" s="156"/>
       <c r="M68" s="35"/>
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
@@ -40563,18 +40564,18 @@
       <c r="R68" s="35"/>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="176"/>
-      <c r="B69" s="179"/>
-      <c r="C69" s="201"/>
-      <c r="D69" s="202"/>
-      <c r="E69" s="201"/>
-      <c r="F69" s="202"/>
-      <c r="G69" s="183"/>
-      <c r="H69" s="184"/>
-      <c r="I69" s="183"/>
-      <c r="J69" s="184"/>
-      <c r="K69" s="189"/>
-      <c r="L69" s="190"/>
+      <c r="A69" s="181"/>
+      <c r="B69" s="172"/>
+      <c r="C69" s="176"/>
+      <c r="D69" s="177"/>
+      <c r="E69" s="176"/>
+      <c r="F69" s="177"/>
+      <c r="G69" s="167"/>
+      <c r="H69" s="168"/>
+      <c r="I69" s="167"/>
+      <c r="J69" s="168"/>
+      <c r="K69" s="155"/>
+      <c r="L69" s="156"/>
       <c r="M69" s="35"/>
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
@@ -40583,18 +40584,18 @@
       <c r="R69" s="35"/>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="176"/>
-      <c r="B70" s="180"/>
-      <c r="C70" s="203"/>
-      <c r="D70" s="204"/>
-      <c r="E70" s="203"/>
-      <c r="F70" s="204"/>
-      <c r="G70" s="185"/>
-      <c r="H70" s="186"/>
-      <c r="I70" s="185"/>
-      <c r="J70" s="186"/>
-      <c r="K70" s="191"/>
-      <c r="L70" s="192"/>
+      <c r="A70" s="181"/>
+      <c r="B70" s="173"/>
+      <c r="C70" s="178"/>
+      <c r="D70" s="179"/>
+      <c r="E70" s="178"/>
+      <c r="F70" s="179"/>
+      <c r="G70" s="169"/>
+      <c r="H70" s="170"/>
+      <c r="I70" s="169"/>
+      <c r="J70" s="170"/>
+      <c r="K70" s="157"/>
+      <c r="L70" s="158"/>
       <c r="M70" s="35"/>
       <c r="N70" s="35"/>
       <c r="O70" s="35"/>
@@ -40603,30 +40604,30 @@
       <c r="R70" s="35"/>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="176"/>
-      <c r="B71" s="178" t="s">
+      <c r="A71" s="181"/>
+      <c r="B71" s="171" t="s">
         <v>1053</v>
       </c>
-      <c r="C71" s="199" t="s">
+      <c r="C71" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="200"/>
-      <c r="E71" s="199" t="s">
+      <c r="D71" s="175"/>
+      <c r="E71" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="F71" s="200"/>
-      <c r="G71" s="199" t="s">
+      <c r="F71" s="175"/>
+      <c r="G71" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="H71" s="200"/>
-      <c r="I71" s="199" t="s">
+      <c r="H71" s="175"/>
+      <c r="I71" s="174" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="200"/>
-      <c r="K71" s="181" t="s">
+      <c r="J71" s="175"/>
+      <c r="K71" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="182"/>
+      <c r="L71" s="166"/>
       <c r="M71" s="35"/>
       <c r="N71" s="35"/>
       <c r="O71" s="35"/>
@@ -40635,18 +40636,18 @@
       <c r="R71" s="35"/>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="176"/>
-      <c r="B72" s="179"/>
-      <c r="C72" s="201"/>
-      <c r="D72" s="202"/>
-      <c r="E72" s="201"/>
-      <c r="F72" s="202"/>
-      <c r="G72" s="201"/>
-      <c r="H72" s="202"/>
-      <c r="I72" s="201"/>
-      <c r="J72" s="202"/>
-      <c r="K72" s="183"/>
-      <c r="L72" s="184"/>
+      <c r="A72" s="181"/>
+      <c r="B72" s="172"/>
+      <c r="C72" s="176"/>
+      <c r="D72" s="177"/>
+      <c r="E72" s="176"/>
+      <c r="F72" s="177"/>
+      <c r="G72" s="176"/>
+      <c r="H72" s="177"/>
+      <c r="I72" s="176"/>
+      <c r="J72" s="177"/>
+      <c r="K72" s="167"/>
+      <c r="L72" s="168"/>
       <c r="M72" s="35"/>
       <c r="N72" s="35"/>
       <c r="O72" s="35"/>
@@ -40655,18 +40656,18 @@
       <c r="R72" s="35"/>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="176"/>
-      <c r="B73" s="179"/>
-      <c r="C73" s="201"/>
-      <c r="D73" s="202"/>
-      <c r="E73" s="201"/>
-      <c r="F73" s="202"/>
-      <c r="G73" s="201"/>
-      <c r="H73" s="202"/>
-      <c r="I73" s="201"/>
-      <c r="J73" s="202"/>
-      <c r="K73" s="183"/>
-      <c r="L73" s="184"/>
+      <c r="A73" s="181"/>
+      <c r="B73" s="172"/>
+      <c r="C73" s="176"/>
+      <c r="D73" s="177"/>
+      <c r="E73" s="176"/>
+      <c r="F73" s="177"/>
+      <c r="G73" s="176"/>
+      <c r="H73" s="177"/>
+      <c r="I73" s="176"/>
+      <c r="J73" s="177"/>
+      <c r="K73" s="167"/>
+      <c r="L73" s="168"/>
       <c r="M73" s="35"/>
       <c r="N73" s="35"/>
       <c r="O73" s="35"/>
@@ -40675,18 +40676,18 @@
       <c r="R73" s="35"/>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="176"/>
-      <c r="B74" s="179"/>
-      <c r="C74" s="201"/>
-      <c r="D74" s="202"/>
-      <c r="E74" s="201"/>
-      <c r="F74" s="202"/>
-      <c r="G74" s="201"/>
-      <c r="H74" s="202"/>
-      <c r="I74" s="201"/>
-      <c r="J74" s="202"/>
-      <c r="K74" s="183"/>
-      <c r="L74" s="184"/>
+      <c r="A74" s="181"/>
+      <c r="B74" s="172"/>
+      <c r="C74" s="176"/>
+      <c r="D74" s="177"/>
+      <c r="E74" s="176"/>
+      <c r="F74" s="177"/>
+      <c r="G74" s="176"/>
+      <c r="H74" s="177"/>
+      <c r="I74" s="176"/>
+      <c r="J74" s="177"/>
+      <c r="K74" s="167"/>
+      <c r="L74" s="168"/>
       <c r="M74" s="35"/>
       <c r="N74" s="35"/>
       <c r="O74" s="35"/>
@@ -40695,18 +40696,18 @@
       <c r="R74" s="35"/>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="177"/>
-      <c r="B75" s="180"/>
-      <c r="C75" s="203"/>
-      <c r="D75" s="204"/>
-      <c r="E75" s="203"/>
-      <c r="F75" s="204"/>
-      <c r="G75" s="203"/>
-      <c r="H75" s="204"/>
-      <c r="I75" s="203"/>
-      <c r="J75" s="204"/>
-      <c r="K75" s="185"/>
-      <c r="L75" s="186"/>
+      <c r="A75" s="182"/>
+      <c r="B75" s="173"/>
+      <c r="C75" s="178"/>
+      <c r="D75" s="179"/>
+      <c r="E75" s="178"/>
+      <c r="F75" s="179"/>
+      <c r="G75" s="178"/>
+      <c r="H75" s="179"/>
+      <c r="I75" s="178"/>
+      <c r="J75" s="179"/>
+      <c r="K75" s="169"/>
+      <c r="L75" s="170"/>
       <c r="M75" s="35"/>
       <c r="N75" s="35"/>
       <c r="O75" s="35"/>
@@ -40736,6 +40737,34 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="A47:B50"/>
+    <mergeCell ref="C47:L48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A51:A75"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C51:D55"/>
+    <mergeCell ref="E51:F55"/>
+    <mergeCell ref="G51:H55"/>
+    <mergeCell ref="B61:B65"/>
+    <mergeCell ref="C61:D65"/>
+    <mergeCell ref="E61:F65"/>
+    <mergeCell ref="G61:H65"/>
+    <mergeCell ref="I51:J55"/>
+    <mergeCell ref="K51:L55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:D60"/>
+    <mergeCell ref="E56:F60"/>
+    <mergeCell ref="G56:H60"/>
+    <mergeCell ref="I56:J60"/>
+    <mergeCell ref="K56:L60"/>
     <mergeCell ref="I61:J65"/>
     <mergeCell ref="K61:L65"/>
     <mergeCell ref="K71:L75"/>
@@ -40750,34 +40779,6 @@
     <mergeCell ref="E71:F75"/>
     <mergeCell ref="G71:H75"/>
     <mergeCell ref="I71:J75"/>
-    <mergeCell ref="I51:J55"/>
-    <mergeCell ref="K51:L55"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:D60"/>
-    <mergeCell ref="E56:F60"/>
-    <mergeCell ref="G56:H60"/>
-    <mergeCell ref="I56:J60"/>
-    <mergeCell ref="K56:L60"/>
-    <mergeCell ref="A51:A75"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C51:D55"/>
-    <mergeCell ref="E51:F55"/>
-    <mergeCell ref="G51:H55"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="C61:D65"/>
-    <mergeCell ref="E61:F65"/>
-    <mergeCell ref="G61:H65"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A47:B50"/>
-    <mergeCell ref="C47:L48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -63805,31 +63806,32 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" t="s">
+      <c r="A13" s="208" t="s">
         <v>305</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="208" t="s">
         <v>306</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="208" t="s">
         <v>725</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="208" t="s">
         <v>726</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="208" t="s">
         <v>727</v>
       </c>
-      <c r="H13" t="s">
+      <c r="G13" s="208"/>
+      <c r="H13" s="208" t="s">
         <v>750</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="208" t="s">
         <v>2</v>
       </c>
     </row>
@@ -64019,34 +64021,34 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" t="s">
+      <c r="A23" s="208" t="s">
         <v>758</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="208" t="s">
         <v>759</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="208" t="s">
         <v>31</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="208" t="s">
         <v>87</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="208" t="s">
         <v>760</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="208" t="s">
         <v>761</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="208" t="s">
         <v>762</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="208" t="s">
         <v>763</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="208" t="s">
         <v>764</v>
       </c>
     </row>
